--- a/pi0_eta_database.xlsx
+++ b/pi0_eta_database.xlsx
@@ -730,11 +730,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sigma_U, sigma_LT, sigma_TT</t>
+          <t>sigma_U, sigma_LT, sigma_TT, sigma_LT'</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -743,12 +743,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.368-0.369</t>
+          <t>0.335-0.394</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.3959..-0.1985</t>
+          <t>-0.4041..-0.1465</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>PRC 83 025201 (2011)</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR231"/>
+  <dimension ref="A1:AR245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25411,37 +25411,39 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ha11_1.94</t>
+          <t>ha11_Kin3</t>
         </is>
       </c>
       <c r="E177" s="2" t="n">
-        <v>1.941</v>
+        <v>2.35</v>
       </c>
       <c r="F177" s="2" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="G177" s="2" t="n">
-        <v>-0.1985</v>
+        <v>-0.1825</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>0.1675778912571499</v>
+        <v>0.173</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>0.03092210874285006</v>
+        <v>0.0095</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="K177" s="3" t="inlineStr"/>
       <c r="L177" s="3" t="inlineStr"/>
       <c r="M177" s="3" t="n">
-        <v>1.941</v>
+        <v>2.35</v>
       </c>
       <c r="N177" s="4" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O177" s="3" t="inlineStr"/>
-      <c r="P177" s="2" t="inlineStr"/>
+      <c r="P177" s="2" t="n">
+        <v>0.649</v>
+      </c>
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="n">
         <v>5.752</v>
@@ -25460,39 +25462,45 @@
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>PRC 83 025201 (2011)</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X177" s="5" t="n">
-        <v>571</v>
+        <v>377</v>
       </c>
       <c r="Y177" s="5" t="n">
         <v>10</v>
       </c>
       <c r="Z177" s="5" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AA177" s="5" t="n">
-        <v>17</v>
+        <v>-13</v>
       </c>
       <c r="AB177" s="5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AC177" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AD177" s="5" t="n">
-        <v>-39</v>
+        <v>-12</v>
       </c>
       <c r="AE177" s="5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AF177" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG177" s="5" t="inlineStr"/>
-      <c r="AH177" s="5" t="inlineStr"/>
-      <c r="AI177" s="5" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="AG177" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH177" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="AI177" s="5" t="n">
+        <v>20</v>
+      </c>
       <c r="AJ177" s="5" t="inlineStr"/>
       <c r="AK177" s="5" t="inlineStr"/>
       <c r="AL177" s="5" t="inlineStr"/>
@@ -25521,37 +25529,39 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ha11_1.94</t>
+          <t>ha11_Kin3</t>
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>1.941</v>
+        <v>2.35</v>
       </c>
       <c r="F178" s="2" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="G178" s="2" t="n">
-        <v>-0.2185</v>
+        <v>-0.2028</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>0.1675778912571499</v>
+        <v>0.173</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>0.05092210874285005</v>
+        <v>0.0298</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="K178" s="3" t="inlineStr"/>
       <c r="L178" s="3" t="inlineStr"/>
       <c r="M178" s="3" t="n">
-        <v>1.941</v>
+        <v>2.35</v>
       </c>
       <c r="N178" s="4" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O178" s="3" t="inlineStr"/>
-      <c r="P178" s="2" t="inlineStr"/>
+      <c r="P178" s="2" t="n">
+        <v>0.649</v>
+      </c>
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="n">
         <v>5.752</v>
@@ -25570,39 +25580,45 @@
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>PRC 83 025201 (2011)</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X178" s="5" t="n">
-        <v>600</v>
+        <v>381</v>
       </c>
       <c r="Y178" s="5" t="n">
         <v>12</v>
       </c>
       <c r="Z178" s="5" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AA178" s="5" t="n">
-        <v>-43</v>
+        <v>38</v>
       </c>
       <c r="AB178" s="5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AC178" s="5" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AD178" s="5" t="n">
-        <v>-110</v>
+        <v>-25</v>
       </c>
       <c r="AE178" s="5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AF178" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG178" s="5" t="inlineStr"/>
-      <c r="AH178" s="5" t="inlineStr"/>
-      <c r="AI178" s="5" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="AG178" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="AH178" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI178" s="5" t="n">
+        <v>21</v>
+      </c>
       <c r="AJ178" s="5" t="inlineStr"/>
       <c r="AK178" s="5" t="inlineStr"/>
       <c r="AL178" s="5" t="inlineStr"/>
@@ -25631,37 +25647,39 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ha11_1.94</t>
+          <t>ha11_Kin3</t>
         </is>
       </c>
       <c r="E179" s="2" t="n">
-        <v>1.941</v>
+        <v>2.35</v>
       </c>
       <c r="F179" s="2" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="G179" s="2" t="n">
-        <v>-0.2425</v>
+        <v>-0.2276</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>0.1675778912571499</v>
+        <v>0.173</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>0.07492210874285005</v>
+        <v>0.0546</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="K179" s="3" t="inlineStr"/>
       <c r="L179" s="3" t="inlineStr"/>
       <c r="M179" s="3" t="n">
-        <v>1.941</v>
+        <v>2.35</v>
       </c>
       <c r="N179" s="4" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O179" s="3" t="inlineStr"/>
-      <c r="P179" s="2" t="inlineStr"/>
+      <c r="P179" s="2" t="n">
+        <v>0.649</v>
+      </c>
       <c r="Q179" t="inlineStr"/>
       <c r="R179" t="n">
         <v>5.752</v>
@@ -25680,39 +25698,45 @@
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>PRC 83 025201 (2011)</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X179" s="5" t="n">
-        <v>641</v>
+        <v>403</v>
       </c>
       <c r="Y179" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z179" s="5" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AA179" s="5" t="n">
-        <v>-23</v>
+        <v>-25</v>
       </c>
       <c r="AB179" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC179" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD179" s="5" t="n">
-        <v>-141</v>
+        <v>-74</v>
       </c>
       <c r="AE179" s="5" t="n">
         <v>22</v>
       </c>
       <c r="AF179" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG179" s="5" t="inlineStr"/>
-      <c r="AH179" s="5" t="inlineStr"/>
-      <c r="AI179" s="5" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="AG179" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="AH179" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI179" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="AJ179" s="5" t="inlineStr"/>
       <c r="AK179" s="5" t="inlineStr"/>
       <c r="AL179" s="5" t="inlineStr"/>
@@ -25741,37 +25765,39 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ha11_1.94</t>
+          <t>ha11_Kin3</t>
         </is>
       </c>
       <c r="E180" s="2" t="n">
-        <v>1.941</v>
+        <v>2.35</v>
       </c>
       <c r="F180" s="2" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="G180" s="2" t="n">
-        <v>-0.2725</v>
+        <v>-0.2574</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>0.1675778912571499</v>
+        <v>0.173</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>0.1049221087428501</v>
+        <v>0.0844</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="K180" s="3" t="inlineStr"/>
       <c r="L180" s="3" t="inlineStr"/>
       <c r="M180" s="3" t="n">
-        <v>1.941</v>
+        <v>2.35</v>
       </c>
       <c r="N180" s="4" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O180" s="3" t="inlineStr"/>
-      <c r="P180" s="2" t="inlineStr"/>
+      <c r="P180" s="2" t="n">
+        <v>0.649</v>
+      </c>
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="n">
         <v>5.752</v>
@@ -25790,39 +25816,45 @@
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>PRC 83 025201 (2011)</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X180" s="5" t="n">
-        <v>673</v>
+        <v>425</v>
       </c>
       <c r="Y180" s="5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Z180" s="5" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AA180" s="5" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
       <c r="AB180" s="5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AC180" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD180" s="5" t="n">
+        <v>-64</v>
+      </c>
+      <c r="AE180" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF180" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="AD180" s="5" t="n">
-        <v>-174</v>
-      </c>
-      <c r="AE180" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF180" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG180" s="5" t="inlineStr"/>
-      <c r="AH180" s="5" t="inlineStr"/>
-      <c r="AI180" s="5" t="inlineStr"/>
+      <c r="AG180" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="AH180" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="AI180" s="5" t="n">
+        <v>30</v>
+      </c>
       <c r="AJ180" s="5" t="inlineStr"/>
       <c r="AK180" s="5" t="inlineStr"/>
       <c r="AL180" s="5" t="inlineStr"/>
@@ -25851,37 +25883,39 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ha11_1.94</t>
+          <t>ha11_Kin3</t>
         </is>
       </c>
       <c r="E181" s="2" t="n">
-        <v>1.941</v>
+        <v>2.35</v>
       </c>
       <c r="F181" s="2" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="G181" s="2" t="n">
-        <v>-0.3065</v>
+        <v>-0.2918</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>0.1675778912571499</v>
+        <v>0.173</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>0.13892210874285</v>
+        <v>0.1188</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="K181" s="3" t="inlineStr"/>
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="3" t="n">
-        <v>1.941</v>
+        <v>2.35</v>
       </c>
       <c r="N181" s="4" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O181" s="3" t="inlineStr"/>
-      <c r="P181" s="2" t="inlineStr"/>
+      <c r="P181" s="2" t="n">
+        <v>0.649</v>
+      </c>
       <c r="Q181" t="inlineStr"/>
       <c r="R181" t="n">
         <v>5.752</v>
@@ -25900,39 +25934,45 @@
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>PRC 83 025201 (2011)</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X181" s="5" t="n">
-        <v>645</v>
+        <v>418</v>
       </c>
       <c r="Y181" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z181" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA181" s="5" t="n">
+        <v>-75</v>
+      </c>
+      <c r="AB181" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC181" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD181" s="5" t="n">
+        <v>-124</v>
+      </c>
+      <c r="AE181" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF181" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="Z181" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA181" s="5" t="n">
-        <v>-103</v>
-      </c>
-      <c r="AB181" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC181" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD181" s="5" t="n">
-        <v>-319</v>
-      </c>
-      <c r="AE181" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF181" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG181" s="5" t="inlineStr"/>
-      <c r="AH181" s="5" t="inlineStr"/>
-      <c r="AI181" s="5" t="inlineStr"/>
+      <c r="AG181" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="AH181" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="AI181" s="5" t="n">
+        <v>17</v>
+      </c>
       <c r="AJ181" s="5" t="inlineStr"/>
       <c r="AK181" s="5" t="inlineStr"/>
       <c r="AL181" s="5" t="inlineStr"/>
@@ -25961,37 +26001,39 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ha11_1.94</t>
+          <t>ha11_Kin3</t>
         </is>
       </c>
       <c r="E182" s="2" t="n">
-        <v>1.941</v>
+        <v>2.35</v>
       </c>
       <c r="F182" s="2" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="G182" s="2" t="n">
-        <v>-0.3465</v>
+        <v>-0.3313</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>0.1675778912571499</v>
+        <v>0.173</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>0.17892210874285</v>
+        <v>0.1583</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="K182" s="3" t="inlineStr"/>
       <c r="L182" s="3" t="inlineStr"/>
       <c r="M182" s="3" t="n">
-        <v>1.941</v>
+        <v>2.35</v>
       </c>
       <c r="N182" s="4" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O182" s="3" t="inlineStr"/>
-      <c r="P182" s="2" t="inlineStr"/>
+      <c r="P182" s="2" t="n">
+        <v>0.649</v>
+      </c>
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="n">
         <v>5.752</v>
@@ -26010,39 +26052,45 @@
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>PRC 83 025201 (2011)</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X182" s="5" t="n">
-        <v>636</v>
+        <v>395</v>
       </c>
       <c r="Y182" s="5" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="Z182" s="5" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AA182" s="5" t="n">
-        <v>-185</v>
+        <v>-91</v>
       </c>
       <c r="AB182" s="5" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="AC182" s="5" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="AD182" s="5" t="n">
-        <v>-352</v>
+        <v>-137</v>
       </c>
       <c r="AE182" s="5" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="AF182" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="AG182" s="5" t="inlineStr"/>
-      <c r="AH182" s="5" t="inlineStr"/>
-      <c r="AI182" s="5" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="AG182" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="AH182" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="AI182" s="5" t="n">
+        <v>23</v>
+      </c>
       <c r="AJ182" s="5" t="inlineStr"/>
       <c r="AK182" s="5" t="inlineStr"/>
       <c r="AL182" s="5" t="inlineStr"/>
@@ -26071,37 +26119,39 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ha11_1.94</t>
+          <t>ha11_Kin3</t>
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>1.941</v>
+        <v>2.35</v>
       </c>
       <c r="F183" s="2" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="G183" s="2" t="n">
-        <v>-0.3945</v>
+        <v>-0.3793</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>0.1675778912571499</v>
+        <v>0.173</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>0.2269221087428501</v>
+        <v>0.2063</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="K183" s="3" t="inlineStr"/>
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="n">
-        <v>1.941</v>
+        <v>2.35</v>
       </c>
       <c r="N183" s="4" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O183" s="3" t="inlineStr"/>
-      <c r="P183" s="2" t="inlineStr"/>
+      <c r="P183" s="2" t="n">
+        <v>0.649</v>
+      </c>
       <c r="Q183" t="inlineStr"/>
       <c r="R183" t="n">
         <v>5.752</v>
@@ -26120,39 +26170,45 @@
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>PRC 83 025201 (2011)</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X183" s="5" t="n">
-        <v>628</v>
+        <v>384</v>
       </c>
       <c r="Y183" s="5" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="Z183" s="5" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="AA183" s="5" t="n">
-        <v>-189</v>
+        <v>-123</v>
       </c>
       <c r="AB183" s="5" t="n">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="AC183" s="5" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="AD183" s="5" t="n">
-        <v>-343</v>
+        <v>-134</v>
       </c>
       <c r="AE183" s="5" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="AF183" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="AG183" s="5" t="inlineStr"/>
-      <c r="AH183" s="5" t="inlineStr"/>
-      <c r="AI183" s="5" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="AG183" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="AH183" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="AI183" s="5" t="n">
+        <v>15</v>
+      </c>
       <c r="AJ183" s="5" t="inlineStr"/>
       <c r="AK183" s="5" t="inlineStr"/>
       <c r="AL183" s="5" t="inlineStr"/>
@@ -26181,37 +26237,39 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ha11_2.35</t>
+          <t>ha11_Kin2</t>
         </is>
       </c>
       <c r="E184" s="2" t="n">
-        <v>2.35</v>
+        <v>1.941</v>
       </c>
       <c r="F184" s="2" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="G184" s="2" t="n">
-        <v>-0.1999</v>
+        <v>-0.1794</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>0.1717939524758059</v>
+        <v>0.17</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>0.02810604752419413</v>
+        <v>0.0094</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="K184" s="3" t="inlineStr"/>
       <c r="L184" s="3" t="inlineStr"/>
       <c r="M184" s="3" t="n">
-        <v>2.35</v>
+        <v>1.941</v>
       </c>
       <c r="N184" s="4" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O184" s="3" t="inlineStr"/>
-      <c r="P184" s="2" t="inlineStr"/>
+      <c r="P184" s="2" t="n">
+        <v>0.769</v>
+      </c>
       <c r="Q184" t="inlineStr"/>
       <c r="R184" t="n">
         <v>5.752</v>
@@ -26230,39 +26288,45 @@
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>PRC 83 025201 (2011)</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X184" s="5" t="n">
-        <v>377</v>
+        <v>571</v>
       </c>
       <c r="Y184" s="5" t="n">
         <v>10</v>
       </c>
       <c r="Z184" s="5" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AA184" s="5" t="n">
-        <v>-13</v>
+        <v>17</v>
       </c>
       <c r="AB184" s="5" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AC184" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AD184" s="5" t="n">
-        <v>-12</v>
+        <v>-39</v>
       </c>
       <c r="AE184" s="5" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AF184" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG184" s="5" t="inlineStr"/>
-      <c r="AH184" s="5" t="inlineStr"/>
-      <c r="AI184" s="5" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AG184" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH184" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="AI184" s="5" t="n">
+        <v>15</v>
+      </c>
       <c r="AJ184" s="5" t="inlineStr"/>
       <c r="AK184" s="5" t="inlineStr"/>
       <c r="AL184" s="5" t="inlineStr"/>
@@ -26291,37 +26355,39 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ha11_2.35</t>
+          <t>ha11_Kin2</t>
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>2.35</v>
+        <v>1.941</v>
       </c>
       <c r="F185" s="2" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="G185" s="2" t="n">
-        <v>-0.2199</v>
+        <v>-0.1996</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>0.1717939524758059</v>
+        <v>0.17</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>0.04810604752419415</v>
+        <v>0.0296</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="K185" s="3" t="inlineStr"/>
       <c r="L185" s="3" t="inlineStr"/>
       <c r="M185" s="3" t="n">
-        <v>2.35</v>
+        <v>1.941</v>
       </c>
       <c r="N185" s="4" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O185" s="3" t="inlineStr"/>
-      <c r="P185" s="2" t="inlineStr"/>
+      <c r="P185" s="2" t="n">
+        <v>0.769</v>
+      </c>
       <c r="Q185" t="inlineStr"/>
       <c r="R185" t="n">
         <v>5.752</v>
@@ -26340,39 +26406,45 @@
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>PRC 83 025201 (2011)</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X185" s="5" t="n">
-        <v>381</v>
+        <v>600</v>
       </c>
       <c r="Y185" s="5" t="n">
         <v>12</v>
       </c>
       <c r="Z185" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA185" s="5" t="n">
+        <v>-43</v>
+      </c>
+      <c r="AB185" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC185" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="AA185" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB185" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC185" s="5" t="n">
+      <c r="AD185" s="5" t="n">
+        <v>-110</v>
+      </c>
+      <c r="AE185" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AD185" s="5" t="n">
-        <v>-25</v>
-      </c>
-      <c r="AE185" s="5" t="n">
-        <v>27</v>
-      </c>
       <c r="AF185" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG185" s="5" t="inlineStr"/>
-      <c r="AH185" s="5" t="inlineStr"/>
-      <c r="AI185" s="5" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="AG185" s="5" t="n">
+        <v>136</v>
+      </c>
+      <c r="AH185" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="AI185" s="5" t="n">
+        <v>24</v>
+      </c>
       <c r="AJ185" s="5" t="inlineStr"/>
       <c r="AK185" s="5" t="inlineStr"/>
       <c r="AL185" s="5" t="inlineStr"/>
@@ -26401,37 +26473,39 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ha11_2.35</t>
+          <t>ha11_Kin2</t>
         </is>
       </c>
       <c r="E186" s="2" t="n">
-        <v>2.35</v>
+        <v>1.941</v>
       </c>
       <c r="F186" s="2" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="G186" s="2" t="n">
-        <v>-0.2439</v>
+        <v>-0.2241</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>0.1717939524758059</v>
+        <v>0.17</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>0.07210604752419414</v>
+        <v>0.0541</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="K186" s="3" t="inlineStr"/>
       <c r="L186" s="3" t="inlineStr"/>
       <c r="M186" s="3" t="n">
-        <v>2.35</v>
+        <v>1.941</v>
       </c>
       <c r="N186" s="4" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O186" s="3" t="inlineStr"/>
-      <c r="P186" s="2" t="inlineStr"/>
+      <c r="P186" s="2" t="n">
+        <v>0.769</v>
+      </c>
       <c r="Q186" t="inlineStr"/>
       <c r="R186" t="n">
         <v>5.752</v>
@@ -26450,39 +26524,45 @@
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>PRC 83 025201 (2011)</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X186" s="5" t="n">
-        <v>403</v>
+        <v>641</v>
       </c>
       <c r="Y186" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z186" s="5" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AA186" s="5" t="n">
-        <v>-25</v>
+        <v>-23</v>
       </c>
       <c r="AB186" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC186" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD186" s="5" t="n">
-        <v>-74</v>
+        <v>-141</v>
       </c>
       <c r="AE186" s="5" t="n">
         <v>22</v>
       </c>
       <c r="AF186" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG186" s="5" t="inlineStr"/>
-      <c r="AH186" s="5" t="inlineStr"/>
-      <c r="AI186" s="5" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="AG186" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="AH186" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="AI186" s="5" t="n">
+        <v>41</v>
+      </c>
       <c r="AJ186" s="5" t="inlineStr"/>
       <c r="AK186" s="5" t="inlineStr"/>
       <c r="AL186" s="5" t="inlineStr"/>
@@ -26511,37 +26591,39 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>ha11_2.35</t>
+          <t>ha11_Kin2</t>
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>2.35</v>
+        <v>1.941</v>
       </c>
       <c r="F187" s="2" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="G187" s="2" t="n">
-        <v>-0.2739</v>
+        <v>-0.2539</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>0.1717939524758059</v>
+        <v>0.17</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>0.1021060475241941</v>
+        <v>0.0839</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="K187" s="3" t="inlineStr"/>
       <c r="L187" s="3" t="inlineStr"/>
       <c r="M187" s="3" t="n">
-        <v>2.35</v>
+        <v>1.941</v>
       </c>
       <c r="N187" s="4" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O187" s="3" t="inlineStr"/>
-      <c r="P187" s="2" t="inlineStr"/>
+      <c r="P187" s="2" t="n">
+        <v>0.769</v>
+      </c>
       <c r="Q187" t="inlineStr"/>
       <c r="R187" t="n">
         <v>5.752</v>
@@ -26560,39 +26642,45 @@
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>PRC 83 025201 (2011)</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X187" s="5" t="n">
-        <v>425</v>
+        <v>673</v>
       </c>
       <c r="Y187" s="5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Z187" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA187" s="5" t="n">
+        <v>-19</v>
+      </c>
+      <c r="AB187" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC187" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="AA187" s="5" t="n">
-        <v>-26</v>
-      </c>
-      <c r="AB187" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC187" s="5" t="n">
-        <v>13</v>
-      </c>
       <c r="AD187" s="5" t="n">
-        <v>-64</v>
+        <v>-174</v>
       </c>
       <c r="AE187" s="5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AF187" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG187" s="5" t="inlineStr"/>
-      <c r="AH187" s="5" t="inlineStr"/>
-      <c r="AI187" s="5" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="AG187" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="AH187" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="AI187" s="5" t="n">
+        <v>20</v>
+      </c>
       <c r="AJ187" s="5" t="inlineStr"/>
       <c r="AK187" s="5" t="inlineStr"/>
       <c r="AL187" s="5" t="inlineStr"/>
@@ -26621,37 +26709,39 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ha11_2.35</t>
+          <t>ha11_Kin2</t>
         </is>
       </c>
       <c r="E188" s="2" t="n">
-        <v>2.35</v>
+        <v>1.941</v>
       </c>
       <c r="F188" s="2" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="G188" s="2" t="n">
-        <v>-0.3079</v>
+        <v>-0.2879</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>0.1717939524758059</v>
+        <v>0.17</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>0.1361060475241941</v>
+        <v>0.1179</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="K188" s="3" t="inlineStr"/>
       <c r="L188" s="3" t="inlineStr"/>
       <c r="M188" s="3" t="n">
-        <v>2.35</v>
+        <v>1.941</v>
       </c>
       <c r="N188" s="4" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O188" s="3" t="inlineStr"/>
-      <c r="P188" s="2" t="inlineStr"/>
+      <c r="P188" s="2" t="n">
+        <v>0.769</v>
+      </c>
       <c r="Q188" t="inlineStr"/>
       <c r="R188" t="n">
         <v>5.752</v>
@@ -26670,39 +26760,45 @@
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>PRC 83 025201 (2011)</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X188" s="5" t="n">
-        <v>418</v>
+        <v>645</v>
       </c>
       <c r="Y188" s="5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Z188" s="5" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AA188" s="5" t="n">
-        <v>-75</v>
+        <v>-103</v>
       </c>
       <c r="AB188" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC188" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD188" s="5" t="n">
+        <v>-319</v>
+      </c>
+      <c r="AE188" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF188" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG188" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AH188" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="AI188" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AC188" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD188" s="5" t="n">
-        <v>-124</v>
-      </c>
-      <c r="AE188" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF188" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG188" s="5" t="inlineStr"/>
-      <c r="AH188" s="5" t="inlineStr"/>
-      <c r="AI188" s="5" t="inlineStr"/>
       <c r="AJ188" s="5" t="inlineStr"/>
       <c r="AK188" s="5" t="inlineStr"/>
       <c r="AL188" s="5" t="inlineStr"/>
@@ -26731,37 +26827,39 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ha11_2.35</t>
+          <t>ha11_Kin2</t>
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>2.35</v>
+        <v>1.941</v>
       </c>
       <c r="F189" s="2" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="G189" s="2" t="n">
-        <v>-0.3479</v>
+        <v>-0.3276</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>0.1717939524758059</v>
+        <v>0.17</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>0.1761060475241941</v>
+        <v>0.1576</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="K189" s="3" t="inlineStr"/>
       <c r="L189" s="3" t="inlineStr"/>
       <c r="M189" s="3" t="n">
-        <v>2.35</v>
+        <v>1.941</v>
       </c>
       <c r="N189" s="4" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O189" s="3" t="inlineStr"/>
-      <c r="P189" s="2" t="inlineStr"/>
+      <c r="P189" s="2" t="n">
+        <v>0.769</v>
+      </c>
       <c r="Q189" t="inlineStr"/>
       <c r="R189" t="n">
         <v>5.752</v>
@@ -26780,39 +26878,45 @@
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>PRC 83 025201 (2011)</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X189" s="5" t="n">
-        <v>395</v>
+        <v>636</v>
       </c>
       <c r="Y189" s="5" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="Z189" s="5" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AA189" s="5" t="n">
-        <v>-91</v>
+        <v>-185</v>
       </c>
       <c r="AB189" s="5" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="AC189" s="5" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="AD189" s="5" t="n">
-        <v>-137</v>
+        <v>-352</v>
       </c>
       <c r="AE189" s="5" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="AF189" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG189" s="5" t="inlineStr"/>
-      <c r="AH189" s="5" t="inlineStr"/>
-      <c r="AI189" s="5" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="AG189" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="AH189" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="AI189" s="5" t="n">
+        <v>36</v>
+      </c>
       <c r="AJ189" s="5" t="inlineStr"/>
       <c r="AK189" s="5" t="inlineStr"/>
       <c r="AL189" s="5" t="inlineStr"/>
@@ -26841,37 +26945,39 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ha11_2.35</t>
+          <t>ha11_Kin2</t>
         </is>
       </c>
       <c r="E190" s="2" t="n">
-        <v>2.35</v>
+        <v>1.941</v>
       </c>
       <c r="F190" s="2" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="G190" s="2" t="n">
-        <v>-0.3959</v>
+        <v>-0.375</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>0.1717939524758059</v>
+        <v>0.17</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>0.2241060475241941</v>
+        <v>0.205</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="K190" s="3" t="inlineStr"/>
       <c r="L190" s="3" t="inlineStr"/>
       <c r="M190" s="3" t="n">
-        <v>2.35</v>
+        <v>1.941</v>
       </c>
       <c r="N190" s="4" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O190" s="3" t="inlineStr"/>
-      <c r="P190" s="2" t="inlineStr"/>
+      <c r="P190" s="2" t="n">
+        <v>0.769</v>
+      </c>
       <c r="Q190" t="inlineStr"/>
       <c r="R190" t="n">
         <v>5.752</v>
@@ -26890,39 +26996,45 @@
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>PRC 83 025201 (2011)</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X190" s="5" t="n">
-        <v>384</v>
+        <v>628</v>
       </c>
       <c r="Y190" s="5" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="Z190" s="5" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="AA190" s="5" t="n">
-        <v>-123</v>
+        <v>-189</v>
       </c>
       <c r="AB190" s="5" t="n">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="AC190" s="5" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="AD190" s="5" t="n">
-        <v>-134</v>
+        <v>-343</v>
       </c>
       <c r="AE190" s="5" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="AF190" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG190" s="5" t="inlineStr"/>
-      <c r="AH190" s="5" t="inlineStr"/>
-      <c r="AI190" s="5" t="inlineStr"/>
+        <v>68</v>
+      </c>
+      <c r="AG190" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="AH190" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="AI190" s="5" t="n">
+        <v>80</v>
+      </c>
       <c r="AJ190" s="5" t="inlineStr"/>
       <c r="AK190" s="5" t="inlineStr"/>
       <c r="AL190" s="5" t="inlineStr"/>
@@ -26936,7 +27048,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>HallA_y21</t>
+          <t>HallA_y11</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -26951,46 +27063,42 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ha21_01</t>
+          <t>ha11_KinX3</t>
         </is>
       </c>
       <c r="E191" s="2" t="n">
-        <v>3.11</v>
+        <v>2.155</v>
       </c>
       <c r="F191" s="2" t="n">
-        <v>0.36</v>
+        <v>0.335</v>
       </c>
       <c r="G191" s="2" t="n">
-        <v>-0.1957109105009766</v>
+        <v>-0.1465</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>0.1657109105009766</v>
+        <v>0.137</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>0.03</v>
+        <v>0.0095</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="K191" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L191" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
+        <v>0.335</v>
+      </c>
+      <c r="K191" s="3" t="inlineStr"/>
+      <c r="L191" s="3" t="inlineStr"/>
       <c r="M191" s="3" t="n">
-        <v>3.11</v>
+        <v>2.155</v>
       </c>
       <c r="N191" s="4" t="n">
-        <v>0.36</v>
+        <v>0.335</v>
       </c>
       <c r="O191" s="3" t="inlineStr"/>
       <c r="P191" s="2" t="n">
-        <v>0.61</v>
+        <v>0.648</v>
       </c>
       <c r="Q191" t="inlineStr"/>
       <c r="R191" t="n">
-        <v>7.38</v>
+        <v>5.752</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -27006,44 +27114,44 @@
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>PRL 127 152301 (2021), supplemental table II</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X191" s="5" t="n">
-        <v>195.46</v>
+        <v>439</v>
       </c>
       <c r="Y191" s="5" t="n">
-        <v>3.66</v>
+        <v>19</v>
       </c>
       <c r="Z191" s="5" t="n">
-        <v>11.93</v>
+        <v>14</v>
       </c>
       <c r="AA191" s="5" t="n">
-        <v>7.05</v>
+        <v>20</v>
       </c>
       <c r="AB191" s="5" t="n">
-        <v>3.19</v>
+        <v>46</v>
       </c>
       <c r="AC191" s="5" t="n">
-        <v>0.25</v>
+        <v>38</v>
       </c>
       <c r="AD191" s="5" t="n">
-        <v>-4.66</v>
+        <v>-16</v>
       </c>
       <c r="AE191" s="5" t="n">
-        <v>7.62</v>
+        <v>44</v>
       </c>
       <c r="AF191" s="5" t="n">
-        <v>0.16</v>
+        <v>16</v>
       </c>
       <c r="AG191" s="5" t="n">
-        <v>14.52</v>
+        <v>68</v>
       </c>
       <c r="AH191" s="5" t="n">
-        <v>6.91</v>
+        <v>97</v>
       </c>
       <c r="AI191" s="5" t="n">
-        <v>0.51</v>
+        <v>35</v>
       </c>
       <c r="AJ191" s="5" t="inlineStr"/>
       <c r="AK191" s="5" t="inlineStr"/>
@@ -27058,7 +27166,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>HallA_y21</t>
+          <t>HallA_y11</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -27073,46 +27181,42 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ha21_01</t>
+          <t>ha11_KinX3</t>
         </is>
       </c>
       <c r="E192" s="2" t="n">
-        <v>3.11</v>
+        <v>2.155</v>
       </c>
       <c r="F192" s="2" t="n">
-        <v>0.36</v>
+        <v>0.335</v>
       </c>
       <c r="G192" s="2" t="n">
-        <v>-0.2657109105009766</v>
+        <v>-0.1667</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>0.1657109105009766</v>
+        <v>0.137</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>0.1</v>
+        <v>0.0297</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="K192" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="L192" s="3" t="n">
-        <v>0.13</v>
-      </c>
+        <v>0.335</v>
+      </c>
+      <c r="K192" s="3" t="inlineStr"/>
+      <c r="L192" s="3" t="inlineStr"/>
       <c r="M192" s="3" t="n">
-        <v>3.11</v>
+        <v>2.155</v>
       </c>
       <c r="N192" s="4" t="n">
-        <v>0.36</v>
+        <v>0.335</v>
       </c>
       <c r="O192" s="3" t="inlineStr"/>
       <c r="P192" s="2" t="n">
-        <v>0.61</v>
+        <v>0.648</v>
       </c>
       <c r="Q192" t="inlineStr"/>
       <c r="R192" t="n">
-        <v>7.38</v>
+        <v>5.752</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -27128,44 +27232,44 @@
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>PRL 127 152301 (2021), supplemental table II</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X192" s="5" t="n">
-        <v>217.29</v>
+        <v>437</v>
       </c>
       <c r="Y192" s="5" t="n">
-        <v>4.22</v>
+        <v>22</v>
       </c>
       <c r="Z192" s="5" t="n">
-        <v>13.26</v>
+        <v>14</v>
       </c>
       <c r="AA192" s="5" t="n">
-        <v>-5.97</v>
+        <v>2</v>
       </c>
       <c r="AB192" s="5" t="n">
-        <v>3.81</v>
+        <v>50</v>
       </c>
       <c r="AC192" s="5" t="n">
-        <v>0.21</v>
+        <v>17</v>
       </c>
       <c r="AD192" s="5" t="n">
-        <v>-67.45</v>
+        <v>-44</v>
       </c>
       <c r="AE192" s="5" t="n">
-        <v>9.029999999999999</v>
+        <v>50</v>
       </c>
       <c r="AF192" s="5" t="n">
-        <v>2.36</v>
+        <v>32</v>
       </c>
       <c r="AG192" s="5" t="n">
-        <v>18.91</v>
+        <v>12</v>
       </c>
       <c r="AH192" s="5" t="n">
-        <v>8.050000000000001</v>
+        <v>109</v>
       </c>
       <c r="AI192" s="5" t="n">
-        <v>0.66</v>
+        <v>39</v>
       </c>
       <c r="AJ192" s="5" t="inlineStr"/>
       <c r="AK192" s="5" t="inlineStr"/>
@@ -27180,7 +27284,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>HallA_y21</t>
+          <t>HallA_y11</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -27195,46 +27299,42 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ha21_01</t>
+          <t>ha11_KinX3</t>
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>3.11</v>
+        <v>2.155</v>
       </c>
       <c r="F193" s="2" t="n">
-        <v>0.36</v>
+        <v>0.335</v>
       </c>
       <c r="G193" s="2" t="n">
-        <v>-0.3457109105009766</v>
+        <v>-0.1915</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>0.1657109105009766</v>
+        <v>0.137</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>0.18</v>
+        <v>0.0545</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="K193" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="L193" s="3" t="n">
-        <v>0.22</v>
-      </c>
+        <v>0.335</v>
+      </c>
+      <c r="K193" s="3" t="inlineStr"/>
+      <c r="L193" s="3" t="inlineStr"/>
       <c r="M193" s="3" t="n">
-        <v>3.11</v>
+        <v>2.155</v>
       </c>
       <c r="N193" s="4" t="n">
-        <v>0.36</v>
+        <v>0.335</v>
       </c>
       <c r="O193" s="3" t="inlineStr"/>
       <c r="P193" s="2" t="n">
-        <v>0.61</v>
+        <v>0.648</v>
       </c>
       <c r="Q193" t="inlineStr"/>
       <c r="R193" t="n">
-        <v>7.38</v>
+        <v>5.752</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
@@ -27250,44 +27350,44 @@
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>PRL 127 152301 (2021), supplemental table II</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X193" s="5" t="n">
-        <v>195.76</v>
+        <v>457</v>
       </c>
       <c r="Y193" s="5" t="n">
-        <v>4.15</v>
+        <v>18</v>
       </c>
       <c r="Z193" s="5" t="n">
-        <v>11.95</v>
+        <v>15</v>
       </c>
       <c r="AA193" s="5" t="n">
-        <v>-11.55</v>
+        <v>-28</v>
       </c>
       <c r="AB193" s="5" t="n">
-        <v>4.01</v>
+        <v>43</v>
       </c>
       <c r="AC193" s="5" t="n">
-        <v>0.4</v>
+        <v>15</v>
       </c>
       <c r="AD193" s="5" t="n">
-        <v>-67.67</v>
+        <v>-63</v>
       </c>
       <c r="AE193" s="5" t="n">
-        <v>8.970000000000001</v>
+        <v>42</v>
       </c>
       <c r="AF193" s="5" t="n">
-        <v>2.37</v>
+        <v>15</v>
       </c>
       <c r="AG193" s="5" t="n">
-        <v>27.63</v>
+        <v>236</v>
       </c>
       <c r="AH193" s="5" t="n">
-        <v>7.17</v>
+        <v>88</v>
       </c>
       <c r="AI193" s="5" t="n">
-        <v>0.97</v>
+        <v>19</v>
       </c>
       <c r="AJ193" s="5" t="inlineStr"/>
       <c r="AK193" s="5" t="inlineStr"/>
@@ -27302,7 +27402,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>HallA_y21</t>
+          <t>HallA_y11</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -27317,46 +27417,42 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ha21_01</t>
+          <t>ha11_KinX3</t>
         </is>
       </c>
       <c r="E194" s="2" t="n">
-        <v>3.11</v>
+        <v>2.155</v>
       </c>
       <c r="F194" s="2" t="n">
-        <v>0.36</v>
+        <v>0.335</v>
       </c>
       <c r="G194" s="2" t="n">
-        <v>-0.4557109105009766</v>
+        <v>-0.2213</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>0.1657109105009766</v>
+        <v>0.137</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>0.29</v>
+        <v>0.0843</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="K194" s="3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="L194" s="3" t="n">
-        <v>0.38</v>
-      </c>
+        <v>0.335</v>
+      </c>
+      <c r="K194" s="3" t="inlineStr"/>
+      <c r="L194" s="3" t="inlineStr"/>
       <c r="M194" s="3" t="n">
-        <v>3.11</v>
+        <v>2.155</v>
       </c>
       <c r="N194" s="4" t="n">
-        <v>0.36</v>
+        <v>0.335</v>
       </c>
       <c r="O194" s="3" t="inlineStr"/>
       <c r="P194" s="2" t="n">
-        <v>0.61</v>
+        <v>0.648</v>
       </c>
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="n">
-        <v>7.38</v>
+        <v>5.752</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -27372,44 +27468,44 @@
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>PRL 127 152301 (2021), supplemental table II</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X194" s="5" t="n">
-        <v>183.18</v>
+        <v>442</v>
       </c>
       <c r="Y194" s="5" t="n">
-        <v>4.54</v>
+        <v>21</v>
       </c>
       <c r="Z194" s="5" t="n">
-        <v>11.18</v>
+        <v>14</v>
       </c>
       <c r="AA194" s="5" t="n">
-        <v>-28.08</v>
+        <v>-37</v>
       </c>
       <c r="AB194" s="5" t="n">
-        <v>4.63</v>
+        <v>50</v>
       </c>
       <c r="AC194" s="5" t="n">
-        <v>0.98</v>
+        <v>19</v>
       </c>
       <c r="AD194" s="5" t="n">
-        <v>-87.12</v>
+        <v>-114</v>
       </c>
       <c r="AE194" s="5" t="n">
-        <v>10.23</v>
+        <v>47</v>
       </c>
       <c r="AF194" s="5" t="n">
-        <v>3.05</v>
+        <v>8</v>
       </c>
       <c r="AG194" s="5" t="n">
-        <v>9.050000000000001</v>
+        <v>126</v>
       </c>
       <c r="AH194" s="5" t="n">
-        <v>6.38</v>
+        <v>99</v>
       </c>
       <c r="AI194" s="5" t="n">
-        <v>0.32</v>
+        <v>26</v>
       </c>
       <c r="AJ194" s="5" t="inlineStr"/>
       <c r="AK194" s="5" t="inlineStr"/>
@@ -27424,7 +27520,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>HallA_y21</t>
+          <t>HallA_y11</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -27439,46 +27535,42 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ha21_02</t>
+          <t>ha11_KinX3</t>
         </is>
       </c>
       <c r="E195" s="2" t="n">
-        <v>3.57</v>
+        <v>2.155</v>
       </c>
       <c r="F195" s="2" t="n">
-        <v>0.36</v>
+        <v>0.335</v>
       </c>
       <c r="G195" s="2" t="n">
-        <v>-0.1971741479167474</v>
+        <v>-0.2558</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>0.1671741479167475</v>
+        <v>0.137</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>0.03</v>
+        <v>0.1188</v>
       </c>
       <c r="J195" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="K195" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L195" s="3" t="n">
-        <v>0.06</v>
-      </c>
+        <v>0.335</v>
+      </c>
+      <c r="K195" s="3" t="inlineStr"/>
+      <c r="L195" s="3" t="inlineStr"/>
       <c r="M195" s="3" t="n">
-        <v>3.57</v>
+        <v>2.155</v>
       </c>
       <c r="N195" s="4" t="n">
-        <v>0.36</v>
+        <v>0.335</v>
       </c>
       <c r="O195" s="3" t="inlineStr"/>
       <c r="P195" s="2" t="n">
-        <v>0.62</v>
+        <v>0.648</v>
       </c>
       <c r="Q195" t="inlineStr"/>
       <c r="R195" t="n">
-        <v>8.52</v>
+        <v>5.752</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
@@ -27494,44 +27586,44 @@
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>PRL 127 152301 (2021), supplemental table II</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X195" s="5" t="n">
-        <v>115.04</v>
+        <v>466</v>
       </c>
       <c r="Y195" s="5" t="n">
-        <v>2.53</v>
+        <v>22</v>
       </c>
       <c r="Z195" s="5" t="n">
-        <v>4.64</v>
+        <v>15</v>
       </c>
       <c r="AA195" s="5" t="n">
-        <v>-2.37</v>
+        <v>-74</v>
       </c>
       <c r="AB195" s="5" t="n">
-        <v>2.18</v>
+        <v>55</v>
       </c>
       <c r="AC195" s="5" t="n">
-        <v>0.08</v>
+        <v>27</v>
       </c>
       <c r="AD195" s="5" t="n">
-        <v>-16.48</v>
+        <v>-156</v>
       </c>
       <c r="AE195" s="5" t="n">
-        <v>5.25</v>
+        <v>50</v>
       </c>
       <c r="AF195" s="5" t="n">
-        <v>0.58</v>
+        <v>18</v>
       </c>
       <c r="AG195" s="5" t="n">
-        <v>-5.08</v>
+        <v>119</v>
       </c>
       <c r="AH195" s="5" t="n">
-        <v>4.97</v>
+        <v>93</v>
       </c>
       <c r="AI195" s="5" t="n">
-        <v>0.18</v>
+        <v>22</v>
       </c>
       <c r="AJ195" s="5" t="inlineStr"/>
       <c r="AK195" s="5" t="inlineStr"/>
@@ -27546,7 +27638,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>HallA_y21</t>
+          <t>HallA_y11</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -27561,46 +27653,42 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ha21_02</t>
+          <t>ha11_KinX3</t>
         </is>
       </c>
       <c r="E196" s="2" t="n">
-        <v>3.57</v>
+        <v>2.155</v>
       </c>
       <c r="F196" s="2" t="n">
-        <v>0.36</v>
+        <v>0.335</v>
       </c>
       <c r="G196" s="2" t="n">
-        <v>-0.2671741479167474</v>
+        <v>-0.2949000000000001</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>0.1671741479167475</v>
+        <v>0.137</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>0.1</v>
+        <v>0.1579</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="K196" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L196" s="3" t="n">
-        <v>0.13</v>
-      </c>
+        <v>0.335</v>
+      </c>
+      <c r="K196" s="3" t="inlineStr"/>
+      <c r="L196" s="3" t="inlineStr"/>
       <c r="M196" s="3" t="n">
-        <v>3.57</v>
+        <v>2.155</v>
       </c>
       <c r="N196" s="4" t="n">
-        <v>0.36</v>
+        <v>0.335</v>
       </c>
       <c r="O196" s="3" t="inlineStr"/>
       <c r="P196" s="2" t="n">
-        <v>0.62</v>
+        <v>0.648</v>
       </c>
       <c r="Q196" t="inlineStr"/>
       <c r="R196" t="n">
-        <v>8.52</v>
+        <v>5.752</v>
       </c>
       <c r="S196" t="inlineStr">
         <is>
@@ -27616,44 +27704,44 @@
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>PRL 127 152301 (2021), supplemental table II</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X196" s="5" t="n">
-        <v>117.51</v>
+        <v>407</v>
       </c>
       <c r="Y196" s="5" t="n">
-        <v>2.77</v>
+        <v>29</v>
       </c>
       <c r="Z196" s="5" t="n">
-        <v>4.74</v>
+        <v>13</v>
       </c>
       <c r="AA196" s="5" t="n">
-        <v>-9.699999999999999</v>
+        <v>-188</v>
       </c>
       <c r="AB196" s="5" t="n">
-        <v>2.54</v>
+        <v>80</v>
       </c>
       <c r="AC196" s="5" t="n">
-        <v>0.34</v>
+        <v>27</v>
       </c>
       <c r="AD196" s="5" t="n">
-        <v>-46.96</v>
+        <v>-244</v>
       </c>
       <c r="AE196" s="5" t="n">
-        <v>5.85</v>
+        <v>66</v>
       </c>
       <c r="AF196" s="5" t="n">
-        <v>1.64</v>
+        <v>35</v>
       </c>
       <c r="AG196" s="5" t="n">
-        <v>18.11</v>
+        <v>246</v>
       </c>
       <c r="AH196" s="5" t="n">
-        <v>5.31</v>
+        <v>106</v>
       </c>
       <c r="AI196" s="5" t="n">
-        <v>0.63</v>
+        <v>89</v>
       </c>
       <c r="AJ196" s="5" t="inlineStr"/>
       <c r="AK196" s="5" t="inlineStr"/>
@@ -27668,7 +27756,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>HallA_y21</t>
+          <t>HallA_y11</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -27683,46 +27771,42 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ha21_02</t>
+          <t>ha11_KinX3</t>
         </is>
       </c>
       <c r="E197" s="2" t="n">
-        <v>3.57</v>
+        <v>2.155</v>
       </c>
       <c r="F197" s="2" t="n">
-        <v>0.36</v>
+        <v>0.335</v>
       </c>
       <c r="G197" s="2" t="n">
-        <v>-0.3371741479167475</v>
+        <v>-0.3427</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>0.1671741479167475</v>
+        <v>0.137</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>0.17</v>
+        <v>0.2057</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="K197" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="L197" s="3" t="n">
-        <v>0.22</v>
-      </c>
+        <v>0.335</v>
+      </c>
+      <c r="K197" s="3" t="inlineStr"/>
+      <c r="L197" s="3" t="inlineStr"/>
       <c r="M197" s="3" t="n">
-        <v>3.57</v>
+        <v>2.155</v>
       </c>
       <c r="N197" s="4" t="n">
-        <v>0.36</v>
+        <v>0.335</v>
       </c>
       <c r="O197" s="3" t="inlineStr"/>
       <c r="P197" s="2" t="n">
-        <v>0.62</v>
+        <v>0.648</v>
       </c>
       <c r="Q197" t="inlineStr"/>
       <c r="R197" t="n">
-        <v>8.52</v>
+        <v>5.752</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -27738,44 +27822,44 @@
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>PRL 127 152301 (2021), supplemental table II</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X197" s="5" t="n">
-        <v>119.61</v>
+        <v>406</v>
       </c>
       <c r="Y197" s="5" t="n">
-        <v>3.35</v>
+        <v>34</v>
       </c>
       <c r="Z197" s="5" t="n">
-        <v>4.82</v>
+        <v>13</v>
       </c>
       <c r="AA197" s="5" t="n">
-        <v>-5.32</v>
+        <v>-174</v>
       </c>
       <c r="AB197" s="5" t="n">
-        <v>3.52</v>
+        <v>90</v>
       </c>
       <c r="AC197" s="5" t="n">
-        <v>0.19</v>
+        <v>32</v>
       </c>
       <c r="AD197" s="5" t="n">
-        <v>-35.39</v>
+        <v>-124</v>
       </c>
       <c r="AE197" s="5" t="n">
-        <v>6.99</v>
+        <v>69</v>
       </c>
       <c r="AF197" s="5" t="n">
-        <v>1.24</v>
+        <v>42</v>
       </c>
       <c r="AG197" s="5" t="n">
-        <v>14.58</v>
+        <v>177</v>
       </c>
       <c r="AH197" s="5" t="n">
-        <v>5.31</v>
+        <v>104</v>
       </c>
       <c r="AI197" s="5" t="n">
-        <v>0.51</v>
+        <v>30</v>
       </c>
       <c r="AJ197" s="5" t="inlineStr"/>
       <c r="AK197" s="5" t="inlineStr"/>
@@ -27790,7 +27874,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>HallA_y21</t>
+          <t>HallA_y11</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -27805,46 +27889,42 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ha21_02</t>
+          <t>ha11_KinX2</t>
         </is>
       </c>
       <c r="E198" s="2" t="n">
-        <v>3.57</v>
+        <v>2.073</v>
       </c>
       <c r="F198" s="2" t="n">
-        <v>0.36</v>
+        <v>0.394</v>
       </c>
       <c r="G198" s="2" t="n">
-        <v>-0.4471741479167475</v>
+        <v>-0.2084</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>0.1671741479167475</v>
+        <v>0.199</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>0.28</v>
+        <v>0.0094</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="K198" s="3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="L198" s="3" t="n">
-        <v>0.35</v>
-      </c>
+        <v>0.394</v>
+      </c>
+      <c r="K198" s="3" t="inlineStr"/>
+      <c r="L198" s="3" t="inlineStr"/>
       <c r="M198" s="3" t="n">
-        <v>3.57</v>
+        <v>2.073</v>
       </c>
       <c r="N198" s="4" t="n">
-        <v>0.36</v>
+        <v>0.394</v>
       </c>
       <c r="O198" s="3" t="inlineStr"/>
       <c r="P198" s="2" t="n">
-        <v>0.62</v>
+        <v>0.768</v>
       </c>
       <c r="Q198" t="inlineStr"/>
       <c r="R198" t="n">
-        <v>8.52</v>
+        <v>5.752</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -27860,44 +27940,44 @@
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>PRL 127 152301 (2021), supplemental table II</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X198" s="5" t="n">
-        <v>105.37</v>
+        <v>635</v>
       </c>
       <c r="Y198" s="5" t="n">
-        <v>4.06</v>
+        <v>17</v>
       </c>
       <c r="Z198" s="5" t="n">
-        <v>4.25</v>
+        <v>26</v>
       </c>
       <c r="AA198" s="5" t="n">
-        <v>-15.08</v>
+        <v>-26</v>
       </c>
       <c r="AB198" s="5" t="n">
-        <v>4.61</v>
+        <v>30</v>
       </c>
       <c r="AC198" s="5" t="n">
-        <v>0.53</v>
+        <v>22</v>
       </c>
       <c r="AD198" s="5" t="n">
-        <v>-56.36</v>
+        <v>-63</v>
       </c>
       <c r="AE198" s="5" t="n">
-        <v>8.24</v>
+        <v>33</v>
       </c>
       <c r="AF198" s="5" t="n">
-        <v>1.97</v>
+        <v>18</v>
       </c>
       <c r="AG198" s="5" t="n">
-        <v>10.04</v>
+        <v>-23</v>
       </c>
       <c r="AH198" s="5" t="n">
-        <v>4.88</v>
+        <v>84</v>
       </c>
       <c r="AI198" s="5" t="n">
-        <v>0.35</v>
+        <v>138</v>
       </c>
       <c r="AJ198" s="5" t="inlineStr"/>
       <c r="AK198" s="5" t="inlineStr"/>
@@ -27912,7 +27992,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>HallA_y21</t>
+          <t>HallA_y11</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -27927,46 +28007,42 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ha21_04</t>
+          <t>ha11_KinX2</t>
         </is>
       </c>
       <c r="E199" s="2" t="n">
-        <v>4.44</v>
+        <v>2.073</v>
       </c>
       <c r="F199" s="2" t="n">
-        <v>0.36</v>
+        <v>0.394</v>
       </c>
       <c r="G199" s="2" t="n">
-        <v>-0.199178052209217</v>
+        <v>-0.2286</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>0.169178052209217</v>
+        <v>0.199</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>0.03</v>
+        <v>0.0296</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="K199" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L199" s="3" t="n">
-        <v>0.06</v>
-      </c>
+        <v>0.394</v>
+      </c>
+      <c r="K199" s="3" t="inlineStr"/>
+      <c r="L199" s="3" t="inlineStr"/>
       <c r="M199" s="3" t="n">
-        <v>4.44</v>
+        <v>2.073</v>
       </c>
       <c r="N199" s="4" t="n">
-        <v>0.36</v>
+        <v>0.394</v>
       </c>
       <c r="O199" s="3" t="inlineStr"/>
       <c r="P199" s="2" t="n">
-        <v>0.63</v>
+        <v>0.768</v>
       </c>
       <c r="Q199" t="inlineStr"/>
       <c r="R199" t="n">
-        <v>10.59</v>
+        <v>5.752</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -27982,44 +28058,44 @@
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>PRL 127 152301 (2021), supplemental table II</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X199" s="5" t="n">
-        <v>57.04</v>
+        <v>703</v>
       </c>
       <c r="Y199" s="5" t="n">
-        <v>1.88</v>
+        <v>21</v>
       </c>
       <c r="Z199" s="5" t="n">
-        <v>2.08</v>
+        <v>29</v>
       </c>
       <c r="AA199" s="5" t="n">
-        <v>-1.84</v>
+        <v>-100</v>
       </c>
       <c r="AB199" s="5" t="n">
-        <v>1.44</v>
+        <v>37</v>
       </c>
       <c r="AC199" s="5" t="n">
-        <v>0.06</v>
+        <v>61</v>
       </c>
       <c r="AD199" s="5" t="n">
-        <v>-2.42</v>
+        <v>-83</v>
       </c>
       <c r="AE199" s="5" t="n">
-        <v>3.43</v>
+        <v>41</v>
       </c>
       <c r="AF199" s="5" t="n">
-        <v>0.08</v>
+        <v>22</v>
       </c>
       <c r="AG199" s="5" t="n">
-        <v>4.92</v>
+        <v>112</v>
       </c>
       <c r="AH199" s="5" t="n">
-        <v>3.24</v>
+        <v>100</v>
       </c>
       <c r="AI199" s="5" t="n">
-        <v>0.17</v>
+        <v>104</v>
       </c>
       <c r="AJ199" s="5" t="inlineStr"/>
       <c r="AK199" s="5" t="inlineStr"/>
@@ -28034,7 +28110,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>HallA_y21</t>
+          <t>HallA_y11</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -28049,46 +28125,42 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ha21_04</t>
+          <t>ha11_KinX2</t>
         </is>
       </c>
       <c r="E200" s="2" t="n">
-        <v>4.44</v>
+        <v>2.073</v>
       </c>
       <c r="F200" s="2" t="n">
-        <v>0.36</v>
+        <v>0.394</v>
       </c>
       <c r="G200" s="2" t="n">
-        <v>-0.259178052209217</v>
+        <v>-0.2532</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>0.169178052209217</v>
+        <v>0.199</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>0.09</v>
+        <v>0.0542</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="K200" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L200" s="3" t="n">
-        <v>0.13</v>
-      </c>
+        <v>0.394</v>
+      </c>
+      <c r="K200" s="3" t="inlineStr"/>
+      <c r="L200" s="3" t="inlineStr"/>
       <c r="M200" s="3" t="n">
-        <v>4.44</v>
+        <v>2.073</v>
       </c>
       <c r="N200" s="4" t="n">
-        <v>0.36</v>
+        <v>0.394</v>
       </c>
       <c r="O200" s="3" t="inlineStr"/>
       <c r="P200" s="2" t="n">
-        <v>0.63</v>
+        <v>0.768</v>
       </c>
       <c r="Q200" t="inlineStr"/>
       <c r="R200" t="n">
-        <v>10.59</v>
+        <v>5.752</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
@@ -28104,44 +28176,44 @@
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>PRL 127 152301 (2021), supplemental table II</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X200" s="5" t="n">
-        <v>62.86</v>
+        <v>683</v>
       </c>
       <c r="Y200" s="5" t="n">
-        <v>2.16</v>
+        <v>19</v>
       </c>
       <c r="Z200" s="5" t="n">
-        <v>2.29</v>
+        <v>28</v>
       </c>
       <c r="AA200" s="5" t="n">
-        <v>-0.23</v>
+        <v>-88</v>
       </c>
       <c r="AB200" s="5" t="n">
-        <v>1.83</v>
+        <v>32</v>
       </c>
       <c r="AC200" s="5" t="n">
-        <v>0.01</v>
+        <v>54</v>
       </c>
       <c r="AD200" s="5" t="n">
-        <v>-13.17</v>
+        <v>-153</v>
       </c>
       <c r="AE200" s="5" t="n">
-        <v>4.03</v>
+        <v>36</v>
       </c>
       <c r="AF200" s="5" t="n">
-        <v>0.46</v>
+        <v>24</v>
       </c>
       <c r="AG200" s="5" t="n">
-        <v>5.04</v>
+        <v>50</v>
       </c>
       <c r="AH200" s="5" t="n">
-        <v>3.63</v>
+        <v>90</v>
       </c>
       <c r="AI200" s="5" t="n">
-        <v>0.18</v>
+        <v>63</v>
       </c>
       <c r="AJ200" s="5" t="inlineStr"/>
       <c r="AK200" s="5" t="inlineStr"/>
@@ -28156,7 +28228,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>HallA_y21</t>
+          <t>HallA_y11</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -28171,46 +28243,42 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ha21_04</t>
+          <t>ha11_KinX2</t>
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>4.44</v>
+        <v>2.073</v>
       </c>
       <c r="F201" s="2" t="n">
-        <v>0.36</v>
+        <v>0.394</v>
       </c>
       <c r="G201" s="2" t="n">
-        <v>-0.339178052209217</v>
+        <v>-0.283</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>0.169178052209217</v>
+        <v>0.199</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>0.17</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="K201" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="L201" s="3" t="n">
-        <v>0.21</v>
-      </c>
+        <v>0.394</v>
+      </c>
+      <c r="K201" s="3" t="inlineStr"/>
+      <c r="L201" s="3" t="inlineStr"/>
       <c r="M201" s="3" t="n">
-        <v>4.44</v>
+        <v>2.073</v>
       </c>
       <c r="N201" s="4" t="n">
-        <v>0.36</v>
+        <v>0.394</v>
       </c>
       <c r="O201" s="3" t="inlineStr"/>
       <c r="P201" s="2" t="n">
-        <v>0.63</v>
+        <v>0.768</v>
       </c>
       <c r="Q201" t="inlineStr"/>
       <c r="R201" t="n">
-        <v>10.59</v>
+        <v>5.752</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -28226,44 +28294,44 @@
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>PRL 127 152301 (2021), supplemental table II</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X201" s="5" t="n">
-        <v>64.53</v>
+        <v>688</v>
       </c>
       <c r="Y201" s="5" t="n">
-        <v>2.47</v>
+        <v>23</v>
       </c>
       <c r="Z201" s="5" t="n">
-        <v>2.35</v>
+        <v>29</v>
       </c>
       <c r="AA201" s="5" t="n">
-        <v>0.62</v>
+        <v>-68</v>
       </c>
       <c r="AB201" s="5" t="n">
-        <v>2.35</v>
+        <v>38</v>
       </c>
       <c r="AC201" s="5" t="n">
-        <v>0.02</v>
+        <v>487</v>
       </c>
       <c r="AD201" s="5" t="n">
-        <v>-13.49</v>
+        <v>-186</v>
       </c>
       <c r="AE201" s="5" t="n">
-        <v>4.66</v>
+        <v>43</v>
       </c>
       <c r="AF201" s="5" t="n">
-        <v>0.47</v>
+        <v>78</v>
       </c>
       <c r="AG201" s="5" t="n">
-        <v>6.39</v>
+        <v>211</v>
       </c>
       <c r="AH201" s="5" t="n">
-        <v>3.65</v>
+        <v>104</v>
       </c>
       <c r="AI201" s="5" t="n">
-        <v>0.22</v>
+        <v>95</v>
       </c>
       <c r="AJ201" s="5" t="inlineStr"/>
       <c r="AK201" s="5" t="inlineStr"/>
@@ -28278,7 +28346,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HallA_y21</t>
+          <t>HallA_y11</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -28293,46 +28361,42 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ha21_04</t>
+          <t>ha11_KinX2</t>
         </is>
       </c>
       <c r="E202" s="2" t="n">
-        <v>4.44</v>
+        <v>2.073</v>
       </c>
       <c r="F202" s="2" t="n">
-        <v>0.36</v>
+        <v>0.394</v>
       </c>
       <c r="G202" s="2" t="n">
-        <v>-0.449178052209217</v>
+        <v>-0.3171</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>0.169178052209217</v>
+        <v>0.199</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>0.28</v>
+        <v>0.1181</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="K202" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="L202" s="3" t="n">
-        <v>0.38</v>
-      </c>
+        <v>0.394</v>
+      </c>
+      <c r="K202" s="3" t="inlineStr"/>
+      <c r="L202" s="3" t="inlineStr"/>
       <c r="M202" s="3" t="n">
-        <v>4.44</v>
+        <v>2.073</v>
       </c>
       <c r="N202" s="4" t="n">
-        <v>0.36</v>
+        <v>0.394</v>
       </c>
       <c r="O202" s="3" t="inlineStr"/>
       <c r="P202" s="2" t="n">
-        <v>0.63</v>
+        <v>0.768</v>
       </c>
       <c r="Q202" t="inlineStr"/>
       <c r="R202" t="n">
-        <v>10.59</v>
+        <v>5.752</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -28348,44 +28412,44 @@
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>PRL 127 152301 (2021), supplemental table II</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X202" s="5" t="n">
-        <v>51.63</v>
+        <v>682</v>
       </c>
       <c r="Y202" s="5" t="n">
-        <v>2.56</v>
+        <v>23</v>
       </c>
       <c r="Z202" s="5" t="n">
-        <v>1.88</v>
+        <v>28</v>
       </c>
       <c r="AA202" s="5" t="n">
-        <v>-5.66</v>
+        <v>-170</v>
       </c>
       <c r="AB202" s="5" t="n">
-        <v>2.61</v>
+        <v>40</v>
       </c>
       <c r="AC202" s="5" t="n">
-        <v>0.2</v>
+        <v>562</v>
       </c>
       <c r="AD202" s="5" t="n">
-        <v>-28.8</v>
+        <v>-327</v>
       </c>
       <c r="AE202" s="5" t="n">
-        <v>4.76</v>
+        <v>44</v>
       </c>
       <c r="AF202" s="5" t="n">
-        <v>1.01</v>
+        <v>109</v>
       </c>
       <c r="AG202" s="5" t="n">
-        <v>5.79</v>
+        <v>3</v>
       </c>
       <c r="AH202" s="5" t="n">
-        <v>3.13</v>
+        <v>106</v>
       </c>
       <c r="AI202" s="5" t="n">
-        <v>0.2</v>
+        <v>111</v>
       </c>
       <c r="AJ202" s="5" t="inlineStr"/>
       <c r="AK202" s="5" t="inlineStr"/>
@@ -28400,7 +28464,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>HallA_y21</t>
+          <t>HallA_y11</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -28415,46 +28479,42 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>ha21_00</t>
+          <t>ha11_KinX2</t>
         </is>
       </c>
       <c r="E203" s="2" t="n">
-        <v>2.67</v>
+        <v>2.073</v>
       </c>
       <c r="F203" s="2" t="n">
-        <v>0.48</v>
+        <v>0.394</v>
       </c>
       <c r="G203" s="2" t="n">
-        <v>-0.3375729731997212</v>
+        <v>-0.3569</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>0.3275729731997212</v>
+        <v>0.199</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>0.01</v>
+        <v>0.1579</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="K203" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L203" s="3" t="n">
-        <v>0.03</v>
-      </c>
+        <v>0.394</v>
+      </c>
+      <c r="K203" s="3" t="inlineStr"/>
+      <c r="L203" s="3" t="inlineStr"/>
       <c r="M203" s="3" t="n">
-        <v>2.67</v>
+        <v>2.073</v>
       </c>
       <c r="N203" s="4" t="n">
-        <v>0.48</v>
+        <v>0.394</v>
       </c>
       <c r="O203" s="3" t="inlineStr"/>
       <c r="P203" s="2" t="n">
-        <v>0.51</v>
+        <v>0.768</v>
       </c>
       <c r="Q203" t="inlineStr"/>
       <c r="R203" t="n">
-        <v>4.49</v>
+        <v>5.752</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
@@ -28470,44 +28530,44 @@
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>PRL 127 152301 (2021), supplemental table II</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X203" s="5" t="n">
-        <v>525.95</v>
+        <v>662</v>
       </c>
       <c r="Y203" s="5" t="n">
-        <v>14.48</v>
+        <v>34</v>
       </c>
       <c r="Z203" s="5" t="n">
-        <v>41.16</v>
+        <v>28</v>
       </c>
       <c r="AA203" s="5" t="n">
-        <v>25.07</v>
+        <v>-155</v>
       </c>
       <c r="AB203" s="5" t="n">
-        <v>16.53</v>
+        <v>63</v>
       </c>
       <c r="AC203" s="5" t="n">
-        <v>0.88</v>
+        <v>657</v>
       </c>
       <c r="AD203" s="5" t="n">
-        <v>-29.14</v>
+        <v>-247</v>
       </c>
       <c r="AE203" s="5" t="n">
-        <v>43.88</v>
+        <v>65</v>
       </c>
       <c r="AF203" s="5" t="n">
-        <v>1.02</v>
+        <v>141</v>
       </c>
       <c r="AG203" s="5" t="n">
-        <v>7.6</v>
+        <v>78</v>
       </c>
       <c r="AH203" s="5" t="n">
-        <v>30.21</v>
+        <v>136</v>
       </c>
       <c r="AI203" s="5" t="n">
-        <v>0.27</v>
+        <v>126</v>
       </c>
       <c r="AJ203" s="5" t="inlineStr"/>
       <c r="AK203" s="5" t="inlineStr"/>
@@ -28522,7 +28582,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>HallA_y21</t>
+          <t>HallA_y11</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -28537,46 +28597,42 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ha21_00</t>
+          <t>ha11_KinX2</t>
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>2.67</v>
+        <v>2.073</v>
       </c>
       <c r="F204" s="2" t="n">
-        <v>0.48</v>
+        <v>0.394</v>
       </c>
       <c r="G204" s="2" t="n">
-        <v>-0.3675729731997212</v>
+        <v>-0.4041</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>0.3275729731997212</v>
+        <v>0.199</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>0.04</v>
+        <v>0.2051</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="K204" s="3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L204" s="3" t="n">
-        <v>0.06</v>
-      </c>
+        <v>0.394</v>
+      </c>
+      <c r="K204" s="3" t="inlineStr"/>
+      <c r="L204" s="3" t="inlineStr"/>
       <c r="M204" s="3" t="n">
-        <v>2.67</v>
+        <v>2.073</v>
       </c>
       <c r="N204" s="4" t="n">
-        <v>0.48</v>
+        <v>0.394</v>
       </c>
       <c r="O204" s="3" t="inlineStr"/>
       <c r="P204" s="2" t="n">
-        <v>0.51</v>
+        <v>0.768</v>
       </c>
       <c r="Q204" t="inlineStr"/>
       <c r="R204" t="n">
-        <v>4.49</v>
+        <v>5.752</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
@@ -28592,44 +28648,44 @@
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>PRL 127 152301 (2021), supplemental table II</t>
+          <t>PRC 83 025201 (2011), tables IV-VII</t>
         </is>
       </c>
       <c r="X204" s="5" t="n">
-        <v>520.4</v>
+        <v>591</v>
       </c>
       <c r="Y204" s="5" t="n">
-        <v>16.36</v>
+        <v>44</v>
       </c>
       <c r="Z204" s="5" t="n">
-        <v>40.73</v>
+        <v>25</v>
       </c>
       <c r="AA204" s="5" t="n">
-        <v>-38.25</v>
+        <v>-228</v>
       </c>
       <c r="AB204" s="5" t="n">
-        <v>19.21</v>
+        <v>82</v>
       </c>
       <c r="AC204" s="5" t="n">
-        <v>1.34</v>
+        <v>738</v>
       </c>
       <c r="AD204" s="5" t="n">
-        <v>-7.88</v>
+        <v>-444</v>
       </c>
       <c r="AE204" s="5" t="n">
-        <v>45.79</v>
+        <v>82</v>
       </c>
       <c r="AF204" s="5" t="n">
-        <v>0.28</v>
+        <v>183</v>
       </c>
       <c r="AG204" s="5" t="n">
-        <v>-5.32</v>
+        <v>62</v>
       </c>
       <c r="AH204" s="5" t="n">
-        <v>31.83</v>
+        <v>146</v>
       </c>
       <c r="AI204" s="5" t="n">
-        <v>0.19</v>
+        <v>146</v>
       </c>
       <c r="AJ204" s="5" t="inlineStr"/>
       <c r="AK204" s="5" t="inlineStr"/>
@@ -28659,46 +28715,46 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>ha21_00</t>
+          <t>ha21_01</t>
         </is>
       </c>
       <c r="E205" s="2" t="n">
-        <v>2.67</v>
+        <v>3.11</v>
       </c>
       <c r="F205" s="2" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="G205" s="2" t="n">
-        <v>-0.4075729731997212</v>
+        <v>-0.1957109105009766</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>0.3275729731997212</v>
+        <v>0.1657109105009766</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="K205" s="3" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="L205" s="3" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>2.67</v>
+        <v>3.11</v>
       </c>
       <c r="N205" s="4" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="O205" s="3" t="inlineStr"/>
       <c r="P205" s="2" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="Q205" t="inlineStr"/>
       <c r="R205" t="n">
-        <v>4.49</v>
+        <v>7.38</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
@@ -28718,40 +28774,40 @@
         </is>
       </c>
       <c r="X205" s="5" t="n">
-        <v>488.33</v>
+        <v>195.46</v>
       </c>
       <c r="Y205" s="5" t="n">
-        <v>17.33</v>
+        <v>3.66</v>
       </c>
       <c r="Z205" s="5" t="n">
-        <v>38.22</v>
+        <v>11.93</v>
       </c>
       <c r="AA205" s="5" t="n">
-        <v>-31.6</v>
+        <v>7.05</v>
       </c>
       <c r="AB205" s="5" t="n">
-        <v>21.71</v>
+        <v>3.19</v>
       </c>
       <c r="AC205" s="5" t="n">
-        <v>1.11</v>
+        <v>0.25</v>
       </c>
       <c r="AD205" s="5" t="n">
-        <v>-55.44</v>
+        <v>-4.66</v>
       </c>
       <c r="AE205" s="5" t="n">
-        <v>47.02</v>
+        <v>7.62</v>
       </c>
       <c r="AF205" s="5" t="n">
-        <v>1.94</v>
+        <v>0.16</v>
       </c>
       <c r="AG205" s="5" t="n">
-        <v>16.7</v>
+        <v>14.52</v>
       </c>
       <c r="AH205" s="5" t="n">
-        <v>28.69</v>
+        <v>6.91</v>
       </c>
       <c r="AI205" s="5" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="AJ205" s="5" t="inlineStr"/>
       <c r="AK205" s="5" t="inlineStr"/>
@@ -28781,46 +28837,46 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ha21_00</t>
+          <t>ha21_01</t>
         </is>
       </c>
       <c r="E206" s="2" t="n">
-        <v>2.67</v>
+        <v>3.11</v>
       </c>
       <c r="F206" s="2" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="G206" s="2" t="n">
-        <v>-0.4675729731997212</v>
+        <v>-0.2657109105009766</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>0.3275729731997212</v>
+        <v>0.1657109105009766</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="K206" s="3" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L206" s="3" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="M206" s="3" t="n">
-        <v>2.67</v>
+        <v>3.11</v>
       </c>
       <c r="N206" s="4" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="O206" s="3" t="inlineStr"/>
       <c r="P206" s="2" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="Q206" t="inlineStr"/>
       <c r="R206" t="n">
-        <v>4.49</v>
+        <v>7.38</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -28840,40 +28896,40 @@
         </is>
       </c>
       <c r="X206" s="5" t="n">
-        <v>480.77</v>
+        <v>217.29</v>
       </c>
       <c r="Y206" s="5" t="n">
-        <v>23.45</v>
+        <v>4.22</v>
       </c>
       <c r="Z206" s="5" t="n">
-        <v>37.63</v>
+        <v>13.26</v>
       </c>
       <c r="AA206" s="5" t="n">
-        <v>-60.2</v>
+        <v>-5.97</v>
       </c>
       <c r="AB206" s="5" t="n">
-        <v>30.66</v>
+        <v>3.81</v>
       </c>
       <c r="AC206" s="5" t="n">
-        <v>2.11</v>
+        <v>0.21</v>
       </c>
       <c r="AD206" s="5" t="n">
-        <v>-116.12</v>
+        <v>-67.45</v>
       </c>
       <c r="AE206" s="5" t="n">
-        <v>57.67</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="AF206" s="5" t="n">
-        <v>4.06</v>
+        <v>2.36</v>
       </c>
       <c r="AG206" s="5" t="n">
-        <v>14.05</v>
+        <v>18.91</v>
       </c>
       <c r="AH206" s="5" t="n">
-        <v>27.05</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AI206" s="5" t="n">
-        <v>0.49</v>
+        <v>0.66</v>
       </c>
       <c r="AJ206" s="5" t="inlineStr"/>
       <c r="AK206" s="5" t="inlineStr"/>
@@ -28903,46 +28959,46 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>ha21_03</t>
+          <t>ha21_01</t>
         </is>
       </c>
       <c r="E207" s="2" t="n">
-        <v>4.06</v>
+        <v>3.11</v>
       </c>
       <c r="F207" s="2" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="G207" s="2" t="n">
-        <v>-0.3658232235492811</v>
+        <v>-0.3457109105009766</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>0.3458232235492811</v>
+        <v>0.1657109105009766</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="K207" s="3" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="L207" s="3" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="M207" s="3" t="n">
-        <v>4.06</v>
+        <v>3.11</v>
       </c>
       <c r="N207" s="4" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="O207" s="3" t="inlineStr"/>
       <c r="P207" s="2" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="Q207" t="inlineStr"/>
       <c r="R207" t="n">
-        <v>8.85</v>
+        <v>7.38</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
@@ -28962,40 +29018,40 @@
         </is>
       </c>
       <c r="X207" s="5" t="n">
-        <v>126.23</v>
+        <v>195.76</v>
       </c>
       <c r="Y207" s="5" t="n">
-        <v>3.84</v>
+        <v>4.15</v>
       </c>
       <c r="Z207" s="5" t="n">
-        <v>6.71</v>
+        <v>11.95</v>
       </c>
       <c r="AA207" s="5" t="n">
-        <v>-3.93</v>
+        <v>-11.55</v>
       </c>
       <c r="AB207" s="5" t="n">
-        <v>3.36</v>
+        <v>4.01</v>
       </c>
       <c r="AC207" s="5" t="n">
-        <v>0.14</v>
+        <v>0.4</v>
       </c>
       <c r="AD207" s="5" t="n">
-        <v>-17.69</v>
+        <v>-67.67</v>
       </c>
       <c r="AE207" s="5" t="n">
-        <v>7.8</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="AF207" s="5" t="n">
-        <v>0.62</v>
+        <v>2.37</v>
       </c>
       <c r="AG207" s="5" t="n">
-        <v>16.81</v>
+        <v>27.63</v>
       </c>
       <c r="AH207" s="5" t="n">
-        <v>8.43</v>
+        <v>7.17</v>
       </c>
       <c r="AI207" s="5" t="n">
-        <v>0.59</v>
+        <v>0.97</v>
       </c>
       <c r="AJ207" s="5" t="inlineStr"/>
       <c r="AK207" s="5" t="inlineStr"/>
@@ -29025,46 +29081,46 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ha21_03</t>
+          <t>ha21_01</t>
         </is>
       </c>
       <c r="E208" s="2" t="n">
-        <v>4.06</v>
+        <v>3.11</v>
       </c>
       <c r="F208" s="2" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="G208" s="2" t="n">
-        <v>-0.4158232235492811</v>
+        <v>-0.4557109105009766</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>0.3458232235492811</v>
+        <v>0.1657109105009766</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="J208" s="2" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="K208" s="3" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="L208" s="3" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="M208" s="3" t="n">
-        <v>4.06</v>
+        <v>3.11</v>
       </c>
       <c r="N208" s="4" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="O208" s="3" t="inlineStr"/>
       <c r="P208" s="2" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="Q208" t="inlineStr"/>
       <c r="R208" t="n">
-        <v>8.85</v>
+        <v>7.38</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -29084,40 +29140,40 @@
         </is>
       </c>
       <c r="X208" s="5" t="n">
-        <v>128.7</v>
+        <v>183.18</v>
       </c>
       <c r="Y208" s="5" t="n">
-        <v>4.65</v>
+        <v>4.54</v>
       </c>
       <c r="Z208" s="5" t="n">
-        <v>6.84</v>
+        <v>11.18</v>
       </c>
       <c r="AA208" s="5" t="n">
-        <v>-9.18</v>
+        <v>-28.08</v>
       </c>
       <c r="AB208" s="5" t="n">
-        <v>4.45</v>
+        <v>4.63</v>
       </c>
       <c r="AC208" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AD208" s="5" t="n">
+        <v>-87.12</v>
+      </c>
+      <c r="AE208" s="5" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="AF208" s="5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AG208" s="5" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="AH208" s="5" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="AI208" s="5" t="n">
         <v>0.32</v>
-      </c>
-      <c r="AD208" s="5" t="n">
-        <v>-13.9</v>
-      </c>
-      <c r="AE208" s="5" t="n">
-        <v>8.66</v>
-      </c>
-      <c r="AF208" s="5" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="AG208" s="5" t="n">
-        <v>26.38</v>
-      </c>
-      <c r="AH208" s="5" t="n">
-        <v>8.65</v>
-      </c>
-      <c r="AI208" s="5" t="n">
-        <v>0.92</v>
       </c>
       <c r="AJ208" s="5" t="inlineStr"/>
       <c r="AK208" s="5" t="inlineStr"/>
@@ -29147,46 +29203,46 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ha21_03</t>
+          <t>ha21_02</t>
         </is>
       </c>
       <c r="E209" s="2" t="n">
-        <v>4.06</v>
+        <v>3.57</v>
       </c>
       <c r="F209" s="2" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="G209" s="2" t="n">
-        <v>-0.4658232235492811</v>
+        <v>-0.1971741479167474</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>0.3458232235492811</v>
+        <v>0.1671741479167475</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="J209" s="2" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="K209" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L209" s="3" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="M209" s="3" t="n">
-        <v>4.06</v>
+        <v>3.57</v>
       </c>
       <c r="N209" s="4" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="O209" s="3" t="inlineStr"/>
       <c r="P209" s="2" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="Q209" t="inlineStr"/>
       <c r="R209" t="n">
-        <v>8.85</v>
+        <v>8.52</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -29206,40 +29262,40 @@
         </is>
       </c>
       <c r="X209" s="5" t="n">
-        <v>115.22</v>
+        <v>115.04</v>
       </c>
       <c r="Y209" s="5" t="n">
-        <v>6.01</v>
+        <v>2.53</v>
       </c>
       <c r="Z209" s="5" t="n">
-        <v>6.12</v>
+        <v>4.64</v>
       </c>
       <c r="AA209" s="5" t="n">
-        <v>-16.42</v>
+        <v>-2.37</v>
       </c>
       <c r="AB209" s="5" t="n">
-        <v>6.24</v>
+        <v>2.18</v>
       </c>
       <c r="AC209" s="5" t="n">
-        <v>0.57</v>
+        <v>0.08</v>
       </c>
       <c r="AD209" s="5" t="n">
-        <v>-23.1</v>
+        <v>-16.48</v>
       </c>
       <c r="AE209" s="5" t="n">
-        <v>10.78</v>
+        <v>5.25</v>
       </c>
       <c r="AF209" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="AG209" s="5" t="n">
-        <v>30.12</v>
+        <v>-5.08</v>
       </c>
       <c r="AH209" s="5" t="n">
-        <v>8.41</v>
+        <v>4.97</v>
       </c>
       <c r="AI209" s="5" t="n">
-        <v>1.05</v>
+        <v>0.18</v>
       </c>
       <c r="AJ209" s="5" t="inlineStr"/>
       <c r="AK209" s="5" t="inlineStr"/>
@@ -29269,46 +29325,46 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ha21_03</t>
+          <t>ha21_02</t>
         </is>
       </c>
       <c r="E210" s="2" t="n">
-        <v>4.06</v>
+        <v>3.57</v>
       </c>
       <c r="F210" s="2" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="G210" s="2" t="n">
-        <v>-0.535823223549281</v>
+        <v>-0.2671741479167474</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>0.3458232235492811</v>
+        <v>0.1671741479167475</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="J210" s="2" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="K210" s="3" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="L210" s="3" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="M210" s="3" t="n">
-        <v>4.06</v>
+        <v>3.57</v>
       </c>
       <c r="N210" s="4" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="O210" s="3" t="inlineStr"/>
       <c r="P210" s="2" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="Q210" t="inlineStr"/>
       <c r="R210" t="n">
-        <v>8.85</v>
+        <v>8.52</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
@@ -29328,40 +29384,40 @@
         </is>
       </c>
       <c r="X210" s="5" t="n">
-        <v>111.89</v>
+        <v>117.51</v>
       </c>
       <c r="Y210" s="5" t="n">
-        <v>8.460000000000001</v>
+        <v>2.77</v>
       </c>
       <c r="Z210" s="5" t="n">
-        <v>5.95</v>
+        <v>4.74</v>
       </c>
       <c r="AA210" s="5" t="n">
-        <v>-18.01</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="AB210" s="5" t="n">
-        <v>8.970000000000001</v>
+        <v>2.54</v>
       </c>
       <c r="AC210" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AD210" s="5" t="n">
+        <v>-46.96</v>
+      </c>
+      <c r="AE210" s="5" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AF210" s="5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG210" s="5" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="AH210" s="5" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="AI210" s="5" t="n">
         <v>0.63</v>
-      </c>
-      <c r="AD210" s="5" t="n">
-        <v>-40.59</v>
-      </c>
-      <c r="AE210" s="5" t="n">
-        <v>13.09</v>
-      </c>
-      <c r="AF210" s="5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG210" s="5" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="AH210" s="5" t="n">
-        <v>8.51</v>
-      </c>
-      <c r="AI210" s="5" t="n">
-        <v>0.27</v>
       </c>
       <c r="AJ210" s="5" t="inlineStr"/>
       <c r="AK210" s="5" t="inlineStr"/>
@@ -29391,46 +29447,46 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ha21_05</t>
+          <t>ha21_02</t>
         </is>
       </c>
       <c r="E211" s="2" t="n">
-        <v>5.16</v>
+        <v>3.57</v>
       </c>
       <c r="F211" s="2" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="G211" s="2" t="n">
-        <v>-0.3841301938334387</v>
+        <v>-0.3371741479167475</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>0.3541301938334387</v>
+        <v>0.1671741479167475</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="K211" s="3" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="L211" s="3" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="M211" s="3" t="n">
-        <v>5.16</v>
+        <v>3.57</v>
       </c>
       <c r="N211" s="4" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="O211" s="3" t="inlineStr"/>
       <c r="P211" s="2" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="Q211" t="inlineStr"/>
       <c r="R211" t="n">
-        <v>8.85</v>
+        <v>8.52</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -29450,40 +29506,40 @@
         </is>
       </c>
       <c r="X211" s="5" t="n">
-        <v>70.45</v>
+        <v>119.61</v>
       </c>
       <c r="Y211" s="5" t="n">
-        <v>2.53</v>
+        <v>3.35</v>
       </c>
       <c r="Z211" s="5" t="n">
-        <v>2.47</v>
+        <v>4.82</v>
       </c>
       <c r="AA211" s="5" t="n">
-        <v>0.04</v>
+        <v>-5.32</v>
       </c>
       <c r="AB211" s="5" t="n">
-        <v>2.23</v>
+        <v>3.52</v>
       </c>
       <c r="AC211" s="5" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AD211" s="5" t="n">
-        <v>-4.31</v>
+        <v>-35.39</v>
       </c>
       <c r="AE211" s="5" t="n">
-        <v>5.55</v>
+        <v>6.99</v>
       </c>
       <c r="AF211" s="5" t="n">
-        <v>0.15</v>
+        <v>1.24</v>
       </c>
       <c r="AG211" s="5" t="n">
-        <v>2.63</v>
+        <v>14.58</v>
       </c>
       <c r="AH211" s="5" t="n">
-        <v>4.28</v>
+        <v>5.31</v>
       </c>
       <c r="AI211" s="5" t="n">
-        <v>0.09</v>
+        <v>0.51</v>
       </c>
       <c r="AJ211" s="5" t="inlineStr"/>
       <c r="AK211" s="5" t="inlineStr"/>
@@ -29513,46 +29569,46 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>ha21_05</t>
+          <t>ha21_02</t>
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>5.16</v>
+        <v>3.57</v>
       </c>
       <c r="F212" s="2" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="G212" s="2" t="n">
-        <v>-0.4341301938334387</v>
+        <v>-0.4471741479167475</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>0.3541301938334387</v>
+        <v>0.1671741479167475</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>0.08</v>
+        <v>0.28</v>
       </c>
       <c r="J212" s="2" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="K212" s="3" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="L212" s="3" t="n">
-        <v>0.11</v>
+        <v>0.35</v>
       </c>
       <c r="M212" s="3" t="n">
-        <v>5.16</v>
+        <v>3.57</v>
       </c>
       <c r="N212" s="4" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="O212" s="3" t="inlineStr"/>
       <c r="P212" s="2" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="Q212" t="inlineStr"/>
       <c r="R212" t="n">
-        <v>8.85</v>
+        <v>8.52</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
@@ -29572,40 +29628,40 @@
         </is>
       </c>
       <c r="X212" s="5" t="n">
-        <v>72.98</v>
+        <v>105.37</v>
       </c>
       <c r="Y212" s="5" t="n">
-        <v>2.78</v>
+        <v>4.06</v>
       </c>
       <c r="Z212" s="5" t="n">
-        <v>2.55</v>
+        <v>4.25</v>
       </c>
       <c r="AA212" s="5" t="n">
-        <v>1.96</v>
+        <v>-15.08</v>
       </c>
       <c r="AB212" s="5" t="n">
-        <v>2.64</v>
+        <v>4.61</v>
       </c>
       <c r="AC212" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AD212" s="5" t="n">
-        <v>-13.84</v>
+        <v>-56.36</v>
       </c>
       <c r="AE212" s="5" t="n">
-        <v>5.89</v>
+        <v>8.24</v>
       </c>
       <c r="AF212" s="5" t="n">
-        <v>0.46</v>
+        <v>1.97</v>
       </c>
       <c r="AG212" s="5" t="n">
-        <v>7.15</v>
+        <v>10.04</v>
       </c>
       <c r="AH212" s="5" t="n">
-        <v>4.4</v>
+        <v>4.88</v>
       </c>
       <c r="AI212" s="5" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="AJ212" s="5" t="inlineStr"/>
       <c r="AK212" s="5" t="inlineStr"/>
@@ -29635,46 +29691,46 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ha21_05</t>
+          <t>ha21_04</t>
         </is>
       </c>
       <c r="E213" s="2" t="n">
-        <v>5.16</v>
+        <v>4.44</v>
       </c>
       <c r="F213" s="2" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="G213" s="2" t="n">
-        <v>-0.4941301938334387</v>
+        <v>-0.199178052209217</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>0.3541301938334387</v>
+        <v>0.169178052209217</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>0.14</v>
+        <v>0.03</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="K213" s="3" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="L213" s="3" t="n">
-        <v>0.19</v>
+        <v>0.06</v>
       </c>
       <c r="M213" s="3" t="n">
-        <v>5.16</v>
+        <v>4.44</v>
       </c>
       <c r="N213" s="4" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="O213" s="3" t="inlineStr"/>
       <c r="P213" s="2" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="Q213" t="inlineStr"/>
       <c r="R213" t="n">
-        <v>8.85</v>
+        <v>10.59</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
@@ -29694,40 +29750,40 @@
         </is>
       </c>
       <c r="X213" s="5" t="n">
-        <v>65.77</v>
+        <v>57.04</v>
       </c>
       <c r="Y213" s="5" t="n">
-        <v>3.17</v>
+        <v>1.88</v>
       </c>
       <c r="Z213" s="5" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AA213" s="5" t="n">
-        <v>-1.82</v>
+        <v>-1.84</v>
       </c>
       <c r="AB213" s="5" t="n">
-        <v>3.51</v>
+        <v>1.44</v>
       </c>
       <c r="AC213" s="5" t="n">
         <v>0.06</v>
       </c>
       <c r="AD213" s="5" t="n">
-        <v>-19.81</v>
+        <v>-2.42</v>
       </c>
       <c r="AE213" s="5" t="n">
-        <v>6.74</v>
+        <v>3.43</v>
       </c>
       <c r="AF213" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="AG213" s="5" t="n">
-        <v>2.16</v>
+        <v>4.92</v>
       </c>
       <c r="AH213" s="5" t="n">
-        <v>4.12</v>
+        <v>3.24</v>
       </c>
       <c r="AI213" s="5" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="AJ213" s="5" t="inlineStr"/>
       <c r="AK213" s="5" t="inlineStr"/>
@@ -29757,46 +29813,46 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>ha21_05</t>
+          <t>ha21_04</t>
         </is>
       </c>
       <c r="E214" s="2" t="n">
-        <v>5.16</v>
+        <v>4.44</v>
       </c>
       <c r="F214" s="2" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="G214" s="2" t="n">
-        <v>-0.6041301938334387</v>
+        <v>-0.259178052209217</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>0.3541301938334387</v>
+        <v>0.169178052209217</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>0.25</v>
+        <v>0.09</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="K214" s="3" t="n">
-        <v>0.19</v>
+        <v>0.06</v>
       </c>
       <c r="L214" s="3" t="n">
-        <v>0.33</v>
+        <v>0.13</v>
       </c>
       <c r="M214" s="3" t="n">
-        <v>5.16</v>
+        <v>4.44</v>
       </c>
       <c r="N214" s="4" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="O214" s="3" t="inlineStr"/>
       <c r="P214" s="2" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="Q214" t="inlineStr"/>
       <c r="R214" t="n">
-        <v>8.85</v>
+        <v>10.59</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -29816,40 +29872,40 @@
         </is>
       </c>
       <c r="X214" s="5" t="n">
-        <v>58.49</v>
+        <v>62.86</v>
       </c>
       <c r="Y214" s="5" t="n">
-        <v>3.74</v>
+        <v>2.16</v>
       </c>
       <c r="Z214" s="5" t="n">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="AA214" s="5" t="n">
-        <v>-4.52</v>
+        <v>-0.23</v>
       </c>
       <c r="AB214" s="5" t="n">
-        <v>4.4</v>
+        <v>1.83</v>
       </c>
       <c r="AC214" s="5" t="n">
-        <v>0.16</v>
+        <v>0.01</v>
       </c>
       <c r="AD214" s="5" t="n">
-        <v>-22.46</v>
+        <v>-13.17</v>
       </c>
       <c r="AE214" s="5" t="n">
-        <v>7.55</v>
+        <v>4.03</v>
       </c>
       <c r="AF214" s="5" t="n">
-        <v>0.79</v>
+        <v>0.46</v>
       </c>
       <c r="AG214" s="5" t="n">
-        <v>6.62</v>
+        <v>5.04</v>
       </c>
       <c r="AH214" s="5" t="n">
-        <v>3.53</v>
+        <v>3.63</v>
       </c>
       <c r="AI214" s="5" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="AJ214" s="5" t="inlineStr"/>
       <c r="AK214" s="5" t="inlineStr"/>
@@ -29879,46 +29935,46 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>ha21_07</t>
+          <t>ha21_04</t>
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>6.56</v>
+        <v>4.44</v>
       </c>
       <c r="F215" s="2" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="G215" s="2" t="n">
-        <v>-0.3810616152049726</v>
+        <v>-0.339178052209217</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>0.3610616152049726</v>
+        <v>0.169178052209217</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>0.02</v>
+        <v>0.17</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="K215" s="3" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="L215" s="3" t="n">
-        <v>0.05</v>
+        <v>0.21</v>
       </c>
       <c r="M215" s="3" t="n">
-        <v>6.56</v>
+        <v>4.44</v>
       </c>
       <c r="N215" s="4" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="O215" s="3" t="inlineStr"/>
       <c r="P215" s="2" t="n">
-        <v>0.52</v>
+        <v>0.63</v>
       </c>
       <c r="Q215" t="inlineStr"/>
       <c r="R215" t="n">
-        <v>10.99</v>
+        <v>10.59</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
@@ -29938,40 +29994,40 @@
         </is>
       </c>
       <c r="X215" s="5" t="n">
-        <v>33.48</v>
+        <v>64.53</v>
       </c>
       <c r="Y215" s="5" t="n">
-        <v>1.6</v>
+        <v>2.47</v>
       </c>
       <c r="Z215" s="5" t="n">
-        <v>1.54</v>
+        <v>2.35</v>
       </c>
       <c r="AA215" s="5" t="n">
-        <v>-0.79</v>
+        <v>0.62</v>
       </c>
       <c r="AB215" s="5" t="n">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="AC215" s="5" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AD215" s="5" t="n">
-        <v>6.43</v>
+        <v>-13.49</v>
       </c>
       <c r="AE215" s="5" t="n">
-        <v>4.08</v>
+        <v>4.66</v>
       </c>
       <c r="AF215" s="5" t="n">
-        <v>0.23</v>
+        <v>0.47</v>
       </c>
       <c r="AG215" s="5" t="n">
-        <v>3.23</v>
+        <v>6.39</v>
       </c>
       <c r="AH215" s="5" t="n">
-        <v>2.96</v>
+        <v>3.65</v>
       </c>
       <c r="AI215" s="5" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="AJ215" s="5" t="inlineStr"/>
       <c r="AK215" s="5" t="inlineStr"/>
@@ -30001,46 +30057,46 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>ha21_07</t>
+          <t>ha21_04</t>
         </is>
       </c>
       <c r="E216" s="2" t="n">
-        <v>6.56</v>
+        <v>4.44</v>
       </c>
       <c r="F216" s="2" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="G216" s="2" t="n">
-        <v>-0.4310616152049726</v>
+        <v>-0.449178052209217</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>0.3610616152049726</v>
+        <v>0.169178052209217</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="K216" s="3" t="n">
-        <v>0.05</v>
+        <v>0.21</v>
       </c>
       <c r="L216" s="3" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="M216" s="3" t="n">
-        <v>6.56</v>
+        <v>4.44</v>
       </c>
       <c r="N216" s="4" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="O216" s="3" t="inlineStr"/>
       <c r="P216" s="2" t="n">
-        <v>0.52</v>
+        <v>0.63</v>
       </c>
       <c r="Q216" t="inlineStr"/>
       <c r="R216" t="n">
-        <v>10.99</v>
+        <v>10.59</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
@@ -30060,40 +30116,40 @@
         </is>
       </c>
       <c r="X216" s="5" t="n">
-        <v>38.21</v>
+        <v>51.63</v>
       </c>
       <c r="Y216" s="5" t="n">
-        <v>2.06</v>
+        <v>2.56</v>
       </c>
       <c r="Z216" s="5" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AA216" s="5" t="n">
-        <v>-0.39</v>
+        <v>-5.66</v>
       </c>
       <c r="AB216" s="5" t="n">
-        <v>2.39</v>
+        <v>2.61</v>
       </c>
       <c r="AC216" s="5" t="n">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
       <c r="AD216" s="5" t="n">
-        <v>2.15</v>
+        <v>-28.8</v>
       </c>
       <c r="AE216" s="5" t="n">
-        <v>5.14</v>
+        <v>4.76</v>
       </c>
       <c r="AF216" s="5" t="n">
-        <v>0.08</v>
+        <v>1.01</v>
       </c>
       <c r="AG216" s="5" t="n">
-        <v>0.98</v>
+        <v>5.79</v>
       </c>
       <c r="AH216" s="5" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="AI216" s="5" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="AJ216" s="5" t="inlineStr"/>
       <c r="AK216" s="5" t="inlineStr"/>
@@ -30123,46 +30179,46 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ha21_07</t>
+          <t>ha21_00</t>
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>6.56</v>
+        <v>2.67</v>
       </c>
       <c r="F217" s="2" t="n">
         <v>0.48</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>-0.4810616152049726</v>
+        <v>-0.3375729731997212</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>0.3610616152049726</v>
+        <v>0.3275729731997212</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="K217" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L217" s="3" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>6.56</v>
+        <v>2.67</v>
       </c>
       <c r="N217" s="4" t="n">
         <v>0.48</v>
       </c>
       <c r="O217" s="3" t="inlineStr"/>
       <c r="P217" s="2" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="Q217" t="inlineStr"/>
       <c r="R217" t="n">
-        <v>10.99</v>
+        <v>4.49</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
@@ -30182,40 +30238,40 @@
         </is>
       </c>
       <c r="X217" s="5" t="n">
-        <v>31.61</v>
+        <v>525.95</v>
       </c>
       <c r="Y217" s="5" t="n">
-        <v>2.35</v>
+        <v>14.48</v>
       </c>
       <c r="Z217" s="5" t="n">
-        <v>1.46</v>
+        <v>41.16</v>
       </c>
       <c r="AA217" s="5" t="n">
-        <v>-4.97</v>
+        <v>25.07</v>
       </c>
       <c r="AB217" s="5" t="n">
-        <v>2.95</v>
+        <v>16.53</v>
       </c>
       <c r="AC217" s="5" t="n">
-        <v>0.17</v>
+        <v>0.88</v>
       </c>
       <c r="AD217" s="5" t="n">
-        <v>-4.24</v>
+        <v>-29.14</v>
       </c>
       <c r="AE217" s="5" t="n">
-        <v>5.56</v>
+        <v>43.88</v>
       </c>
       <c r="AF217" s="5" t="n">
-        <v>0.15</v>
+        <v>1.02</v>
       </c>
       <c r="AG217" s="5" t="n">
-        <v>10.66</v>
+        <v>7.6</v>
       </c>
       <c r="AH217" s="5" t="n">
-        <v>3.11</v>
+        <v>30.21</v>
       </c>
       <c r="AI217" s="5" t="n">
-        <v>0.37</v>
+        <v>0.27</v>
       </c>
       <c r="AJ217" s="5" t="inlineStr"/>
       <c r="AK217" s="5" t="inlineStr"/>
@@ -30245,46 +30301,46 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>ha21_07</t>
+          <t>ha21_00</t>
         </is>
       </c>
       <c r="E218" s="2" t="n">
-        <v>6.56</v>
+        <v>2.67</v>
       </c>
       <c r="F218" s="2" t="n">
         <v>0.48</v>
       </c>
       <c r="G218" s="2" t="n">
-        <v>-0.5410616152049725</v>
+        <v>-0.3675729731997212</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>0.3610616152049726</v>
+        <v>0.3275729731997212</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>0.18</v>
+        <v>0.04</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="K218" s="3" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="L218" s="3" t="n">
-        <v>0.21</v>
+        <v>0.06</v>
       </c>
       <c r="M218" s="3" t="n">
-        <v>6.56</v>
+        <v>2.67</v>
       </c>
       <c r="N218" s="4" t="n">
         <v>0.48</v>
       </c>
       <c r="O218" s="3" t="inlineStr"/>
       <c r="P218" s="2" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="Q218" t="inlineStr"/>
       <c r="R218" t="n">
-        <v>10.99</v>
+        <v>4.49</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -30304,40 +30360,40 @@
         </is>
       </c>
       <c r="X218" s="5" t="n">
-        <v>43.74</v>
+        <v>520.4</v>
       </c>
       <c r="Y218" s="5" t="n">
-        <v>4.23</v>
+        <v>16.36</v>
       </c>
       <c r="Z218" s="5" t="n">
-        <v>2.02</v>
+        <v>40.73</v>
       </c>
       <c r="AA218" s="5" t="n">
-        <v>11.91</v>
+        <v>-38.25</v>
       </c>
       <c r="AB218" s="5" t="n">
-        <v>5.51</v>
+        <v>19.21</v>
       </c>
       <c r="AC218" s="5" t="n">
-        <v>0.42</v>
+        <v>1.34</v>
       </c>
       <c r="AD218" s="5" t="n">
-        <v>-4.12</v>
+        <v>-7.88</v>
       </c>
       <c r="AE218" s="5" t="n">
-        <v>8.539999999999999</v>
+        <v>45.79</v>
       </c>
       <c r="AF218" s="5" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="AG218" s="5" t="n">
-        <v>6.22</v>
+        <v>-5.32</v>
       </c>
       <c r="AH218" s="5" t="n">
-        <v>3.39</v>
+        <v>31.83</v>
       </c>
       <c r="AI218" s="5" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="AJ218" s="5" t="inlineStr"/>
       <c r="AK218" s="5" t="inlineStr"/>
@@ -30367,46 +30423,46 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>ha21_06</t>
+          <t>ha21_00</t>
         </is>
       </c>
       <c r="E219" s="2" t="n">
-        <v>5.49</v>
+        <v>2.67</v>
       </c>
       <c r="F219" s="2" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="G219" s="2" t="n">
-        <v>-0.7291233923215201</v>
+        <v>-0.4075729731997212</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>0.6691233923215201</v>
+        <v>0.3275729731997212</v>
       </c>
       <c r="I219" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J219" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K219" s="3" t="n">
         <v>0.06</v>
       </c>
-      <c r="J219" s="2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="K219" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L219" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M219" s="3" t="n">
-        <v>5.49</v>
+        <v>2.67</v>
       </c>
       <c r="N219" s="4" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="O219" s="3" t="inlineStr"/>
       <c r="P219" s="2" t="n">
-        <v>0.66</v>
+        <v>0.51</v>
       </c>
       <c r="Q219" t="inlineStr"/>
       <c r="R219" t="n">
-        <v>8.52</v>
+        <v>4.49</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -30426,40 +30482,40 @@
         </is>
       </c>
       <c r="X219" s="5" t="n">
-        <v>92.48</v>
+        <v>488.33</v>
       </c>
       <c r="Y219" s="5" t="n">
-        <v>1.42</v>
+        <v>17.33</v>
       </c>
       <c r="Z219" s="5" t="n">
-        <v>4.26</v>
+        <v>38.22</v>
       </c>
       <c r="AA219" s="5" t="n">
-        <v>-2.18</v>
+        <v>-31.6</v>
       </c>
       <c r="AB219" s="5" t="n">
-        <v>0.7</v>
+        <v>21.71</v>
       </c>
       <c r="AC219" s="5" t="n">
-        <v>0.44</v>
+        <v>1.11</v>
       </c>
       <c r="AD219" s="5" t="n">
-        <v>-3.29</v>
+        <v>-55.44</v>
       </c>
       <c r="AE219" s="5" t="n">
-        <v>1.67</v>
+        <v>47.02</v>
       </c>
       <c r="AF219" s="5" t="n">
-        <v>0.12</v>
+        <v>1.94</v>
       </c>
       <c r="AG219" s="5" t="n">
-        <v>6.61</v>
+        <v>16.7</v>
       </c>
       <c r="AH219" s="5" t="n">
-        <v>1.68</v>
+        <v>28.69</v>
       </c>
       <c r="AI219" s="5" t="n">
-        <v>0.23</v>
+        <v>0.5</v>
       </c>
       <c r="AJ219" s="5" t="inlineStr"/>
       <c r="AK219" s="5" t="inlineStr"/>
@@ -30489,46 +30545,46 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>ha21_06</t>
+          <t>ha21_00</t>
         </is>
       </c>
       <c r="E220" s="2" t="n">
-        <v>5.49</v>
+        <v>2.67</v>
       </c>
       <c r="F220" s="2" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="G220" s="2" t="n">
-        <v>-0.84912339232152</v>
+        <v>-0.4675729731997212</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>0.6691233923215201</v>
+        <v>0.3275729731997212</v>
       </c>
       <c r="I220" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J220" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K220" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L220" s="3" t="n">
         <v>0.18</v>
       </c>
-      <c r="J220" s="2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="K220" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="L220" s="3" t="n">
-        <v>0.26</v>
-      </c>
       <c r="M220" s="3" t="n">
-        <v>5.49</v>
+        <v>2.67</v>
       </c>
       <c r="N220" s="4" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="O220" s="3" t="inlineStr"/>
       <c r="P220" s="2" t="n">
-        <v>0.66</v>
+        <v>0.51</v>
       </c>
       <c r="Q220" t="inlineStr"/>
       <c r="R220" t="n">
-        <v>8.52</v>
+        <v>4.49</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
@@ -30548,40 +30604,40 @@
         </is>
       </c>
       <c r="X220" s="5" t="n">
-        <v>86.89</v>
+        <v>480.77</v>
       </c>
       <c r="Y220" s="5" t="n">
-        <v>1.39</v>
+        <v>23.45</v>
       </c>
       <c r="Z220" s="5" t="n">
-        <v>4.01</v>
+        <v>37.63</v>
       </c>
       <c r="AA220" s="5" t="n">
-        <v>-5.12</v>
+        <v>-60.2</v>
       </c>
       <c r="AB220" s="5" t="n">
-        <v>0.75</v>
+        <v>30.66</v>
       </c>
       <c r="AC220" s="5" t="n">
-        <v>1.04</v>
+        <v>2.11</v>
       </c>
       <c r="AD220" s="5" t="n">
-        <v>-4.28</v>
+        <v>-116.12</v>
       </c>
       <c r="AE220" s="5" t="n">
-        <v>1.66</v>
+        <v>57.67</v>
       </c>
       <c r="AF220" s="5" t="n">
-        <v>0.15</v>
+        <v>4.06</v>
       </c>
       <c r="AG220" s="5" t="n">
-        <v>6.47</v>
+        <v>14.05</v>
       </c>
       <c r="AH220" s="5" t="n">
-        <v>1.6</v>
+        <v>27.05</v>
       </c>
       <c r="AI220" s="5" t="n">
-        <v>0.23</v>
+        <v>0.49</v>
       </c>
       <c r="AJ220" s="5" t="inlineStr"/>
       <c r="AK220" s="5" t="inlineStr"/>
@@ -30611,46 +30667,46 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>ha21_06</t>
+          <t>ha21_03</t>
         </is>
       </c>
       <c r="E221" s="2" t="n">
-        <v>5.49</v>
+        <v>4.06</v>
       </c>
       <c r="F221" s="2" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="G221" s="2" t="n">
-        <v>-1.00912339232152</v>
+        <v>-0.3658232235492811</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>0.6691233923215201</v>
+        <v>0.3458232235492811</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>0.34</v>
+        <v>0.02</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>0.59</v>
+        <v>0.45</v>
       </c>
       <c r="K221" s="3" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="L221" s="3" t="n">
-        <v>0.44</v>
+        <v>0.05</v>
       </c>
       <c r="M221" s="3" t="n">
-        <v>5.49</v>
+        <v>4.06</v>
       </c>
       <c r="N221" s="4" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="O221" s="3" t="inlineStr"/>
       <c r="P221" s="2" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="Q221" t="inlineStr"/>
       <c r="R221" t="n">
-        <v>8.52</v>
+        <v>8.85</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -30670,40 +30726,40 @@
         </is>
       </c>
       <c r="X221" s="5" t="n">
-        <v>78.95999999999999</v>
+        <v>126.23</v>
       </c>
       <c r="Y221" s="5" t="n">
-        <v>1.38</v>
+        <v>3.84</v>
       </c>
       <c r="Z221" s="5" t="n">
-        <v>3.64</v>
+        <v>6.71</v>
       </c>
       <c r="AA221" s="5" t="n">
-        <v>-6.44</v>
+        <v>-3.93</v>
       </c>
       <c r="AB221" s="5" t="n">
-        <v>0.86</v>
+        <v>3.36</v>
       </c>
       <c r="AC221" s="5" t="n">
-        <v>1.31</v>
+        <v>0.14</v>
       </c>
       <c r="AD221" s="5" t="n">
-        <v>-17.84</v>
+        <v>-17.69</v>
       </c>
       <c r="AE221" s="5" t="n">
-        <v>1.74</v>
+        <v>7.8</v>
       </c>
       <c r="AF221" s="5" t="n">
         <v>0.62</v>
       </c>
       <c r="AG221" s="5" t="n">
-        <v>5.47</v>
+        <v>16.81</v>
       </c>
       <c r="AH221" s="5" t="n">
-        <v>1.47</v>
+        <v>8.43</v>
       </c>
       <c r="AI221" s="5" t="n">
-        <v>0.19</v>
+        <v>0.59</v>
       </c>
       <c r="AJ221" s="5" t="inlineStr"/>
       <c r="AK221" s="5" t="inlineStr"/>
@@ -30733,46 +30789,46 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>ha21_06</t>
+          <t>ha21_03</t>
         </is>
       </c>
       <c r="E222" s="2" t="n">
-        <v>5.49</v>
+        <v>4.06</v>
       </c>
       <c r="F222" s="2" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="G222" s="2" t="n">
-        <v>-1.27912339232152</v>
+        <v>-0.4158232235492811</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>0.6691233923215201</v>
+        <v>0.3458232235492811</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>0.61</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>0.59</v>
+        <v>0.45</v>
       </c>
       <c r="K222" s="3" t="n">
-        <v>0.44</v>
+        <v>0.05</v>
       </c>
       <c r="L222" s="3" t="n">
-        <v>0.88</v>
+        <v>0.1</v>
       </c>
       <c r="M222" s="3" t="n">
-        <v>5.49</v>
+        <v>4.06</v>
       </c>
       <c r="N222" s="4" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="O222" s="3" t="inlineStr"/>
       <c r="P222" s="2" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="Q222" t="inlineStr"/>
       <c r="R222" t="n">
-        <v>8.52</v>
+        <v>8.85</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
@@ -30792,40 +30848,40 @@
         </is>
       </c>
       <c r="X222" s="5" t="n">
-        <v>63.43</v>
+        <v>128.7</v>
       </c>
       <c r="Y222" s="5" t="n">
-        <v>1.37</v>
+        <v>4.65</v>
       </c>
       <c r="Z222" s="5" t="n">
-        <v>2.92</v>
+        <v>6.84</v>
       </c>
       <c r="AA222" s="5" t="n">
-        <v>-4.87</v>
+        <v>-9.18</v>
       </c>
       <c r="AB222" s="5" t="n">
-        <v>1.03</v>
+        <v>4.45</v>
       </c>
       <c r="AC222" s="5" t="n">
-        <v>0.99</v>
+        <v>0.32</v>
       </c>
       <c r="AD222" s="5" t="n">
-        <v>-13.65</v>
+        <v>-13.9</v>
       </c>
       <c r="AE222" s="5" t="n">
-        <v>1.82</v>
+        <v>8.66</v>
       </c>
       <c r="AF222" s="5" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="AG222" s="5" t="n">
-        <v>6.66</v>
+        <v>26.38</v>
       </c>
       <c r="AH222" s="5" t="n">
-        <v>1.1</v>
+        <v>8.65</v>
       </c>
       <c r="AI222" s="5" t="n">
-        <v>0.23</v>
+        <v>0.92</v>
       </c>
       <c r="AJ222" s="5" t="inlineStr"/>
       <c r="AK222" s="5" t="inlineStr"/>
@@ -30855,46 +30911,46 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>ha21_08</t>
+          <t>ha21_03</t>
         </is>
       </c>
       <c r="E223" s="2" t="n">
-        <v>8.31</v>
+        <v>4.06</v>
       </c>
       <c r="F223" s="2" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="G223" s="2" t="n">
-        <v>-0.7555260302250792</v>
+        <v>-0.4658232235492811</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>0.7055260302250792</v>
+        <v>0.3458232235492811</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="K223" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L223" s="3" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="M223" s="3" t="n">
-        <v>8.31</v>
+        <v>4.06</v>
       </c>
       <c r="N223" s="4" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="O223" s="3" t="inlineStr"/>
       <c r="P223" s="2" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="Q223" t="inlineStr"/>
       <c r="R223" t="n">
-        <v>10.59</v>
+        <v>8.85</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
@@ -30914,40 +30970,40 @@
         </is>
       </c>
       <c r="X223" s="5" t="n">
-        <v>27.29</v>
+        <v>115.22</v>
       </c>
       <c r="Y223" s="5" t="n">
-        <v>0.9</v>
+        <v>6.01</v>
       </c>
       <c r="Z223" s="5" t="n">
-        <v>1.1</v>
+        <v>6.12</v>
       </c>
       <c r="AA223" s="5" t="n">
-        <v>-0.36</v>
+        <v>-16.42</v>
       </c>
       <c r="AB223" s="5" t="n">
-        <v>0.48</v>
+        <v>6.24</v>
       </c>
       <c r="AC223" s="5" t="n">
-        <v>0.01</v>
+        <v>0.57</v>
       </c>
       <c r="AD223" s="5" t="n">
-        <v>-1.72</v>
+        <v>-23.1</v>
       </c>
       <c r="AE223" s="5" t="n">
-        <v>1.25</v>
+        <v>10.78</v>
       </c>
       <c r="AF223" s="5" t="n">
-        <v>0.06</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AG223" s="5" t="n">
-        <v>1.18</v>
+        <v>30.12</v>
       </c>
       <c r="AH223" s="5" t="n">
-        <v>0.9</v>
+        <v>8.41</v>
       </c>
       <c r="AI223" s="5" t="n">
-        <v>0.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ223" s="5" t="inlineStr"/>
       <c r="AK223" s="5" t="inlineStr"/>
@@ -30977,46 +31033,46 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ha21_08</t>
+          <t>ha21_03</t>
         </is>
       </c>
       <c r="E224" s="2" t="n">
-        <v>8.31</v>
+        <v>4.06</v>
       </c>
       <c r="F224" s="2" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="G224" s="2" t="n">
-        <v>-0.8555260302250792</v>
+        <v>-0.535823223549281</v>
       </c>
       <c r="H224" s="2" t="n">
-        <v>0.7055260302250792</v>
+        <v>0.3458232235492811</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="K224" s="3" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="L224" s="3" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="M224" s="3" t="n">
-        <v>8.31</v>
+        <v>4.06</v>
       </c>
       <c r="N224" s="4" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="O224" s="3" t="inlineStr"/>
       <c r="P224" s="2" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="Q224" t="inlineStr"/>
       <c r="R224" t="n">
-        <v>10.59</v>
+        <v>8.85</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -31036,40 +31092,40 @@
         </is>
       </c>
       <c r="X224" s="5" t="n">
-        <v>24.72</v>
+        <v>111.89</v>
       </c>
       <c r="Y224" s="5" t="n">
-        <v>0.86</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="Z224" s="5" t="n">
-        <v>1</v>
+        <v>5.95</v>
       </c>
       <c r="AA224" s="5" t="n">
-        <v>-0.75</v>
+        <v>-18.01</v>
       </c>
       <c r="AB224" s="5" t="n">
-        <v>0.48</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="AC224" s="5" t="n">
-        <v>0.03</v>
+        <v>0.63</v>
       </c>
       <c r="AD224" s="5" t="n">
-        <v>-2.5</v>
+        <v>-40.59</v>
       </c>
       <c r="AE224" s="5" t="n">
-        <v>1.18</v>
+        <v>13.09</v>
       </c>
       <c r="AF224" s="5" t="n">
-        <v>0.09</v>
+        <v>1.42</v>
       </c>
       <c r="AG224" s="5" t="n">
-        <v>1.7</v>
+        <v>7.79</v>
       </c>
       <c r="AH224" s="5" t="n">
-        <v>0.83</v>
+        <v>8.51</v>
       </c>
       <c r="AI224" s="5" t="n">
-        <v>0.06</v>
+        <v>0.27</v>
       </c>
       <c r="AJ224" s="5" t="inlineStr"/>
       <c r="AK224" s="5" t="inlineStr"/>
@@ -31099,46 +31155,46 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>ha21_08</t>
+          <t>ha21_05</t>
         </is>
       </c>
       <c r="E225" s="2" t="n">
-        <v>8.31</v>
+        <v>5.16</v>
       </c>
       <c r="F225" s="2" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="G225" s="2" t="n">
-        <v>-0.9855260302250792</v>
+        <v>-0.3841301938334387</v>
       </c>
       <c r="H225" s="2" t="n">
-        <v>0.7055260302250792</v>
+        <v>0.3541301938334387</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>0.28</v>
+        <v>0.03</v>
       </c>
       <c r="J225" s="2" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="K225" s="3" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="L225" s="3" t="n">
-        <v>0.36</v>
+        <v>0.05</v>
       </c>
       <c r="M225" s="3" t="n">
-        <v>8.31</v>
+        <v>5.16</v>
       </c>
       <c r="N225" s="4" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="O225" s="3" t="inlineStr"/>
       <c r="P225" s="2" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="Q225" t="inlineStr"/>
       <c r="R225" t="n">
-        <v>10.59</v>
+        <v>8.85</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -31158,40 +31214,40 @@
         </is>
       </c>
       <c r="X225" s="5" t="n">
-        <v>21.43</v>
+        <v>70.45</v>
       </c>
       <c r="Y225" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.53</v>
       </c>
       <c r="Z225" s="5" t="n">
-        <v>0.86</v>
+        <v>2.47</v>
       </c>
       <c r="AA225" s="5" t="n">
-        <v>-2.43</v>
+        <v>0.04</v>
       </c>
       <c r="AB225" s="5" t="n">
-        <v>0.49</v>
+        <v>2.23</v>
       </c>
       <c r="AC225" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD225" s="5" t="n">
+        <v>-4.31</v>
+      </c>
+      <c r="AE225" s="5" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AF225" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AG225" s="5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH225" s="5" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AI225" s="5" t="n">
         <v>0.09</v>
-      </c>
-      <c r="AD225" s="5" t="n">
-        <v>-4.71</v>
-      </c>
-      <c r="AE225" s="5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF225" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AG225" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AH225" s="5" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AI225" s="5" t="n">
-        <v>0.01</v>
       </c>
       <c r="AJ225" s="5" t="inlineStr"/>
       <c r="AK225" s="5" t="inlineStr"/>
@@ -31221,46 +31277,46 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>ha21_08</t>
+          <t>ha21_05</t>
         </is>
       </c>
       <c r="E226" s="2" t="n">
-        <v>8.31</v>
+        <v>5.16</v>
       </c>
       <c r="F226" s="2" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="G226" s="2" t="n">
-        <v>-1.205526030225079</v>
+        <v>-0.4341301938334387</v>
       </c>
       <c r="H226" s="2" t="n">
-        <v>0.7055260302250792</v>
+        <v>0.3541301938334387</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="J226" s="2" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="K226" s="3" t="n">
-        <v>0.36</v>
+        <v>0.05</v>
       </c>
       <c r="L226" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="M226" s="3" t="n">
-        <v>8.31</v>
+        <v>5.16</v>
       </c>
       <c r="N226" s="4" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="O226" s="3" t="inlineStr"/>
       <c r="P226" s="2" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="Q226" t="inlineStr"/>
       <c r="R226" t="n">
-        <v>10.59</v>
+        <v>8.85</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -31280,40 +31336,40 @@
         </is>
       </c>
       <c r="X226" s="5" t="n">
-        <v>18.48</v>
+        <v>72.98</v>
       </c>
       <c r="Y226" s="5" t="n">
-        <v>0.79</v>
+        <v>2.78</v>
       </c>
       <c r="Z226" s="5" t="n">
-        <v>0.74</v>
+        <v>2.55</v>
       </c>
       <c r="AA226" s="5" t="n">
-        <v>-1.2</v>
+        <v>1.96</v>
       </c>
       <c r="AB226" s="5" t="n">
-        <v>0.58</v>
+        <v>2.64</v>
       </c>
       <c r="AC226" s="5" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AD226" s="5" t="n">
-        <v>-4.33</v>
+        <v>-13.84</v>
       </c>
       <c r="AE226" s="5" t="n">
-        <v>1.18</v>
+        <v>5.89</v>
       </c>
       <c r="AF226" s="5" t="n">
-        <v>0.15</v>
+        <v>0.46</v>
       </c>
       <c r="AG226" s="5" t="n">
-        <v>3.1</v>
+        <v>7.15</v>
       </c>
       <c r="AH226" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="AI226" s="5" t="n">
-        <v>0.11</v>
+        <v>0.25</v>
       </c>
       <c r="AJ226" s="5" t="inlineStr"/>
       <c r="AK226" s="5" t="inlineStr"/>
@@ -31328,7 +31384,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>COMPASS_y20</t>
+          <t>HallA_y21</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -31343,40 +31399,46 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>compass_00</t>
+          <t>ha21_05</t>
         </is>
       </c>
       <c r="E227" s="2" t="n">
-        <v>2</v>
+        <v>5.16</v>
       </c>
       <c r="F227" s="2" t="n">
-        <v>0.093</v>
+        <v>0.48</v>
       </c>
       <c r="G227" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.4941301938334387</v>
       </c>
       <c r="H227" s="2" t="n">
-        <v>0.008489367844016771</v>
+        <v>0.3541301938334387</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>0.07151063215598323</v>
+        <v>0.14</v>
       </c>
       <c r="J227" s="2" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="K227" s="3" t="inlineStr"/>
-      <c r="L227" s="3" t="inlineStr"/>
+        <v>0.46</v>
+      </c>
+      <c r="K227" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L227" s="3" t="n">
+        <v>0.19</v>
+      </c>
       <c r="M227" s="3" t="n">
-        <v>2</v>
+        <v>5.16</v>
       </c>
       <c r="N227" s="4" t="n">
-        <v>0.093</v>
+        <v>0.48</v>
       </c>
       <c r="O227" s="3" t="inlineStr"/>
-      <c r="P227" s="2" t="inlineStr"/>
+      <c r="P227" s="2" t="n">
+        <v>0.55</v>
+      </c>
       <c r="Q227" t="inlineStr"/>
       <c r="R227" t="n">
-        <v>160</v>
+        <v>8.85</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
@@ -31392,39 +31454,45 @@
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>COMPASS, Phys. Lett. B 805 135454 (2020)</t>
+          <t>PRL 127 152301 (2021), supplemental table II</t>
         </is>
       </c>
       <c r="X227" s="5" t="n">
-        <v>16.3</v>
+        <v>65.77</v>
       </c>
       <c r="Y227" s="5" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="Z227" s="5" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AA227" s="5" t="n">
-        <v>0</v>
+        <v>-1.82</v>
       </c>
       <c r="AB227" s="5" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AC227" s="5" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AD227" s="5" t="n">
-        <v>0</v>
+        <v>-19.81</v>
       </c>
       <c r="AE227" s="5" t="n">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="AF227" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG227" s="5" t="inlineStr"/>
-      <c r="AH227" s="5" t="inlineStr"/>
-      <c r="AI227" s="5" t="inlineStr"/>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AG227" s="5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH227" s="5" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AI227" s="5" t="n">
+        <v>0.08</v>
+      </c>
       <c r="AJ227" s="5" t="inlineStr"/>
       <c r="AK227" s="5" t="inlineStr"/>
       <c r="AL227" s="5" t="inlineStr"/>
@@ -31438,7 +31506,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>COMPASS_y20</t>
+          <t>HallA_y21</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -31453,40 +31521,46 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>compass_00</t>
+          <t>ha21_05</t>
         </is>
       </c>
       <c r="E228" s="2" t="n">
-        <v>2</v>
+        <v>5.16</v>
       </c>
       <c r="F228" s="2" t="n">
-        <v>0.093</v>
+        <v>0.48</v>
       </c>
       <c r="G228" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.6041301938334387</v>
       </c>
       <c r="H228" s="2" t="n">
-        <v>0.008489367844016771</v>
+        <v>0.3541301938334387</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>0.1415106321559832</v>
+        <v>0.25</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="K228" s="3" t="inlineStr"/>
-      <c r="L228" s="3" t="inlineStr"/>
+        <v>0.46</v>
+      </c>
+      <c r="K228" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="L228" s="3" t="n">
+        <v>0.33</v>
+      </c>
       <c r="M228" s="3" t="n">
-        <v>2</v>
+        <v>5.16</v>
       </c>
       <c r="N228" s="4" t="n">
-        <v>0.093</v>
+        <v>0.48</v>
       </c>
       <c r="O228" s="3" t="inlineStr"/>
-      <c r="P228" s="2" t="inlineStr"/>
+      <c r="P228" s="2" t="n">
+        <v>0.55</v>
+      </c>
       <c r="Q228" t="inlineStr"/>
       <c r="R228" t="n">
-        <v>160</v>
+        <v>8.85</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -31502,39 +31576,45 @@
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>COMPASS, Phys. Lett. B 805 135454 (2020)</t>
+          <t>PRL 127 152301 (2021), supplemental table II</t>
         </is>
       </c>
       <c r="X228" s="5" t="n">
-        <v>16.2</v>
+        <v>58.49</v>
       </c>
       <c r="Y228" s="5" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="Z228" s="5" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA228" s="5" t="n">
-        <v>0</v>
+        <v>-4.52</v>
       </c>
       <c r="AB228" s="5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AC228" s="5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="AD228" s="5" t="n">
-        <v>0</v>
+        <v>-22.46</v>
       </c>
       <c r="AE228" s="5" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="AF228" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG228" s="5" t="inlineStr"/>
-      <c r="AH228" s="5" t="inlineStr"/>
-      <c r="AI228" s="5" t="inlineStr"/>
+        <v>0.79</v>
+      </c>
+      <c r="AG228" s="5" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="AH228" s="5" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AI228" s="5" t="n">
+        <v>0.23</v>
+      </c>
       <c r="AJ228" s="5" t="inlineStr"/>
       <c r="AK228" s="5" t="inlineStr"/>
       <c r="AL228" s="5" t="inlineStr"/>
@@ -31548,7 +31628,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>COMPASS_y20</t>
+          <t>HallA_y21</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -31563,40 +31643,46 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>compass_00</t>
+          <t>ha21_07</t>
         </is>
       </c>
       <c r="E229" s="2" t="n">
-        <v>2</v>
+        <v>6.56</v>
       </c>
       <c r="F229" s="2" t="n">
-        <v>0.093</v>
+        <v>0.48</v>
       </c>
       <c r="G229" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.3810616152049726</v>
       </c>
       <c r="H229" s="2" t="n">
-        <v>0.008489367844016771</v>
+        <v>0.3610616152049726</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>0.2115106321559832</v>
+        <v>0.02</v>
       </c>
       <c r="J229" s="2" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="K229" s="3" t="inlineStr"/>
-      <c r="L229" s="3" t="inlineStr"/>
+        <v>0.46</v>
+      </c>
+      <c r="K229" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L229" s="3" t="n">
+        <v>0.05</v>
+      </c>
       <c r="M229" s="3" t="n">
-        <v>2</v>
+        <v>6.56</v>
       </c>
       <c r="N229" s="4" t="n">
-        <v>0.093</v>
+        <v>0.48</v>
       </c>
       <c r="O229" s="3" t="inlineStr"/>
-      <c r="P229" s="2" t="inlineStr"/>
+      <c r="P229" s="2" t="n">
+        <v>0.52</v>
+      </c>
       <c r="Q229" t="inlineStr"/>
       <c r="R229" t="n">
-        <v>160</v>
+        <v>10.99</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
@@ -31612,39 +31698,45 @@
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>COMPASS, Phys. Lett. B 805 135454 (2020)</t>
+          <t>PRL 127 152301 (2021), supplemental table II</t>
         </is>
       </c>
       <c r="X229" s="5" t="n">
-        <v>11.5</v>
+        <v>33.48</v>
       </c>
       <c r="Y229" s="5" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="Z229" s="5" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AA229" s="5" t="n">
-        <v>0</v>
+        <v>-0.79</v>
       </c>
       <c r="AB229" s="5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC229" s="5" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AD229" s="5" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="AE229" s="5" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="AF229" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG229" s="5" t="inlineStr"/>
-      <c r="AH229" s="5" t="inlineStr"/>
-      <c r="AI229" s="5" t="inlineStr"/>
+        <v>0.23</v>
+      </c>
+      <c r="AG229" s="5" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AH229" s="5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AI229" s="5" t="n">
+        <v>0.11</v>
+      </c>
       <c r="AJ229" s="5" t="inlineStr"/>
       <c r="AK229" s="5" t="inlineStr"/>
       <c r="AL229" s="5" t="inlineStr"/>
@@ -31658,7 +31750,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>COMPASS_y20</t>
+          <t>HallA_y21</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -31673,40 +31765,46 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>compass_00</t>
+          <t>ha21_07</t>
         </is>
       </c>
       <c r="E230" s="2" t="n">
-        <v>2</v>
+        <v>6.56</v>
       </c>
       <c r="F230" s="2" t="n">
-        <v>0.093</v>
+        <v>0.48</v>
       </c>
       <c r="G230" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.4310616152049726</v>
       </c>
       <c r="H230" s="2" t="n">
-        <v>0.008489367844016771</v>
+        <v>0.3610616152049726</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>0.3515106321559832</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="K230" s="3" t="inlineStr"/>
-      <c r="L230" s="3" t="inlineStr"/>
+        <v>0.46</v>
+      </c>
+      <c r="K230" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L230" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M230" s="3" t="n">
-        <v>2</v>
+        <v>6.56</v>
       </c>
       <c r="N230" s="4" t="n">
-        <v>0.093</v>
+        <v>0.48</v>
       </c>
       <c r="O230" s="3" t="inlineStr"/>
-      <c r="P230" s="2" t="inlineStr"/>
+      <c r="P230" s="2" t="n">
+        <v>0.52</v>
+      </c>
       <c r="Q230" t="inlineStr"/>
       <c r="R230" t="n">
-        <v>160</v>
+        <v>10.99</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -31722,39 +31820,45 @@
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>COMPASS, Phys. Lett. B 805 135454 (2020)</t>
+          <t>PRL 127 152301 (2021), supplemental table II</t>
         </is>
       </c>
       <c r="X230" s="5" t="n">
-        <v>3.4</v>
+        <v>38.21</v>
       </c>
       <c r="Y230" s="5" t="n">
-        <v>1.4</v>
+        <v>2.06</v>
       </c>
       <c r="Z230" s="5" t="n">
-        <v>0.8</v>
+        <v>1.76</v>
       </c>
       <c r="AA230" s="5" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="AB230" s="5" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC230" s="5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AD230" s="5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE230" s="5" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="AF230" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG230" s="5" t="inlineStr"/>
-      <c r="AH230" s="5" t="inlineStr"/>
-      <c r="AI230" s="5" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="AG230" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AH230" s="5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AI230" s="5" t="n">
+        <v>0.03</v>
+      </c>
       <c r="AJ230" s="5" t="inlineStr"/>
       <c r="AK230" s="5" t="inlineStr"/>
       <c r="AL230" s="5" t="inlineStr"/>
@@ -31768,7 +31872,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>COMPASS_y20</t>
+          <t>HallA_y21</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -31783,40 +31887,46 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>compass_00</t>
+          <t>ha21_07</t>
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>2</v>
+        <v>6.56</v>
       </c>
       <c r="F231" s="2" t="n">
-        <v>0.093</v>
+        <v>0.48</v>
       </c>
       <c r="G231" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.4810616152049726</v>
       </c>
       <c r="H231" s="2" t="n">
-        <v>0.008489367844016771</v>
+        <v>0.3610616152049726</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>0.4915106321559832</v>
+        <v>0.12</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="K231" s="3" t="inlineStr"/>
-      <c r="L231" s="3" t="inlineStr"/>
+        <v>0.46</v>
+      </c>
+      <c r="K231" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L231" s="3" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M231" s="3" t="n">
-        <v>2</v>
+        <v>6.56</v>
       </c>
       <c r="N231" s="4" t="n">
-        <v>0.093</v>
+        <v>0.48</v>
       </c>
       <c r="O231" s="3" t="inlineStr"/>
-      <c r="P231" s="2" t="inlineStr"/>
+      <c r="P231" s="2" t="n">
+        <v>0.52</v>
+      </c>
       <c r="Q231" t="inlineStr"/>
       <c r="R231" t="n">
-        <v>160</v>
+        <v>10.99</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
@@ -31832,39 +31942,45 @@
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>COMPASS, Phys. Lett. B 805 135454 (2020)</t>
+          <t>PRL 127 152301 (2021), supplemental table II</t>
         </is>
       </c>
       <c r="X231" s="5" t="n">
-        <v>1.5</v>
+        <v>31.61</v>
       </c>
       <c r="Y231" s="5" t="n">
-        <v>1</v>
+        <v>2.35</v>
       </c>
       <c r="Z231" s="5" t="n">
-        <v>0.4</v>
+        <v>1.46</v>
       </c>
       <c r="AA231" s="5" t="n">
-        <v>0</v>
+        <v>-4.97</v>
       </c>
       <c r="AB231" s="5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AC231" s="5" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AD231" s="5" t="n">
-        <v>0</v>
+        <v>-4.24</v>
       </c>
       <c r="AE231" s="5" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="AF231" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG231" s="5" t="inlineStr"/>
-      <c r="AH231" s="5" t="inlineStr"/>
-      <c r="AI231" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="AG231" s="5" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="AH231" s="5" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AI231" s="5" t="n">
+        <v>0.37</v>
+      </c>
       <c r="AJ231" s="5" t="inlineStr"/>
       <c r="AK231" s="5" t="inlineStr"/>
       <c r="AL231" s="5" t="inlineStr"/>
@@ -31874,6 +31990,1654 @@
       <c r="AP231" s="5" t="inlineStr"/>
       <c r="AQ231" s="5" t="inlineStr"/>
       <c r="AR231" s="5" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>HallA_y21</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>ha21_07</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="F232" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G232" s="2" t="n">
+        <v>-0.5410616152049725</v>
+      </c>
+      <c r="H232" s="2" t="n">
+        <v>0.3610616152049726</v>
+      </c>
+      <c r="I232" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J232" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K232" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L232" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M232" s="3" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="N232" s="4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="O232" s="3" t="inlineStr"/>
+      <c r="P232" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Q232" t="inlineStr"/>
+      <c r="R232" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T232" s="5" t="inlineStr"/>
+      <c r="U232" s="5" t="inlineStr"/>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>PRL 127 152301 (2021), supplemental table II</t>
+        </is>
+      </c>
+      <c r="X232" s="5" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="Y232" s="5" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="Z232" s="5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA232" s="5" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="AB232" s="5" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="AC232" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AD232" s="5" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="AE232" s="5" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="AF232" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AG232" s="5" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="AH232" s="5" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AI232" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AJ232" s="5" t="inlineStr"/>
+      <c r="AK232" s="5" t="inlineStr"/>
+      <c r="AL232" s="5" t="inlineStr"/>
+      <c r="AM232" s="5" t="inlineStr"/>
+      <c r="AN232" s="5" t="inlineStr"/>
+      <c r="AO232" s="5" t="inlineStr"/>
+      <c r="AP232" s="5" t="inlineStr"/>
+      <c r="AQ232" s="5" t="inlineStr"/>
+      <c r="AR232" s="5" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>HallA_y21</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>ha21_06</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="F233" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G233" s="2" t="n">
+        <v>-0.7291233923215201</v>
+      </c>
+      <c r="H233" s="2" t="n">
+        <v>0.6691233923215201</v>
+      </c>
+      <c r="I233" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J233" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K233" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L233" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M233" s="3" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="N233" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O233" s="3" t="inlineStr"/>
+      <c r="P233" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="Q233" t="inlineStr"/>
+      <c r="R233" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T233" s="5" t="inlineStr"/>
+      <c r="U233" s="5" t="inlineStr"/>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>PRL 127 152301 (2021), supplemental table II</t>
+        </is>
+      </c>
+      <c r="X233" s="5" t="n">
+        <v>92.48</v>
+      </c>
+      <c r="Y233" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z233" s="5" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AA233" s="5" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="AB233" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC233" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AD233" s="5" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="AE233" s="5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF233" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG233" s="5" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="AH233" s="5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI233" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AJ233" s="5" t="inlineStr"/>
+      <c r="AK233" s="5" t="inlineStr"/>
+      <c r="AL233" s="5" t="inlineStr"/>
+      <c r="AM233" s="5" t="inlineStr"/>
+      <c r="AN233" s="5" t="inlineStr"/>
+      <c r="AO233" s="5" t="inlineStr"/>
+      <c r="AP233" s="5" t="inlineStr"/>
+      <c r="AQ233" s="5" t="inlineStr"/>
+      <c r="AR233" s="5" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>HallA_y21</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>ha21_06</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="F234" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G234" s="2" t="n">
+        <v>-0.84912339232152</v>
+      </c>
+      <c r="H234" s="2" t="n">
+        <v>0.6691233923215201</v>
+      </c>
+      <c r="I234" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J234" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K234" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L234" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M234" s="3" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="N234" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O234" s="3" t="inlineStr"/>
+      <c r="P234" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="Q234" t="inlineStr"/>
+      <c r="R234" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T234" s="5" t="inlineStr"/>
+      <c r="U234" s="5" t="inlineStr"/>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>PRL 127 152301 (2021), supplemental table II</t>
+        </is>
+      </c>
+      <c r="X234" s="5" t="n">
+        <v>86.89</v>
+      </c>
+      <c r="Y234" s="5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z234" s="5" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AA234" s="5" t="n">
+        <v>-5.12</v>
+      </c>
+      <c r="AB234" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC234" s="5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD234" s="5" t="n">
+        <v>-4.28</v>
+      </c>
+      <c r="AE234" s="5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF234" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AG234" s="5" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="AH234" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI234" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AJ234" s="5" t="inlineStr"/>
+      <c r="AK234" s="5" t="inlineStr"/>
+      <c r="AL234" s="5" t="inlineStr"/>
+      <c r="AM234" s="5" t="inlineStr"/>
+      <c r="AN234" s="5" t="inlineStr"/>
+      <c r="AO234" s="5" t="inlineStr"/>
+      <c r="AP234" s="5" t="inlineStr"/>
+      <c r="AQ234" s="5" t="inlineStr"/>
+      <c r="AR234" s="5" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>HallA_y21</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>ha21_06</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="F235" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G235" s="2" t="n">
+        <v>-1.00912339232152</v>
+      </c>
+      <c r="H235" s="2" t="n">
+        <v>0.6691233923215201</v>
+      </c>
+      <c r="I235" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J235" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K235" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L235" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M235" s="3" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="N235" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O235" s="3" t="inlineStr"/>
+      <c r="P235" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="Q235" t="inlineStr"/>
+      <c r="R235" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T235" s="5" t="inlineStr"/>
+      <c r="U235" s="5" t="inlineStr"/>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>PRL 127 152301 (2021), supplemental table II</t>
+        </is>
+      </c>
+      <c r="X235" s="5" t="n">
+        <v>78.95999999999999</v>
+      </c>
+      <c r="Y235" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z235" s="5" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AA235" s="5" t="n">
+        <v>-6.44</v>
+      </c>
+      <c r="AB235" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AC235" s="5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD235" s="5" t="n">
+        <v>-17.84</v>
+      </c>
+      <c r="AE235" s="5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF235" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AG235" s="5" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="AH235" s="5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI235" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AJ235" s="5" t="inlineStr"/>
+      <c r="AK235" s="5" t="inlineStr"/>
+      <c r="AL235" s="5" t="inlineStr"/>
+      <c r="AM235" s="5" t="inlineStr"/>
+      <c r="AN235" s="5" t="inlineStr"/>
+      <c r="AO235" s="5" t="inlineStr"/>
+      <c r="AP235" s="5" t="inlineStr"/>
+      <c r="AQ235" s="5" t="inlineStr"/>
+      <c r="AR235" s="5" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>HallA_y21</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>ha21_06</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="F236" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G236" s="2" t="n">
+        <v>-1.27912339232152</v>
+      </c>
+      <c r="H236" s="2" t="n">
+        <v>0.6691233923215201</v>
+      </c>
+      <c r="I236" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="J236" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K236" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L236" s="3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M236" s="3" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="N236" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O236" s="3" t="inlineStr"/>
+      <c r="P236" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="Q236" t="inlineStr"/>
+      <c r="R236" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T236" s="5" t="inlineStr"/>
+      <c r="U236" s="5" t="inlineStr"/>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>PRL 127 152301 (2021), supplemental table II</t>
+        </is>
+      </c>
+      <c r="X236" s="5" t="n">
+        <v>63.43</v>
+      </c>
+      <c r="Y236" s="5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z236" s="5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA236" s="5" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="AB236" s="5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC236" s="5" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AD236" s="5" t="n">
+        <v>-13.65</v>
+      </c>
+      <c r="AE236" s="5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF236" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AG236" s="5" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="AH236" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI236" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AJ236" s="5" t="inlineStr"/>
+      <c r="AK236" s="5" t="inlineStr"/>
+      <c r="AL236" s="5" t="inlineStr"/>
+      <c r="AM236" s="5" t="inlineStr"/>
+      <c r="AN236" s="5" t="inlineStr"/>
+      <c r="AO236" s="5" t="inlineStr"/>
+      <c r="AP236" s="5" t="inlineStr"/>
+      <c r="AQ236" s="5" t="inlineStr"/>
+      <c r="AR236" s="5" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>HallA_y21</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>ha21_08</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="F237" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G237" s="2" t="n">
+        <v>-0.7555260302250792</v>
+      </c>
+      <c r="H237" s="2" t="n">
+        <v>0.7055260302250792</v>
+      </c>
+      <c r="I237" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J237" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K237" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L237" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M237" s="3" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="N237" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O237" s="3" t="inlineStr"/>
+      <c r="P237" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q237" t="inlineStr"/>
+      <c r="R237" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T237" s="5" t="inlineStr"/>
+      <c r="U237" s="5" t="inlineStr"/>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>PRL 127 152301 (2021), supplemental table II</t>
+        </is>
+      </c>
+      <c r="X237" s="5" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="Y237" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z237" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA237" s="5" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="AB237" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AC237" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AD237" s="5" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="AE237" s="5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF237" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AG237" s="5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH237" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI237" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AJ237" s="5" t="inlineStr"/>
+      <c r="AK237" s="5" t="inlineStr"/>
+      <c r="AL237" s="5" t="inlineStr"/>
+      <c r="AM237" s="5" t="inlineStr"/>
+      <c r="AN237" s="5" t="inlineStr"/>
+      <c r="AO237" s="5" t="inlineStr"/>
+      <c r="AP237" s="5" t="inlineStr"/>
+      <c r="AQ237" s="5" t="inlineStr"/>
+      <c r="AR237" s="5" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>HallA_y21</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>ha21_08</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="F238" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G238" s="2" t="n">
+        <v>-0.8555260302250792</v>
+      </c>
+      <c r="H238" s="2" t="n">
+        <v>0.7055260302250792</v>
+      </c>
+      <c r="I238" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J238" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K238" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L238" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M238" s="3" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="N238" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O238" s="3" t="inlineStr"/>
+      <c r="P238" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q238" t="inlineStr"/>
+      <c r="R238" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T238" s="5" t="inlineStr"/>
+      <c r="U238" s="5" t="inlineStr"/>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>PRL 127 152301 (2021), supplemental table II</t>
+        </is>
+      </c>
+      <c r="X238" s="5" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="Y238" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="Z238" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA238" s="5" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AB238" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AC238" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AD238" s="5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AE238" s="5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF238" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG238" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH238" s="5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AI238" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AJ238" s="5" t="inlineStr"/>
+      <c r="AK238" s="5" t="inlineStr"/>
+      <c r="AL238" s="5" t="inlineStr"/>
+      <c r="AM238" s="5" t="inlineStr"/>
+      <c r="AN238" s="5" t="inlineStr"/>
+      <c r="AO238" s="5" t="inlineStr"/>
+      <c r="AP238" s="5" t="inlineStr"/>
+      <c r="AQ238" s="5" t="inlineStr"/>
+      <c r="AR238" s="5" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>HallA_y21</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>ha21_08</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="F239" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G239" s="2" t="n">
+        <v>-0.9855260302250792</v>
+      </c>
+      <c r="H239" s="2" t="n">
+        <v>0.7055260302250792</v>
+      </c>
+      <c r="I239" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J239" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K239" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L239" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M239" s="3" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="N239" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O239" s="3" t="inlineStr"/>
+      <c r="P239" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q239" t="inlineStr"/>
+      <c r="R239" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T239" s="5" t="inlineStr"/>
+      <c r="U239" s="5" t="inlineStr"/>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>PRL 127 152301 (2021), supplemental table II</t>
+        </is>
+      </c>
+      <c r="X239" s="5" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="Y239" s="5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="Z239" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AA239" s="5" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="AB239" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AC239" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AD239" s="5" t="n">
+        <v>-4.71</v>
+      </c>
+      <c r="AE239" s="5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF239" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AG239" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AH239" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AI239" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AJ239" s="5" t="inlineStr"/>
+      <c r="AK239" s="5" t="inlineStr"/>
+      <c r="AL239" s="5" t="inlineStr"/>
+      <c r="AM239" s="5" t="inlineStr"/>
+      <c r="AN239" s="5" t="inlineStr"/>
+      <c r="AO239" s="5" t="inlineStr"/>
+      <c r="AP239" s="5" t="inlineStr"/>
+      <c r="AQ239" s="5" t="inlineStr"/>
+      <c r="AR239" s="5" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>HallA_y21</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>ha21_08</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="F240" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G240" s="2" t="n">
+        <v>-1.205526030225079</v>
+      </c>
+      <c r="H240" s="2" t="n">
+        <v>0.7055260302250792</v>
+      </c>
+      <c r="I240" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J240" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K240" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L240" s="3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M240" s="3" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="N240" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O240" s="3" t="inlineStr"/>
+      <c r="P240" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q240" t="inlineStr"/>
+      <c r="R240" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T240" s="5" t="inlineStr"/>
+      <c r="U240" s="5" t="inlineStr"/>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>PRL 127 152301 (2021), supplemental table II</t>
+        </is>
+      </c>
+      <c r="X240" s="5" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="Y240" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Z240" s="5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AA240" s="5" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AB240" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AC240" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AD240" s="5" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="AE240" s="5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF240" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AG240" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH240" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AI240" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AJ240" s="5" t="inlineStr"/>
+      <c r="AK240" s="5" t="inlineStr"/>
+      <c r="AL240" s="5" t="inlineStr"/>
+      <c r="AM240" s="5" t="inlineStr"/>
+      <c r="AN240" s="5" t="inlineStr"/>
+      <c r="AO240" s="5" t="inlineStr"/>
+      <c r="AP240" s="5" t="inlineStr"/>
+      <c r="AQ240" s="5" t="inlineStr"/>
+      <c r="AR240" s="5" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>COMPASS_y20</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>compass_00</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F241" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="G241" s="2" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="H241" s="2" t="n">
+        <v>0.008489367844016771</v>
+      </c>
+      <c r="I241" s="2" t="n">
+        <v>0.07151063215598323</v>
+      </c>
+      <c r="J241" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="K241" s="3" t="inlineStr"/>
+      <c r="L241" s="3" t="inlineStr"/>
+      <c r="M241" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N241" s="4" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="O241" s="3" t="inlineStr"/>
+      <c r="P241" s="2" t="inlineStr"/>
+      <c r="Q241" t="inlineStr"/>
+      <c r="R241" t="n">
+        <v>160</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T241" s="5" t="inlineStr"/>
+      <c r="U241" s="5" t="inlineStr"/>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>COMPASS, Phys. Lett. B 805 135454 (2020)</t>
+        </is>
+      </c>
+      <c r="X241" s="5" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="Y241" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Z241" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA241" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB241" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC241" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD241" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE241" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF241" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG241" s="5" t="inlineStr"/>
+      <c r="AH241" s="5" t="inlineStr"/>
+      <c r="AI241" s="5" t="inlineStr"/>
+      <c r="AJ241" s="5" t="inlineStr"/>
+      <c r="AK241" s="5" t="inlineStr"/>
+      <c r="AL241" s="5" t="inlineStr"/>
+      <c r="AM241" s="5" t="inlineStr"/>
+      <c r="AN241" s="5" t="inlineStr"/>
+      <c r="AO241" s="5" t="inlineStr"/>
+      <c r="AP241" s="5" t="inlineStr"/>
+      <c r="AQ241" s="5" t="inlineStr"/>
+      <c r="AR241" s="5" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>COMPASS_y20</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>compass_00</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F242" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="G242" s="2" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="H242" s="2" t="n">
+        <v>0.008489367844016771</v>
+      </c>
+      <c r="I242" s="2" t="n">
+        <v>0.1415106321559832</v>
+      </c>
+      <c r="J242" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="K242" s="3" t="inlineStr"/>
+      <c r="L242" s="3" t="inlineStr"/>
+      <c r="M242" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N242" s="4" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="O242" s="3" t="inlineStr"/>
+      <c r="P242" s="2" t="inlineStr"/>
+      <c r="Q242" t="inlineStr"/>
+      <c r="R242" t="n">
+        <v>160</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T242" s="5" t="inlineStr"/>
+      <c r="U242" s="5" t="inlineStr"/>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>COMPASS, Phys. Lett. B 805 135454 (2020)</t>
+        </is>
+      </c>
+      <c r="X242" s="5" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="Y242" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Z242" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA242" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB242" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC242" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD242" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE242" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF242" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG242" s="5" t="inlineStr"/>
+      <c r="AH242" s="5" t="inlineStr"/>
+      <c r="AI242" s="5" t="inlineStr"/>
+      <c r="AJ242" s="5" t="inlineStr"/>
+      <c r="AK242" s="5" t="inlineStr"/>
+      <c r="AL242" s="5" t="inlineStr"/>
+      <c r="AM242" s="5" t="inlineStr"/>
+      <c r="AN242" s="5" t="inlineStr"/>
+      <c r="AO242" s="5" t="inlineStr"/>
+      <c r="AP242" s="5" t="inlineStr"/>
+      <c r="AQ242" s="5" t="inlineStr"/>
+      <c r="AR242" s="5" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>COMPASS_y20</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>compass_00</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F243" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="G243" s="2" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="H243" s="2" t="n">
+        <v>0.008489367844016771</v>
+      </c>
+      <c r="I243" s="2" t="n">
+        <v>0.2115106321559832</v>
+      </c>
+      <c r="J243" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="K243" s="3" t="inlineStr"/>
+      <c r="L243" s="3" t="inlineStr"/>
+      <c r="M243" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N243" s="4" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="O243" s="3" t="inlineStr"/>
+      <c r="P243" s="2" t="inlineStr"/>
+      <c r="Q243" t="inlineStr"/>
+      <c r="R243" t="n">
+        <v>160</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T243" s="5" t="inlineStr"/>
+      <c r="U243" s="5" t="inlineStr"/>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>COMPASS, Phys. Lett. B 805 135454 (2020)</t>
+        </is>
+      </c>
+      <c r="X243" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y243" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z243" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA243" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB243" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC243" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD243" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE243" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF243" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG243" s="5" t="inlineStr"/>
+      <c r="AH243" s="5" t="inlineStr"/>
+      <c r="AI243" s="5" t="inlineStr"/>
+      <c r="AJ243" s="5" t="inlineStr"/>
+      <c r="AK243" s="5" t="inlineStr"/>
+      <c r="AL243" s="5" t="inlineStr"/>
+      <c r="AM243" s="5" t="inlineStr"/>
+      <c r="AN243" s="5" t="inlineStr"/>
+      <c r="AO243" s="5" t="inlineStr"/>
+      <c r="AP243" s="5" t="inlineStr"/>
+      <c r="AQ243" s="5" t="inlineStr"/>
+      <c r="AR243" s="5" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>COMPASS_y20</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>compass_00</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F244" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="G244" s="2" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="H244" s="2" t="n">
+        <v>0.008489367844016771</v>
+      </c>
+      <c r="I244" s="2" t="n">
+        <v>0.3515106321559832</v>
+      </c>
+      <c r="J244" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="K244" s="3" t="inlineStr"/>
+      <c r="L244" s="3" t="inlineStr"/>
+      <c r="M244" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N244" s="4" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="O244" s="3" t="inlineStr"/>
+      <c r="P244" s="2" t="inlineStr"/>
+      <c r="Q244" t="inlineStr"/>
+      <c r="R244" t="n">
+        <v>160</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T244" s="5" t="inlineStr"/>
+      <c r="U244" s="5" t="inlineStr"/>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>COMPASS, Phys. Lett. B 805 135454 (2020)</t>
+        </is>
+      </c>
+      <c r="X244" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y244" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z244" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AA244" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB244" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC244" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD244" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE244" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF244" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG244" s="5" t="inlineStr"/>
+      <c r="AH244" s="5" t="inlineStr"/>
+      <c r="AI244" s="5" t="inlineStr"/>
+      <c r="AJ244" s="5" t="inlineStr"/>
+      <c r="AK244" s="5" t="inlineStr"/>
+      <c r="AL244" s="5" t="inlineStr"/>
+      <c r="AM244" s="5" t="inlineStr"/>
+      <c r="AN244" s="5" t="inlineStr"/>
+      <c r="AO244" s="5" t="inlineStr"/>
+      <c r="AP244" s="5" t="inlineStr"/>
+      <c r="AQ244" s="5" t="inlineStr"/>
+      <c r="AR244" s="5" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>COMPASS_y20</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>compass_00</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F245" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="G245" s="2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H245" s="2" t="n">
+        <v>0.008489367844016771</v>
+      </c>
+      <c r="I245" s="2" t="n">
+        <v>0.4915106321559832</v>
+      </c>
+      <c r="J245" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="K245" s="3" t="inlineStr"/>
+      <c r="L245" s="3" t="inlineStr"/>
+      <c r="M245" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N245" s="4" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="O245" s="3" t="inlineStr"/>
+      <c r="P245" s="2" t="inlineStr"/>
+      <c r="Q245" t="inlineStr"/>
+      <c r="R245" t="n">
+        <v>160</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T245" s="5" t="inlineStr"/>
+      <c r="U245" s="5" t="inlineStr"/>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>COMPASS, Phys. Lett. B 805 135454 (2020)</t>
+        </is>
+      </c>
+      <c r="X245" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y245" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z245" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA245" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB245" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC245" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD245" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE245" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF245" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG245" s="5" t="inlineStr"/>
+      <c r="AH245" s="5" t="inlineStr"/>
+      <c r="AI245" s="5" t="inlineStr"/>
+      <c r="AJ245" s="5" t="inlineStr"/>
+      <c r="AK245" s="5" t="inlineStr"/>
+      <c r="AL245" s="5" t="inlineStr"/>
+      <c r="AM245" s="5" t="inlineStr"/>
+      <c r="AN245" s="5" t="inlineStr"/>
+      <c r="AO245" s="5" t="inlineStr"/>
+      <c r="AP245" s="5" t="inlineStr"/>
+      <c r="AQ245" s="5" t="inlineStr"/>
+      <c r="AR245" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pi0_eta_database.xlsx
+++ b/pi0_eta_database.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,7 +891,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>COMPASS_y20 pi0 p</t>
+          <t>COMPASS_y25 pi0 p</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.00-2.00</t>
+          <t>1.22-4.33</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.093-0.093</t>
+          <t>0.057-0.247</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.5000..-0.0800</t>
+          <t>-0.5700..-0.1200</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -934,47 +934,47 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>COMPASS, Phys. Lett. B 805 135454 (2020)</t>
+          <t>COMPASS, PLB 870 139832 (2025), t projection</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>asymmetry</t>
+          <t>cross section</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CLAS6_demasi</t>
+          <t>COMPASS_y20 pi0 p</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_U, sigma_LT, sigma_TT</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.30-4.40</t>
+          <t>2.00-2.00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.141-0.517</t>
+          <t>0.093-0.093</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-1.3320..-0.1470</t>
+          <t>-0.5000..-0.0800</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.776</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -984,12 +984,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>De Masi et al., PRC 77 042201(R) (2008), figure extraction</t>
+          <t>superseded by PLB 870 139832 (2025); t here is the bin lower edge and Q2, xB are nominal, not the bin averages</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CLAS6_zhao</t>
+          <t>CLAS6_demasi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1010,21 +1010,21 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.51-3.10</t>
+          <t>1.30-4.40</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.210-0.400</t>
+          <t>0.141-0.517</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.2100..-0.2580</t>
+          <t>-1.3320..-0.1470</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Zhao et al., PLB 789 426 (2019), figure extraction</t>
+          <t>De Masi et al., PRC 77 042201(R) (2008), figure extraction</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLAS12_y24</t>
+          <t>CLAS6_zhao</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1065,26 +1065,26 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.58-6.64</t>
+          <t>1.51-3.10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.290-0.560</t>
+          <t>0.210-0.400</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.6510..-0.3250</t>
+          <t>-1.2100..-0.2580</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>5.776</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Zhao et al., PLB 789 426 (2019), figure extraction</t>
         </is>
       </c>
     </row>
@@ -1111,35 +1111,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>eg1dvcs</t>
+          <t>CLAS12_y24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A_UL^sinphi</t>
+          <t>A_LU^sinphi</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.94-2.83</t>
+          <t>2.58-6.64</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.250-0.400</t>
+          <t>0.290-0.560</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-1.5900..-0.1500</t>
+          <t>-1.6510..-0.3250</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 768 168 (2017), CLAS DB E154M5</t>
+          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A_UL^sin2phi</t>
+          <t>A_UL^sinphi</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 768 168 (2017), CLAS DB E154M7</t>
+          <t>Kim et al., PLB 768 168 (2017), CLAS DB E154M5</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A_LL^const</t>
+          <t>A_UL^sin2phi</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 768 168 (2017), CLAS DB E154M9</t>
+          <t>Kim et al., PLB 768 168 (2017), CLAS DB E154M7</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A_LL^cosphi</t>
+          <t>A_LL^const</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1318,6 +1318,61 @@
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>Kim et al., PLB 768 168 (2017), CLAS DB E154M9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>asymmetry</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>eg1dvcs</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>A_LL^cosphi</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.94-2.83</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.250-0.400</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-1.5900..-0.1500</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>Kim et al., PLB 768 168 (2017), CLAS DB E154M11</t>
         </is>
@@ -1334,7 +1389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR392"/>
+  <dimension ref="A1:AR405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49320,7 +49375,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>COMPASS_y20</t>
+          <t>COMPASS_y25</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -49335,37 +49390,39 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>compass_00</t>
+          <t>compass_t</t>
         </is>
       </c>
       <c r="E388" s="2" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="F388" s="2" t="n">
-        <v>0.093</v>
+        <v>0.104</v>
       </c>
       <c r="G388" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="H388" s="2" t="n">
-        <v>0.008489367844016771</v>
+        <v>0.01072995875111937</v>
       </c>
       <c r="I388" s="2" t="n">
-        <v>0.07151063215598323</v>
+        <v>0.1092700412488806</v>
       </c>
       <c r="J388" s="2" t="n">
-        <v>0.093</v>
+        <v>0.104</v>
       </c>
       <c r="K388" s="3" t="inlineStr"/>
       <c r="L388" s="3" t="inlineStr"/>
       <c r="M388" s="3" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="N388" s="4" t="n">
-        <v>0.093</v>
+        <v>0.104</v>
       </c>
       <c r="O388" s="3" t="inlineStr"/>
-      <c r="P388" s="2" t="inlineStr"/>
+      <c r="P388" s="2" t="n">
+        <v>0.996</v>
+      </c>
       <c r="Q388" t="inlineStr"/>
       <c r="R388" t="n">
         <v>160</v>
@@ -49384,35 +49441,29 @@
       </c>
       <c r="W388" t="inlineStr">
         <is>
-          <t>COMPASS, Phys. Lett. B 805 135454 (2020)</t>
+          <t>COMPASS, PLB 870 139832 (2025), t projection</t>
         </is>
       </c>
       <c r="X388" s="5" t="n">
-        <v>16.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y388" s="5" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="Z388" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA388" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB388" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC388" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="AA388" s="5" t="inlineStr"/>
+      <c r="AB388" s="5" t="inlineStr"/>
+      <c r="AC388" s="5" t="inlineStr"/>
       <c r="AD388" s="5" t="n">
-        <v>0</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE388" s="5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF388" s="5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AG388" s="5" t="inlineStr"/>
       <c r="AH388" s="5" t="inlineStr"/>
@@ -49430,7 +49481,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>COMPASS_y20</t>
+          <t>COMPASS_y25</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -49445,37 +49496,39 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>compass_00</t>
+          <t>compass_t</t>
         </is>
       </c>
       <c r="E389" s="2" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="F389" s="2" t="n">
-        <v>0.093</v>
+        <v>0.123</v>
       </c>
       <c r="G389" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.18</v>
       </c>
       <c r="H389" s="2" t="n">
-        <v>0.008489367844016771</v>
+        <v>0.01526527820435675</v>
       </c>
       <c r="I389" s="2" t="n">
-        <v>0.1415106321559832</v>
+        <v>0.1647347217956432</v>
       </c>
       <c r="J389" s="2" t="n">
-        <v>0.093</v>
+        <v>0.123</v>
       </c>
       <c r="K389" s="3" t="inlineStr"/>
       <c r="L389" s="3" t="inlineStr"/>
       <c r="M389" s="3" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="N389" s="4" t="n">
-        <v>0.093</v>
+        <v>0.123</v>
       </c>
       <c r="O389" s="3" t="inlineStr"/>
-      <c r="P389" s="2" t="inlineStr"/>
+      <c r="P389" s="2" t="n">
+        <v>0.997</v>
+      </c>
       <c r="Q389" t="inlineStr"/>
       <c r="R389" t="n">
         <v>160</v>
@@ -49494,35 +49547,29 @@
       </c>
       <c r="W389" t="inlineStr">
         <is>
-          <t>COMPASS, Phys. Lett. B 805 135454 (2020)</t>
+          <t>COMPASS, PLB 870 139832 (2025), t projection</t>
         </is>
       </c>
       <c r="X389" s="5" t="n">
-        <v>16.2</v>
+        <v>11.5</v>
       </c>
       <c r="Y389" s="5" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="Z389" s="5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA389" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB389" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC389" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>1.3</v>
+      </c>
+      <c r="AA389" s="5" t="inlineStr"/>
+      <c r="AB389" s="5" t="inlineStr"/>
+      <c r="AC389" s="5" t="inlineStr"/>
       <c r="AD389" s="5" t="n">
-        <v>0</v>
+        <v>-6.3</v>
       </c>
       <c r="AE389" s="5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF389" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AG389" s="5" t="inlineStr"/>
       <c r="AH389" s="5" t="inlineStr"/>
@@ -49540,7 +49587,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>COMPASS_y20</t>
+          <t>COMPASS_y25</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -49555,37 +49602,39 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>compass_00</t>
+          <t>compass_t</t>
         </is>
       </c>
       <c r="E390" s="2" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="F390" s="2" t="n">
-        <v>0.093</v>
+        <v>0.14</v>
       </c>
       <c r="G390" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.28</v>
       </c>
       <c r="H390" s="2" t="n">
-        <v>0.008489367844016771</v>
+        <v>0.02008695356633927</v>
       </c>
       <c r="I390" s="2" t="n">
-        <v>0.2115106321559832</v>
+        <v>0.2599130464336608</v>
       </c>
       <c r="J390" s="2" t="n">
-        <v>0.093</v>
+        <v>0.14</v>
       </c>
       <c r="K390" s="3" t="inlineStr"/>
       <c r="L390" s="3" t="inlineStr"/>
       <c r="M390" s="3" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="N390" s="4" t="n">
-        <v>0.093</v>
+        <v>0.14</v>
       </c>
       <c r="O390" s="3" t="inlineStr"/>
-      <c r="P390" s="2" t="inlineStr"/>
+      <c r="P390" s="2" t="n">
+        <v>0.997</v>
+      </c>
       <c r="Q390" t="inlineStr"/>
       <c r="R390" t="n">
         <v>160</v>
@@ -49604,35 +49653,29 @@
       </c>
       <c r="W390" t="inlineStr">
         <is>
-          <t>COMPASS, Phys. Lett. B 805 135454 (2020)</t>
+          <t>COMPASS, PLB 870 139832 (2025), t projection</t>
         </is>
       </c>
       <c r="X390" s="5" t="n">
-        <v>11.5</v>
+        <v>6.8</v>
       </c>
       <c r="Y390" s="5" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="Z390" s="5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA390" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB390" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC390" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="AA390" s="5" t="inlineStr"/>
+      <c r="AB390" s="5" t="inlineStr"/>
+      <c r="AC390" s="5" t="inlineStr"/>
       <c r="AD390" s="5" t="n">
-        <v>0</v>
+        <v>-4.1</v>
       </c>
       <c r="AE390" s="5" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AF390" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AG390" s="5" t="inlineStr"/>
       <c r="AH390" s="5" t="inlineStr"/>
@@ -49650,7 +49693,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>COMPASS_y20</t>
+          <t>COMPASS_y25</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -49665,37 +49708,39 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>compass_00</t>
+          <t>compass_t</t>
         </is>
       </c>
       <c r="E391" s="2" t="n">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="F391" s="2" t="n">
-        <v>0.093</v>
+        <v>0.15</v>
       </c>
       <c r="G391" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.42</v>
       </c>
       <c r="H391" s="2" t="n">
-        <v>0.008489367844016771</v>
+        <v>0.02327735895058192</v>
       </c>
       <c r="I391" s="2" t="n">
-        <v>0.3515106321559832</v>
+        <v>0.3967226410494181</v>
       </c>
       <c r="J391" s="2" t="n">
-        <v>0.093</v>
+        <v>0.15</v>
       </c>
       <c r="K391" s="3" t="inlineStr"/>
       <c r="L391" s="3" t="inlineStr"/>
       <c r="M391" s="3" t="n">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="N391" s="4" t="n">
-        <v>0.093</v>
+        <v>0.15</v>
       </c>
       <c r="O391" s="3" t="inlineStr"/>
-      <c r="P391" s="2" t="inlineStr"/>
+      <c r="P391" s="2" t="n">
+        <v>0.998</v>
+      </c>
       <c r="Q391" t="inlineStr"/>
       <c r="R391" t="n">
         <v>160</v>
@@ -49714,35 +49759,29 @@
       </c>
       <c r="W391" t="inlineStr">
         <is>
-          <t>COMPASS, Phys. Lett. B 805 135454 (2020)</t>
+          <t>COMPASS, PLB 870 139832 (2025), t projection</t>
         </is>
       </c>
       <c r="X391" s="5" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="Y391" s="5" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="Z391" s="5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AA391" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB391" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC391" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="AA391" s="5" t="inlineStr"/>
+      <c r="AB391" s="5" t="inlineStr"/>
+      <c r="AC391" s="5" t="inlineStr"/>
       <c r="AD391" s="5" t="n">
-        <v>0</v>
+        <v>-3.8</v>
       </c>
       <c r="AE391" s="5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AF391" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AG391" s="5" t="inlineStr"/>
       <c r="AH391" s="5" t="inlineStr"/>
@@ -49760,7 +49799,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>COMPASS_y20</t>
+          <t>COMPASS_y25</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -49775,37 +49814,39 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>compass_00</t>
+          <t>compass_t</t>
         </is>
       </c>
       <c r="E392" s="2" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="F392" s="2" t="n">
-        <v>0.093</v>
+        <v>0.165</v>
       </c>
       <c r="G392" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.57</v>
       </c>
       <c r="H392" s="2" t="n">
-        <v>0.008489367844016771</v>
+        <v>0.0285779856216859</v>
       </c>
       <c r="I392" s="2" t="n">
-        <v>0.4915106321559832</v>
+        <v>0.5414220143783141</v>
       </c>
       <c r="J392" s="2" t="n">
-        <v>0.093</v>
+        <v>0.165</v>
       </c>
       <c r="K392" s="3" t="inlineStr"/>
       <c r="L392" s="3" t="inlineStr"/>
       <c r="M392" s="3" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="N392" s="4" t="n">
-        <v>0.093</v>
+        <v>0.165</v>
       </c>
       <c r="O392" s="3" t="inlineStr"/>
-      <c r="P392" s="2" t="inlineStr"/>
+      <c r="P392" s="2" t="n">
+        <v>0.998</v>
+      </c>
       <c r="Q392" t="inlineStr"/>
       <c r="R392" t="n">
         <v>160</v>
@@ -49824,35 +49865,29 @@
       </c>
       <c r="W392" t="inlineStr">
         <is>
-          <t>COMPASS, Phys. Lett. B 805 135454 (2020)</t>
+          <t>COMPASS, PLB 870 139832 (2025), t projection</t>
         </is>
       </c>
       <c r="X392" s="5" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="Y392" s="5" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Z392" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AA392" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB392" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC392" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="AA392" s="5" t="inlineStr"/>
+      <c r="AB392" s="5" t="inlineStr"/>
+      <c r="AC392" s="5" t="inlineStr"/>
       <c r="AD392" s="5" t="n">
-        <v>0</v>
+        <v>-2.8</v>
       </c>
       <c r="AE392" s="5" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AF392" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG392" s="5" t="inlineStr"/>
       <c r="AH392" s="5" t="inlineStr"/>
@@ -49866,6 +49901,1410 @@
       <c r="AP392" s="5" t="inlineStr"/>
       <c r="AQ392" s="5" t="inlineStr"/>
       <c r="AR392" s="5" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>COMPASS_y25</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>compass_Q2</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F393" s="2" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="G393" s="2" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="H393" s="2" t="n">
+        <v>0.005033257335086194</v>
+      </c>
+      <c r="I393" s="2" t="n">
+        <v>0.2649667426649138</v>
+      </c>
+      <c r="J393" s="2" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="K393" s="3" t="inlineStr"/>
+      <c r="L393" s="3" t="inlineStr"/>
+      <c r="M393" s="3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="N393" s="4" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="O393" s="3" t="inlineStr"/>
+      <c r="P393" s="2" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="Q393" t="inlineStr"/>
+      <c r="R393" t="n">
+        <v>160</v>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T393" s="5" t="inlineStr"/>
+      <c r="U393" s="5" t="inlineStr"/>
+      <c r="V393" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W393" t="inlineStr">
+        <is>
+          <t>COMPASS, PLB 870 139832 (2025), Q2 projection</t>
+        </is>
+      </c>
+      <c r="X393" s="5" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="Y393" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z393" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA393" s="5" t="inlineStr"/>
+      <c r="AB393" s="5" t="inlineStr"/>
+      <c r="AC393" s="5" t="inlineStr"/>
+      <c r="AD393" s="5" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="AE393" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF393" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AG393" s="5" t="inlineStr"/>
+      <c r="AH393" s="5" t="inlineStr"/>
+      <c r="AI393" s="5" t="inlineStr"/>
+      <c r="AJ393" s="5" t="inlineStr"/>
+      <c r="AK393" s="5" t="inlineStr"/>
+      <c r="AL393" s="5" t="inlineStr"/>
+      <c r="AM393" s="5" t="inlineStr"/>
+      <c r="AN393" s="5" t="inlineStr"/>
+      <c r="AO393" s="5" t="inlineStr"/>
+      <c r="AP393" s="5" t="inlineStr"/>
+      <c r="AQ393" s="5" t="inlineStr"/>
+      <c r="AR393" s="5" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>COMPASS_y25</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>compass_Q2</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="F394" s="2" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="G394" s="2" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="H394" s="2" t="n">
+        <v>0.01185047772727166</v>
+      </c>
+      <c r="I394" s="2" t="n">
+        <v>0.2581495222727284</v>
+      </c>
+      <c r="J394" s="2" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="K394" s="3" t="inlineStr"/>
+      <c r="L394" s="3" t="inlineStr"/>
+      <c r="M394" s="3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="N394" s="4" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="O394" s="3" t="inlineStr"/>
+      <c r="P394" s="2" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="Q394" t="inlineStr"/>
+      <c r="R394" t="n">
+        <v>160</v>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T394" s="5" t="inlineStr"/>
+      <c r="U394" s="5" t="inlineStr"/>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W394" t="inlineStr">
+        <is>
+          <t>COMPASS, PLB 870 139832 (2025), Q2 projection</t>
+        </is>
+      </c>
+      <c r="X394" s="5" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="Y394" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Z394" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA394" s="5" t="inlineStr"/>
+      <c r="AB394" s="5" t="inlineStr"/>
+      <c r="AC394" s="5" t="inlineStr"/>
+      <c r="AD394" s="5" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="AE394" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF394" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AG394" s="5" t="inlineStr"/>
+      <c r="AH394" s="5" t="inlineStr"/>
+      <c r="AI394" s="5" t="inlineStr"/>
+      <c r="AJ394" s="5" t="inlineStr"/>
+      <c r="AK394" s="5" t="inlineStr"/>
+      <c r="AL394" s="5" t="inlineStr"/>
+      <c r="AM394" s="5" t="inlineStr"/>
+      <c r="AN394" s="5" t="inlineStr"/>
+      <c r="AO394" s="5" t="inlineStr"/>
+      <c r="AP394" s="5" t="inlineStr"/>
+      <c r="AQ394" s="5" t="inlineStr"/>
+      <c r="AR394" s="5" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>COMPASS_y25</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>compass_Q2</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F395" s="2" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="G395" s="2" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="H395" s="2" t="n">
+        <v>0.02567379528513003</v>
+      </c>
+      <c r="I395" s="2" t="n">
+        <v>0.28432620471487</v>
+      </c>
+      <c r="J395" s="2" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="K395" s="3" t="inlineStr"/>
+      <c r="L395" s="3" t="inlineStr"/>
+      <c r="M395" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="N395" s="4" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="O395" s="3" t="inlineStr"/>
+      <c r="P395" s="2" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="Q395" t="inlineStr"/>
+      <c r="R395" t="n">
+        <v>160</v>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T395" s="5" t="inlineStr"/>
+      <c r="U395" s="5" t="inlineStr"/>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W395" t="inlineStr">
+        <is>
+          <t>COMPASS, PLB 870 139832 (2025), Q2 projection</t>
+        </is>
+      </c>
+      <c r="X395" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y395" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Z395" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA395" s="5" t="inlineStr"/>
+      <c r="AB395" s="5" t="inlineStr"/>
+      <c r="AC395" s="5" t="inlineStr"/>
+      <c r="AD395" s="5" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="AE395" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF395" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG395" s="5" t="inlineStr"/>
+      <c r="AH395" s="5" t="inlineStr"/>
+      <c r="AI395" s="5" t="inlineStr"/>
+      <c r="AJ395" s="5" t="inlineStr"/>
+      <c r="AK395" s="5" t="inlineStr"/>
+      <c r="AL395" s="5" t="inlineStr"/>
+      <c r="AM395" s="5" t="inlineStr"/>
+      <c r="AN395" s="5" t="inlineStr"/>
+      <c r="AO395" s="5" t="inlineStr"/>
+      <c r="AP395" s="5" t="inlineStr"/>
+      <c r="AQ395" s="5" t="inlineStr"/>
+      <c r="AR395" s="5" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>COMPASS_y25</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>compass_Q2</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F396" s="2" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="G396" s="2" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="H396" s="2" t="n">
+        <v>0.07002657658567468</v>
+      </c>
+      <c r="I396" s="2" t="n">
+        <v>0.2599734234143253</v>
+      </c>
+      <c r="J396" s="2" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="K396" s="3" t="inlineStr"/>
+      <c r="L396" s="3" t="inlineStr"/>
+      <c r="M396" s="3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N396" s="4" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="O396" s="3" t="inlineStr"/>
+      <c r="P396" s="2" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="Q396" t="inlineStr"/>
+      <c r="R396" t="n">
+        <v>160</v>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T396" s="5" t="inlineStr"/>
+      <c r="U396" s="5" t="inlineStr"/>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W396" t="inlineStr">
+        <is>
+          <t>COMPASS, PLB 870 139832 (2025), Q2 projection</t>
+        </is>
+      </c>
+      <c r="X396" s="5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y396" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z396" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AA396" s="5" t="inlineStr"/>
+      <c r="AB396" s="5" t="inlineStr"/>
+      <c r="AC396" s="5" t="inlineStr"/>
+      <c r="AD396" s="5" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AE396" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF396" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG396" s="5" t="inlineStr"/>
+      <c r="AH396" s="5" t="inlineStr"/>
+      <c r="AI396" s="5" t="inlineStr"/>
+      <c r="AJ396" s="5" t="inlineStr"/>
+      <c r="AK396" s="5" t="inlineStr"/>
+      <c r="AL396" s="5" t="inlineStr"/>
+      <c r="AM396" s="5" t="inlineStr"/>
+      <c r="AN396" s="5" t="inlineStr"/>
+      <c r="AO396" s="5" t="inlineStr"/>
+      <c r="AP396" s="5" t="inlineStr"/>
+      <c r="AQ396" s="5" t="inlineStr"/>
+      <c r="AR396" s="5" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>COMPASS_y25</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>compass_nu</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F397" s="2" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="G397" s="2" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="H397" s="2" t="n">
+        <v>0.0253132710014885</v>
+      </c>
+      <c r="I397" s="2" t="n">
+        <v>0.2846867289985115</v>
+      </c>
+      <c r="J397" s="2" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="K397" s="3" t="inlineStr"/>
+      <c r="L397" s="3" t="inlineStr"/>
+      <c r="M397" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N397" s="4" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="O397" s="3" t="inlineStr"/>
+      <c r="P397" s="2" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="Q397" t="inlineStr"/>
+      <c r="R397" t="n">
+        <v>160</v>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T397" s="5" t="inlineStr"/>
+      <c r="U397" s="5" t="inlineStr"/>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W397" t="inlineStr">
+        <is>
+          <t>COMPASS, PLB 870 139832 (2025), nu projection</t>
+        </is>
+      </c>
+      <c r="X397" s="5" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="Y397" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z397" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA397" s="5" t="inlineStr"/>
+      <c r="AB397" s="5" t="inlineStr"/>
+      <c r="AC397" s="5" t="inlineStr"/>
+      <c r="AD397" s="5" t="n">
+        <v>-26.2</v>
+      </c>
+      <c r="AE397" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AF397" s="5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG397" s="5" t="inlineStr"/>
+      <c r="AH397" s="5" t="inlineStr"/>
+      <c r="AI397" s="5" t="inlineStr"/>
+      <c r="AJ397" s="5" t="inlineStr"/>
+      <c r="AK397" s="5" t="inlineStr"/>
+      <c r="AL397" s="5" t="inlineStr"/>
+      <c r="AM397" s="5" t="inlineStr"/>
+      <c r="AN397" s="5" t="inlineStr"/>
+      <c r="AO397" s="5" t="inlineStr"/>
+      <c r="AP397" s="5" t="inlineStr"/>
+      <c r="AQ397" s="5" t="inlineStr"/>
+      <c r="AR397" s="5" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>COMPASS_y25</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>compass_nu</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F398" s="2" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="G398" s="2" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="H398" s="2" t="n">
+        <v>0.01743474968546499</v>
+      </c>
+      <c r="I398" s="2" t="n">
+        <v>0.272565250314535</v>
+      </c>
+      <c r="J398" s="2" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="K398" s="3" t="inlineStr"/>
+      <c r="L398" s="3" t="inlineStr"/>
+      <c r="M398" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N398" s="4" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="O398" s="3" t="inlineStr"/>
+      <c r="P398" s="2" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="Q398" t="inlineStr"/>
+      <c r="R398" t="n">
+        <v>160</v>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T398" s="5" t="inlineStr"/>
+      <c r="U398" s="5" t="inlineStr"/>
+      <c r="V398" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W398" t="inlineStr">
+        <is>
+          <t>COMPASS, PLB 870 139832 (2025), nu projection</t>
+        </is>
+      </c>
+      <c r="X398" s="5" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y398" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z398" s="5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA398" s="5" t="inlineStr"/>
+      <c r="AB398" s="5" t="inlineStr"/>
+      <c r="AC398" s="5" t="inlineStr"/>
+      <c r="AD398" s="5" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="AE398" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF398" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AG398" s="5" t="inlineStr"/>
+      <c r="AH398" s="5" t="inlineStr"/>
+      <c r="AI398" s="5" t="inlineStr"/>
+      <c r="AJ398" s="5" t="inlineStr"/>
+      <c r="AK398" s="5" t="inlineStr"/>
+      <c r="AL398" s="5" t="inlineStr"/>
+      <c r="AM398" s="5" t="inlineStr"/>
+      <c r="AN398" s="5" t="inlineStr"/>
+      <c r="AO398" s="5" t="inlineStr"/>
+      <c r="AP398" s="5" t="inlineStr"/>
+      <c r="AQ398" s="5" t="inlineStr"/>
+      <c r="AR398" s="5" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>COMPASS_y25</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>compass_nu</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="F399" s="2" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="G399" s="2" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="H399" s="2" t="n">
+        <v>0.003079301020125325</v>
+      </c>
+      <c r="I399" s="2" t="n">
+        <v>0.2369206989798747</v>
+      </c>
+      <c r="J399" s="2" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="K399" s="3" t="inlineStr"/>
+      <c r="L399" s="3" t="inlineStr"/>
+      <c r="M399" s="3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="N399" s="4" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="O399" s="3" t="inlineStr"/>
+      <c r="P399" s="2" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="Q399" t="inlineStr"/>
+      <c r="R399" t="n">
+        <v>160</v>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T399" s="5" t="inlineStr"/>
+      <c r="U399" s="5" t="inlineStr"/>
+      <c r="V399" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W399" t="inlineStr">
+        <is>
+          <t>COMPASS, PLB 870 139832 (2025), nu projection</t>
+        </is>
+      </c>
+      <c r="X399" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y399" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z399" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AA399" s="5" t="inlineStr"/>
+      <c r="AB399" s="5" t="inlineStr"/>
+      <c r="AC399" s="5" t="inlineStr"/>
+      <c r="AD399" s="5" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="AE399" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF399" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AG399" s="5" t="inlineStr"/>
+      <c r="AH399" s="5" t="inlineStr"/>
+      <c r="AI399" s="5" t="inlineStr"/>
+      <c r="AJ399" s="5" t="inlineStr"/>
+      <c r="AK399" s="5" t="inlineStr"/>
+      <c r="AL399" s="5" t="inlineStr"/>
+      <c r="AM399" s="5" t="inlineStr"/>
+      <c r="AN399" s="5" t="inlineStr"/>
+      <c r="AO399" s="5" t="inlineStr"/>
+      <c r="AP399" s="5" t="inlineStr"/>
+      <c r="AQ399" s="5" t="inlineStr"/>
+      <c r="AR399" s="5" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>COMPASS_y25</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>compass_ref27</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F400" s="2" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="G400" s="2" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="H400" s="2" t="n">
+        <v>0.01050378440241095</v>
+      </c>
+      <c r="I400" s="2" t="n">
+        <v>0.2694962155975891</v>
+      </c>
+      <c r="J400" s="2" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="K400" s="3" t="inlineStr"/>
+      <c r="L400" s="3" t="inlineStr"/>
+      <c r="M400" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="N400" s="4" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="O400" s="3" t="inlineStr"/>
+      <c r="P400" s="2" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="Q400" t="inlineStr"/>
+      <c r="R400" t="n">
+        <v>160</v>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T400" s="5" t="inlineStr"/>
+      <c r="U400" s="5" t="inlineStr"/>
+      <c r="V400" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W400" t="inlineStr">
+        <is>
+          <t>COMPASS, PLB 870 139832 (2025), ref27 projection</t>
+        </is>
+      </c>
+      <c r="X400" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y400" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z400" s="5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA400" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB400" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC400" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD400" s="5" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AE400" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AF400" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG400" s="5" t="inlineStr"/>
+      <c r="AH400" s="5" t="inlineStr"/>
+      <c r="AI400" s="5" t="inlineStr"/>
+      <c r="AJ400" s="5" t="inlineStr"/>
+      <c r="AK400" s="5" t="inlineStr"/>
+      <c r="AL400" s="5" t="inlineStr"/>
+      <c r="AM400" s="5" t="inlineStr"/>
+      <c r="AN400" s="5" t="inlineStr"/>
+      <c r="AO400" s="5" t="inlineStr"/>
+      <c r="AP400" s="5" t="inlineStr"/>
+      <c r="AQ400" s="5" t="inlineStr"/>
+      <c r="AR400" s="5" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>COMPASS_y20</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>compass_y20</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F401" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="G401" s="2" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="H401" s="2" t="n">
+        <v>0.008489367844016771</v>
+      </c>
+      <c r="I401" s="2" t="n">
+        <v>0.07151063215598323</v>
+      </c>
+      <c r="J401" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="K401" s="3" t="inlineStr"/>
+      <c r="L401" s="3" t="inlineStr"/>
+      <c r="M401" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N401" s="4" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="O401" s="3" t="inlineStr"/>
+      <c r="P401" s="2" t="inlineStr"/>
+      <c r="Q401" t="inlineStr"/>
+      <c r="R401" t="n">
+        <v>160</v>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T401" s="5" t="inlineStr"/>
+      <c r="U401" s="5" t="inlineStr"/>
+      <c r="V401" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W401" t="inlineStr">
+        <is>
+          <t>superseded by PLB 870 139832 (2025); t here is the bin lower edge and Q2, xB are nominal, not the bin averages</t>
+        </is>
+      </c>
+      <c r="X401" s="5" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="Y401" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Z401" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA401" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB401" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC401" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD401" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE401" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF401" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG401" s="5" t="inlineStr"/>
+      <c r="AH401" s="5" t="inlineStr"/>
+      <c r="AI401" s="5" t="inlineStr"/>
+      <c r="AJ401" s="5" t="inlineStr"/>
+      <c r="AK401" s="5" t="inlineStr"/>
+      <c r="AL401" s="5" t="inlineStr"/>
+      <c r="AM401" s="5" t="inlineStr"/>
+      <c r="AN401" s="5" t="inlineStr"/>
+      <c r="AO401" s="5" t="inlineStr"/>
+      <c r="AP401" s="5" t="inlineStr"/>
+      <c r="AQ401" s="5" t="inlineStr"/>
+      <c r="AR401" s="5" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>COMPASS_y20</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>compass_y20</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F402" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="G402" s="2" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="H402" s="2" t="n">
+        <v>0.008489367844016771</v>
+      </c>
+      <c r="I402" s="2" t="n">
+        <v>0.1415106321559832</v>
+      </c>
+      <c r="J402" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="K402" s="3" t="inlineStr"/>
+      <c r="L402" s="3" t="inlineStr"/>
+      <c r="M402" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N402" s="4" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="O402" s="3" t="inlineStr"/>
+      <c r="P402" s="2" t="inlineStr"/>
+      <c r="Q402" t="inlineStr"/>
+      <c r="R402" t="n">
+        <v>160</v>
+      </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T402" s="5" t="inlineStr"/>
+      <c r="U402" s="5" t="inlineStr"/>
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W402" t="inlineStr">
+        <is>
+          <t>superseded by PLB 870 139832 (2025); t here is the bin lower edge and Q2, xB are nominal, not the bin averages</t>
+        </is>
+      </c>
+      <c r="X402" s="5" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="Y402" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Z402" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA402" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB402" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC402" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD402" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE402" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF402" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG402" s="5" t="inlineStr"/>
+      <c r="AH402" s="5" t="inlineStr"/>
+      <c r="AI402" s="5" t="inlineStr"/>
+      <c r="AJ402" s="5" t="inlineStr"/>
+      <c r="AK402" s="5" t="inlineStr"/>
+      <c r="AL402" s="5" t="inlineStr"/>
+      <c r="AM402" s="5" t="inlineStr"/>
+      <c r="AN402" s="5" t="inlineStr"/>
+      <c r="AO402" s="5" t="inlineStr"/>
+      <c r="AP402" s="5" t="inlineStr"/>
+      <c r="AQ402" s="5" t="inlineStr"/>
+      <c r="AR402" s="5" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>COMPASS_y20</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>compass_y20</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F403" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="G403" s="2" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="H403" s="2" t="n">
+        <v>0.008489367844016771</v>
+      </c>
+      <c r="I403" s="2" t="n">
+        <v>0.2115106321559832</v>
+      </c>
+      <c r="J403" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="K403" s="3" t="inlineStr"/>
+      <c r="L403" s="3" t="inlineStr"/>
+      <c r="M403" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N403" s="4" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="O403" s="3" t="inlineStr"/>
+      <c r="P403" s="2" t="inlineStr"/>
+      <c r="Q403" t="inlineStr"/>
+      <c r="R403" t="n">
+        <v>160</v>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T403" s="5" t="inlineStr"/>
+      <c r="U403" s="5" t="inlineStr"/>
+      <c r="V403" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W403" t="inlineStr">
+        <is>
+          <t>superseded by PLB 870 139832 (2025); t here is the bin lower edge and Q2, xB are nominal, not the bin averages</t>
+        </is>
+      </c>
+      <c r="X403" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y403" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z403" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA403" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB403" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC403" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD403" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE403" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF403" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG403" s="5" t="inlineStr"/>
+      <c r="AH403" s="5" t="inlineStr"/>
+      <c r="AI403" s="5" t="inlineStr"/>
+      <c r="AJ403" s="5" t="inlineStr"/>
+      <c r="AK403" s="5" t="inlineStr"/>
+      <c r="AL403" s="5" t="inlineStr"/>
+      <c r="AM403" s="5" t="inlineStr"/>
+      <c r="AN403" s="5" t="inlineStr"/>
+      <c r="AO403" s="5" t="inlineStr"/>
+      <c r="AP403" s="5" t="inlineStr"/>
+      <c r="AQ403" s="5" t="inlineStr"/>
+      <c r="AR403" s="5" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>COMPASS_y20</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>compass_y20</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F404" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="G404" s="2" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="H404" s="2" t="n">
+        <v>0.008489367844016771</v>
+      </c>
+      <c r="I404" s="2" t="n">
+        <v>0.3515106321559832</v>
+      </c>
+      <c r="J404" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="K404" s="3" t="inlineStr"/>
+      <c r="L404" s="3" t="inlineStr"/>
+      <c r="M404" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N404" s="4" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="O404" s="3" t="inlineStr"/>
+      <c r="P404" s="2" t="inlineStr"/>
+      <c r="Q404" t="inlineStr"/>
+      <c r="R404" t="n">
+        <v>160</v>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T404" s="5" t="inlineStr"/>
+      <c r="U404" s="5" t="inlineStr"/>
+      <c r="V404" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W404" t="inlineStr">
+        <is>
+          <t>superseded by PLB 870 139832 (2025); t here is the bin lower edge and Q2, xB are nominal, not the bin averages</t>
+        </is>
+      </c>
+      <c r="X404" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y404" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z404" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AA404" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB404" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC404" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD404" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE404" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF404" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG404" s="5" t="inlineStr"/>
+      <c r="AH404" s="5" t="inlineStr"/>
+      <c r="AI404" s="5" t="inlineStr"/>
+      <c r="AJ404" s="5" t="inlineStr"/>
+      <c r="AK404" s="5" t="inlineStr"/>
+      <c r="AL404" s="5" t="inlineStr"/>
+      <c r="AM404" s="5" t="inlineStr"/>
+      <c r="AN404" s="5" t="inlineStr"/>
+      <c r="AO404" s="5" t="inlineStr"/>
+      <c r="AP404" s="5" t="inlineStr"/>
+      <c r="AQ404" s="5" t="inlineStr"/>
+      <c r="AR404" s="5" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>COMPASS_y20</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>pi0</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>compass_y20</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F405" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="G405" s="2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H405" s="2" t="n">
+        <v>0.008489367844016771</v>
+      </c>
+      <c r="I405" s="2" t="n">
+        <v>0.4915106321559832</v>
+      </c>
+      <c r="J405" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="K405" s="3" t="inlineStr"/>
+      <c r="L405" s="3" t="inlineStr"/>
+      <c r="M405" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N405" s="4" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="O405" s="3" t="inlineStr"/>
+      <c r="P405" s="2" t="inlineStr"/>
+      <c r="Q405" t="inlineStr"/>
+      <c r="R405" t="n">
+        <v>160</v>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>sigma_U</t>
+        </is>
+      </c>
+      <c r="T405" s="5" t="inlineStr"/>
+      <c r="U405" s="5" t="inlineStr"/>
+      <c r="V405" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W405" t="inlineStr">
+        <is>
+          <t>superseded by PLB 870 139832 (2025); t here is the bin lower edge and Q2, xB are nominal, not the bin averages</t>
+        </is>
+      </c>
+      <c r="X405" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y405" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z405" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA405" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB405" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC405" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD405" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE405" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF405" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG405" s="5" t="inlineStr"/>
+      <c r="AH405" s="5" t="inlineStr"/>
+      <c r="AI405" s="5" t="inlineStr"/>
+      <c r="AJ405" s="5" t="inlineStr"/>
+      <c r="AK405" s="5" t="inlineStr"/>
+      <c r="AL405" s="5" t="inlineStr"/>
+      <c r="AM405" s="5" t="inlineStr"/>
+      <c r="AN405" s="5" t="inlineStr"/>
+      <c r="AO405" s="5" t="inlineStr"/>
+      <c r="AP405" s="5" t="inlineStr"/>
+      <c r="AQ405" s="5" t="inlineStr"/>
+      <c r="AR405" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pi0_eta_database.xlsx
+++ b/pi0_eta_database.xlsx
@@ -1116,7 +1116,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.58-6.64</t>
+          <t>2.52-6.77</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.290-0.560</t>
+          <t>0.280-0.584</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-1.6510..-0.3250</t>
+          <t>-1.6506..-0.3255</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -55203,25 +55203,27 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>4.65</v>
+        <v>2.5495</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>0.37</v>
+        <v>0.2952</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>-0.358</v>
+        <v>-0.3255</v>
       </c>
       <c r="H76" s="6" t="n">
-        <v>0.1832</v>
+        <v>0.0711</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="J76" s="6" t="inlineStr"/>
+        <v>0.0246</v>
+      </c>
+      <c r="J76" s="6" t="n">
+        <v>0.0241</v>
+      </c>
       <c r="K76" t="n">
         <v>10.6</v>
       </c>
@@ -55232,7 +55234,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -55254,25 +55256,27 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>4.65</v>
+        <v>2.553</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0.37</v>
+        <v>0.2959</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>-0.488</v>
+        <v>-0.626</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>0.133</v>
+        <v>0.0655</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>0.0523</v>
-      </c>
-      <c r="J77" s="6" t="inlineStr"/>
+        <v>0.0222</v>
+      </c>
+      <c r="J77" s="6" t="n">
+        <v>0.0307</v>
+      </c>
       <c r="K77" t="n">
         <v>10.6</v>
       </c>
@@ -55283,7 +55287,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -55305,25 +55309,27 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>4.65</v>
+        <v>2.6203</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0.37</v>
+        <v>0.2843</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>-0.654</v>
+        <v>-1.3359</v>
       </c>
       <c r="H78" s="6" t="n">
-        <v>0.0422</v>
+        <v>0.0253</v>
       </c>
       <c r="I78" s="6" t="n">
-        <v>0.0427</v>
-      </c>
-      <c r="J78" s="6" t="inlineStr"/>
+        <v>0.025</v>
+      </c>
+      <c r="J78" s="6" t="n">
+        <v>0.0337</v>
+      </c>
       <c r="K78" t="n">
         <v>10.6</v>
       </c>
@@ -55334,7 +55340,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -55356,25 +55362,27 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>4.65</v>
+        <v>2.8677</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>0.37</v>
+        <v>0.3915</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>-0.806</v>
+        <v>-0.3356</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.0259</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>0.0475</v>
-      </c>
-      <c r="J79" s="6" t="inlineStr"/>
+        <v>0.0173</v>
+      </c>
+      <c r="J79" s="6" t="n">
+        <v>0.0242</v>
+      </c>
       <c r="K79" t="n">
         <v>10.6</v>
       </c>
@@ -55385,7 +55393,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -55407,25 +55415,27 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>4.65</v>
+        <v>2.9663</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>0.37</v>
+        <v>0.3955</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>-1.36</v>
+        <v>-0.6188</v>
       </c>
       <c r="H80" s="6" t="n">
-        <v>0.1056</v>
+        <v>0.0608</v>
       </c>
       <c r="I80" s="6" t="n">
-        <v>0.0409</v>
-      </c>
-      <c r="J80" s="6" t="inlineStr"/>
+        <v>0.014</v>
+      </c>
+      <c r="J80" s="6" t="n">
+        <v>0.0227</v>
+      </c>
       <c r="K80" t="n">
         <v>10.6</v>
       </c>
@@ -55436,7 +55446,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -55458,25 +55468,27 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>4.65</v>
+        <v>3.1997</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>0.37</v>
+        <v>0.3948</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>-1.448</v>
+        <v>-1.2711</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>0.1352</v>
+        <v>0.0432</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>0.0394</v>
-      </c>
-      <c r="J81" s="6" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="J81" s="6" t="n">
+        <v>0.0289</v>
+      </c>
       <c r="K81" t="n">
         <v>10.6</v>
       </c>
@@ -55487,7 +55499,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -55509,25 +55521,27 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>2.58</v>
+        <v>4.5846</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>0.29</v>
+        <v>0.368</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>-0.325</v>
+        <v>-0.3584</v>
       </c>
       <c r="H82" s="6" t="n">
-        <v>0.1336</v>
+        <v>0.1259</v>
       </c>
       <c r="I82" s="6" t="n">
-        <v>0.0399</v>
-      </c>
-      <c r="J82" s="6" t="inlineStr"/>
+        <v>0.0381</v>
+      </c>
+      <c r="J82" s="6" t="n">
+        <v>0.0468</v>
+      </c>
       <c r="K82" t="n">
         <v>10.6</v>
       </c>
@@ -55538,7 +55552,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -55560,25 +55574,27 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>2.58</v>
+        <v>4.725</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>-0.484</v>
+        <v>-0.654</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>0.1263</v>
+        <v>0.029</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="J83" s="6" t="inlineStr"/>
+        <v>0.0338</v>
+      </c>
+      <c r="J83" s="6" t="n">
+        <v>0.0277</v>
+      </c>
       <c r="K83" t="n">
         <v>10.6</v>
       </c>
@@ -55589,7 +55605,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -55611,25 +55627,27 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>2.58</v>
+        <v>4.6608</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>0.29</v>
+        <v>0.3691</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>-0.626</v>
+        <v>-1.3596</v>
       </c>
       <c r="H84" s="6" t="n">
-        <v>0.1229</v>
+        <v>0.0726</v>
       </c>
       <c r="I84" s="6" t="n">
-        <v>0.0353</v>
-      </c>
-      <c r="J84" s="6" t="inlineStr"/>
+        <v>0.0325</v>
+      </c>
+      <c r="J84" s="6" t="n">
+        <v>0.03</v>
+      </c>
       <c r="K84" t="n">
         <v>10.6</v>
       </c>
@@ -55640,7 +55658,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -55662,25 +55680,27 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>2.58</v>
+        <v>3.6891</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>0.29</v>
+        <v>0.4832</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>-0.832</v>
+        <v>-0.5091</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>0.0834</v>
+        <v>0.0198</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>0.0316</v>
-      </c>
-      <c r="J85" s="6" t="inlineStr"/>
+        <v>0.0217</v>
+      </c>
+      <c r="J85" s="6" t="n">
+        <v>0.0257</v>
+      </c>
       <c r="K85" t="n">
         <v>10.6</v>
       </c>
@@ -55691,7 +55711,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -55713,25 +55733,27 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>2.58</v>
+        <v>4.0646</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>0.29</v>
+        <v>0.5118</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>-1.336</v>
+        <v>-0.7857</v>
       </c>
       <c r="H86" s="6" t="n">
-        <v>0.0475</v>
+        <v>0.0484</v>
       </c>
       <c r="I86" s="6" t="n">
-        <v>0.0406</v>
-      </c>
-      <c r="J86" s="6" t="inlineStr"/>
+        <v>0.0186</v>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>0.0229</v>
+      </c>
       <c r="K86" t="n">
         <v>10.6</v>
       </c>
@@ -55742,7 +55764,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -55764,25 +55786,27 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>2.58</v>
+        <v>4.3727</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>0.29</v>
+        <v>0.5275</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>-1.472</v>
+        <v>-1.3613</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>0.0615</v>
+        <v>0.0805</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>0.0305</v>
-      </c>
-      <c r="J87" s="6" t="inlineStr"/>
+        <v>0.0187</v>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>0.0293</v>
+      </c>
       <c r="K87" t="n">
         <v>10.6</v>
       </c>
@@ -55793,7 +55817,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -55815,25 +55839,27 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>4.14</v>
+        <v>6.0104</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>0.51</v>
+        <v>0.5049</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>-0.509</v>
+        <v>-0.6398</v>
       </c>
       <c r="H88" s="6" t="n">
-        <v>0.0395</v>
+        <v>0.0597</v>
       </c>
       <c r="I88" s="6" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="J88" s="6" t="inlineStr"/>
+        <v>0.0335</v>
+      </c>
+      <c r="J88" s="6" t="n">
+        <v>0.0416</v>
+      </c>
       <c r="K88" t="n">
         <v>10.6</v>
       </c>
@@ -55844,7 +55870,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -55866,25 +55892,27 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>4.14</v>
+        <v>6.4545</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>0.51</v>
+        <v>0.5523</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-1.0374</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>0.095</v>
+        <v>0.0871</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="J89" s="6" t="inlineStr"/>
+        <v>0.0312</v>
+      </c>
+      <c r="J89" s="6" t="n">
+        <v>0.0295</v>
+      </c>
       <c r="K89" t="n">
         <v>10.6</v>
       </c>
@@ -55895,7 +55923,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -55917,25 +55945,27 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>4.14</v>
+        <v>6.7747</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>0.51</v>
+        <v>0.5841</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>-0.786</v>
+        <v>-1.6012</v>
       </c>
       <c r="H90" s="6" t="n">
-        <v>0.0968</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="I90" s="6" t="n">
-        <v>0.0307</v>
-      </c>
-      <c r="J90" s="6" t="inlineStr"/>
+        <v>0.0291</v>
+      </c>
+      <c r="J90" s="6" t="n">
+        <v>0.0285</v>
+      </c>
       <c r="K90" t="n">
         <v>10.6</v>
       </c>
@@ -55946,7 +55976,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -55968,25 +55998,27 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>4.14</v>
+        <v>2.5152</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>0.51</v>
+        <v>0.2891</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>-0.878</v>
+        <v>-0.4835</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>0.1044</v>
+        <v>0.0673</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>0.0343</v>
-      </c>
-      <c r="J91" s="6" t="inlineStr"/>
+        <v>0.0209</v>
+      </c>
+      <c r="J91" s="6" t="n">
+        <v>0.0268</v>
+      </c>
       <c r="K91" t="n">
         <v>10.6</v>
       </c>
@@ -55997,7 +56029,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -56019,25 +56051,27 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>4.14</v>
+        <v>2.515</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>0.51</v>
+        <v>0.2912</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>-1.361</v>
+        <v>-0.8321</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>0.1608</v>
+        <v>0.0444</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>0.0309</v>
-      </c>
-      <c r="J92" s="6" t="inlineStr"/>
+        <v>0.0202</v>
+      </c>
+      <c r="J92" s="6" t="n">
+        <v>0.0227</v>
+      </c>
       <c r="K92" t="n">
         <v>10.6</v>
       </c>
@@ -56048,7 +56082,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -56070,25 +56104,27 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>4.14</v>
+        <v>2.5472</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>0.51</v>
+        <v>0.2802</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>-1.447</v>
+        <v>-1.4717</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0328</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="J93" s="6" t="inlineStr"/>
+        <v>0.0196</v>
+      </c>
+      <c r="J93" s="6" t="n">
+        <v>0.0247</v>
+      </c>
       <c r="K93" t="n">
         <v>10.6</v>
       </c>
@@ -56099,7 +56135,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -56121,25 +56157,27 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>3.02</v>
+        <v>2.8221</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>0.39</v>
+        <v>0.3937</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>-0.336</v>
+        <v>-0.4729</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>0.0551</v>
+        <v>0.0321</v>
       </c>
       <c r="I94" s="6" t="n">
-        <v>0.0305</v>
-      </c>
-      <c r="J94" s="6" t="inlineStr"/>
+        <v>0.0176</v>
+      </c>
+      <c r="J94" s="6" t="n">
+        <v>0.029</v>
+      </c>
       <c r="K94" t="n">
         <v>10.6</v>
       </c>
@@ -56150,7 +56188,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -56172,25 +56210,27 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>0.39</v>
+        <v>0.3926</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>-0.473</v>
+        <v>-0.7557</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0567</v>
       </c>
       <c r="I95" s="6" t="n">
-        <v>0.0313</v>
-      </c>
-      <c r="J95" s="6" t="inlineStr"/>
+        <v>0.0171</v>
+      </c>
+      <c r="J95" s="6" t="n">
+        <v>0.027</v>
+      </c>
       <c r="K95" t="n">
         <v>10.6</v>
       </c>
@@ -56201,7 +56241,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -56223,25 +56263,27 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>3.02</v>
+        <v>3.0698</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>0.39</v>
+        <v>0.3926</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>-0.619</v>
+        <v>-1.3199</v>
       </c>
       <c r="H96" s="6" t="n">
-        <v>0.1296</v>
+        <v>0.0543</v>
       </c>
       <c r="I96" s="6" t="n">
-        <v>0.0236</v>
-      </c>
-      <c r="J96" s="6" t="inlineStr"/>
+        <v>0.0162</v>
+      </c>
+      <c r="J96" s="6" t="n">
+        <v>0.0256</v>
+      </c>
       <c r="K96" t="n">
         <v>10.6</v>
       </c>
@@ -56252,7 +56294,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -56274,25 +56316,27 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>3.02</v>
+        <v>4.5121</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>0.39</v>
+        <v>0.3609</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>-0.756</v>
+        <v>-0.4884</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>0.121</v>
+        <v>0.0914</v>
       </c>
       <c r="I97" s="6" t="n">
-        <v>0.0302</v>
-      </c>
-      <c r="J97" s="6" t="inlineStr"/>
+        <v>0.0403</v>
+      </c>
+      <c r="J97" s="6" t="n">
+        <v>0.0419</v>
+      </c>
       <c r="K97" t="n">
         <v>10.6</v>
       </c>
@@ -56303,7 +56347,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -56325,25 +56369,27 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>3.02</v>
+        <v>4.631</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>0.39</v>
+        <v>0.3717</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>-1.271</v>
+        <v>-0.8062</v>
       </c>
       <c r="H98" s="6" t="n">
-        <v>0.0922</v>
+        <v>0.0581</v>
       </c>
       <c r="I98" s="6" t="n">
-        <v>0.0362</v>
-      </c>
-      <c r="J98" s="6" t="inlineStr"/>
+        <v>0.0371</v>
+      </c>
+      <c r="J98" s="6" t="n">
+        <v>0.0313</v>
+      </c>
       <c r="K98" t="n">
         <v>10.6</v>
       </c>
@@ -56354,7 +56400,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -56376,25 +56422,27 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>3.02</v>
+        <v>4.573</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>0.39</v>
+        <v>0.3626</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>-1.32</v>
+        <v>-1.4475</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>0.1157</v>
+        <v>0.0929</v>
       </c>
       <c r="I99" s="6" t="n">
-        <v>0.0282</v>
-      </c>
-      <c r="J99" s="6" t="inlineStr"/>
+        <v>0.0315</v>
+      </c>
+      <c r="J99" s="6" t="n">
+        <v>0.0287</v>
+      </c>
       <c r="K99" t="n">
         <v>10.6</v>
       </c>
@@ -56405,7 +56453,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -56427,25 +56475,27 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>6.64</v>
+        <v>3.6791</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4897</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>-0.64</v>
+        <v>-0.5611</v>
       </c>
       <c r="H100" s="6" t="n">
-        <v>0.0891</v>
+        <v>0.0476</v>
       </c>
       <c r="I100" s="6" t="n">
-        <v>0.0436</v>
-      </c>
-      <c r="J100" s="6" t="inlineStr"/>
+        <v>0.0232</v>
+      </c>
+      <c r="J100" s="6" t="n">
+        <v>0.0338</v>
+      </c>
       <c r="K100" t="n">
         <v>10.6</v>
       </c>
@@ -56456,7 +56506,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -56478,25 +56528,27 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>6.64</v>
+        <v>4.0496</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5155</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>-0.733</v>
+        <v>-0.8779</v>
       </c>
       <c r="H101" s="6" t="n">
-        <v>0.1149</v>
+        <v>0.0523</v>
       </c>
       <c r="I101" s="6" t="n">
-        <v>0.0519</v>
-      </c>
-      <c r="J101" s="6" t="inlineStr"/>
+        <v>0.0204</v>
+      </c>
+      <c r="J101" s="6" t="n">
+        <v>0.0296</v>
+      </c>
       <c r="K101" t="n">
         <v>10.6</v>
       </c>
@@ -56507,7 +56559,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -56529,25 +56581,27 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>6.64</v>
+        <v>4.2635</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5234</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>-1.037</v>
+        <v>-1.4471</v>
       </c>
       <c r="H102" s="6" t="n">
-        <v>0.1299</v>
+        <v>0.039</v>
       </c>
       <c r="I102" s="6" t="n">
-        <v>0.0402</v>
-      </c>
-      <c r="J102" s="6" t="inlineStr"/>
+        <v>0.0197</v>
+      </c>
+      <c r="J102" s="6" t="n">
+        <v>0.0399</v>
+      </c>
       <c r="K102" t="n">
         <v>10.6</v>
       </c>
@@ -56558,7 +56612,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -56580,25 +56634,27 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>6.64</v>
+        <v>5.9867</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5131</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>-1.146</v>
+        <v>-0.733</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>0.176</v>
+        <v>0.077</v>
       </c>
       <c r="I103" s="6" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="J103" s="6" t="inlineStr"/>
+        <v>0.0391</v>
+      </c>
+      <c r="J103" s="6" t="n">
+        <v>0.0377</v>
+      </c>
       <c r="K103" t="n">
         <v>10.6</v>
       </c>
@@ -56609,7 +56665,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -56631,25 +56687,27 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>6.64</v>
+        <v>6.3396</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5543</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>-1.601</v>
+        <v>-1.1461</v>
       </c>
       <c r="H104" s="6" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.118</v>
       </c>
       <c r="I104" s="6" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="J104" s="6" t="inlineStr"/>
+        <v>0.0358</v>
+      </c>
+      <c r="J104" s="6" t="n">
+        <v>0.0443</v>
+      </c>
       <c r="K104" t="n">
         <v>10.6</v>
       </c>
@@ -56660,7 +56718,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>
@@ -56682,25 +56740,27 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>A_LU^sinphi</t>
+          <t>sigma_LT'/sigma_0</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>6.64</v>
+        <v>6.587</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5782</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>-1.651</v>
+        <v>-1.6506</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>0.0215</v>
+        <v>0.0144</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>0.0443</v>
-      </c>
-      <c r="J105" s="6" t="inlineStr"/>
+        <v>0.034</v>
+      </c>
+      <c r="J105" s="6" t="n">
+        <v>0.0233</v>
+      </c>
       <c r="K105" t="n">
         <v>10.6</v>
       </c>
@@ -56711,7 +56771,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Kim et al., PLB 849 138459 (2024), figure extraction</t>
+          <t>Kim et al., PLB 849 138459 (2024), supplemental tables III and IV</t>
         </is>
       </c>
     </row>

--- a/pi0_eta_database.xlsx
+++ b/pi0_eta_database.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Zhao et al., PLB 789 426 (2019), figure extraction</t>
+          <t>Zhao et al., PLB 789 426 (2019), figure 5 read from the vector PDF</t>
         </is>
       </c>
     </row>
@@ -54580,13 +54580,13 @@
         <v>-0.26</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>0.2122</v>
+        <v>0.212</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>0.027</v>
+        <v>0.035</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0478</v>
       </c>
       <c r="K64" t="n">
         <v>5.776</v>
@@ -54598,7 +54598,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Zhao et al., PLB 789 426 (2019), figure extraction</t>
+          <t>Zhao et al., PLB 789 426 (2019), figure 5 read from the vector PDF</t>
         </is>
       </c>
     </row>
@@ -54636,10 +54636,10 @@
         <v>0.0951</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>0.026</v>
+        <v>0.034</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0243</v>
       </c>
       <c r="K65" t="n">
         <v>5.776</v>
@@ -54651,7 +54651,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Zhao et al., PLB 789 426 (2019), figure extraction</t>
+          <t>Zhao et al., PLB 789 426 (2019), figure 5 read from the vector PDF</t>
         </is>
       </c>
     </row>
@@ -54689,10 +54689,10 @@
         <v>0.1231</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>0.029</v>
+        <v>0.037</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0393</v>
       </c>
       <c r="K66" t="n">
         <v>5.776</v>
@@ -54704,7 +54704,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Zhao et al., PLB 789 426 (2019), figure extraction</t>
+          <t>Zhao et al., PLB 789 426 (2019), figure 5 read from the vector PDF</t>
         </is>
       </c>
     </row>
@@ -54739,13 +54739,13 @@
         <v>-0.258</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>0.1471</v>
+        <v>0.147</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>0.032</v>
+        <v>0.04</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0346</v>
       </c>
       <c r="K67" t="n">
         <v>5.776</v>
@@ -54757,7 +54757,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Zhao et al., PLB 789 426 (2019), figure extraction</t>
+          <t>Zhao et al., PLB 789 426 (2019), figure 5 read from the vector PDF</t>
         </is>
       </c>
     </row>
@@ -54792,13 +54792,13 @@
         <v>-0.577</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>0.1331</v>
+        <v>0.133</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>0.026</v>
+        <v>0.034</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0218</v>
       </c>
       <c r="K68" t="n">
         <v>5.776</v>
@@ -54810,7 +54810,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Zhao et al., PLB 789 426 (2019), figure extraction</t>
+          <t>Zhao et al., PLB 789 426 (2019), figure 5 read from the vector PDF</t>
         </is>
       </c>
     </row>
@@ -54845,13 +54845,13 @@
         <v>-1.13</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>0.1631</v>
+        <v>0.163</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>0.035</v>
+        <v>0.043</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0367</v>
       </c>
       <c r="K69" t="n">
         <v>5.776</v>
@@ -54863,7 +54863,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Zhao et al., PLB 789 426 (2019), figure extraction</t>
+          <t>Zhao et al., PLB 789 426 (2019), figure 5 read from the vector PDF</t>
         </is>
       </c>
     </row>
@@ -54898,13 +54898,13 @@
         <v>-0.318</v>
       </c>
       <c r="H70" s="6" t="n">
-        <v>0.2031</v>
+        <v>0.2081</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>0.0528</v>
+        <v>0.0597</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="K70" t="n">
         <v>5.776</v>
@@ -54916,7 +54916,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Zhao et al., PLB 789 426 (2019), figure extraction</t>
+          <t>Zhao et al., PLB 789 426 (2019), figure 5 read from the vector PDF</t>
         </is>
       </c>
     </row>
@@ -54951,13 +54951,13 @@
         <v>-0.593</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>0.131</v>
+        <v>0.1377</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>0.0238</v>
+        <v>0.0313</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0366</v>
       </c>
       <c r="K71" t="n">
         <v>5.776</v>
@@ -54969,7 +54969,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Zhao et al., PLB 789 426 (2019), figure extraction</t>
+          <t>Zhao et al., PLB 789 426 (2019), figure 5 read from the vector PDF</t>
         </is>
       </c>
     </row>
@@ -55004,13 +55004,13 @@
         <v>-1.19</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>0.137</v>
+        <v>0.1436</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>0.0218</v>
+        <v>0.0293</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0395</v>
       </c>
       <c r="K72" t="n">
         <v>5.776</v>
@@ -55022,7 +55022,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Zhao et al., PLB 789 426 (2019), figure extraction</t>
+          <t>Zhao et al., PLB 789 426 (2019), figure 5 read from the vector PDF</t>
         </is>
       </c>
     </row>
@@ -55057,13 +55057,13 @@
         <v>-0.318</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>0.1891</v>
+        <v>0.1944</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>0.0668</v>
+        <v>0.0733</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0447</v>
       </c>
       <c r="K73" t="n">
         <v>5.776</v>
@@ -55075,7 +55075,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Zhao et al., PLB 789 426 (2019), figure extraction</t>
+          <t>Zhao et al., PLB 789 426 (2019), figure 5 read from the vector PDF</t>
         </is>
       </c>
     </row>
@@ -55110,13 +55110,13 @@
         <v>-0.601</v>
       </c>
       <c r="H74" s="6" t="n">
-        <v>0.1771</v>
+        <v>0.1827</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>0.0308</v>
+        <v>0.0381</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0437</v>
       </c>
       <c r="K74" t="n">
         <v>5.776</v>
@@ -55128,7 +55128,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Zhao et al., PLB 789 426 (2019), figure extraction</t>
+          <t>Zhao et al., PLB 789 426 (2019), figure 5 read from the vector PDF</t>
         </is>
       </c>
     </row>
@@ -55163,13 +55163,13 @@
         <v>-1.21</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>0.1991</v>
+        <v>0.2042</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>0.0238</v>
+        <v>0.0313</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0438</v>
       </c>
       <c r="K75" t="n">
         <v>5.776</v>
@@ -55181,7 +55181,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Zhao et al., PLB 789 426 (2019), figure extraction</t>
+          <t>Zhao et al., PLB 789 426 (2019), figure 5 read from the vector PDF</t>
         </is>
       </c>
     </row>
